--- a/(e)CRF/Per visite/V2 - Aanmeting voetorthese/Metingen en klinische registratie/Pressure monitoring tool_patient.xlsx
+++ b/(e)CRF/Per visite/V2 - Aanmeting voetorthese/Metingen en klinische registratie/Pressure monitoring tool_patient.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kuleuven-my.sharepoint.com/personal/janou_debuyser_kuleuven_be1/Documents/Documents/PhD Brugge/Site/(e)CRF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1093" documentId="8_{ED26CC68-7C05-4D39-8592-D9D42AE93F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E852BABA-01FA-4ABA-85C7-7E0125A5F045}"/>
+  <xr:revisionPtr revIDLastSave="1111" documentId="8_{ED26CC68-7C05-4D39-8592-D9D42AE93F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63045DD7-530C-4D1B-BFA4-67F3C321410A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D8186157-3417-4030-89A9-46AA9F0BACB5}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="14400" windowHeight="7450" xr2:uid="{D8186157-3417-4030-89A9-46AA9F0BACB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Meting" sheetId="4" r:id="rId1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="110">
   <si>
     <t>LEFT</t>
   </si>
@@ -128,9 +128,6 @@
   </si>
   <si>
     <t>Guidelines:</t>
-  </si>
-  <si>
-    <t>Stance Average</t>
   </si>
   <si>
     <t>Target region</t>
@@ -337,84 +334,6 @@
     <t>Windows + Shift + S, kader rond het voetbeeld en de kleurenschaal, dan Ctrl + V in het vak hieronder. Wijzig het palet nooit tussen deelnemers of visites.</t>
   </si>
   <si>
-    <t>7. Per regio - acht regio's per voet</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>A_Rechts</t>
-  </si>
-  <si>
-    <t>Hallux</t>
-  </si>
-  <si>
-    <t>B_Rechts</t>
-  </si>
-  <si>
-    <t>Tenen 2-5</t>
-  </si>
-  <si>
-    <t>C_Rechts</t>
-  </si>
-  <si>
-    <t>Metatarsaal 1</t>
-  </si>
-  <si>
-    <t>D_Rechts</t>
-  </si>
-  <si>
-    <t>Metatarsaal 2-3</t>
-  </si>
-  <si>
-    <t>E_Rechts</t>
-  </si>
-  <si>
-    <t>Metatarsaal 4-5</t>
-  </si>
-  <si>
-    <t>F_Rechts</t>
-  </si>
-  <si>
-    <t>Mediale middenvoet</t>
-  </si>
-  <si>
-    <t>G_Rechts</t>
-  </si>
-  <si>
-    <t>Laterale middenvoet</t>
-  </si>
-  <si>
-    <t>H_Rechts</t>
-  </si>
-  <si>
-    <t>Hiel</t>
-  </si>
-  <si>
-    <t>I_Links</t>
-  </si>
-  <si>
-    <t>J_Links</t>
-  </si>
-  <si>
-    <t>K_Links</t>
-  </si>
-  <si>
-    <t>L_Links</t>
-  </si>
-  <si>
-    <t>M_Links</t>
-  </si>
-  <si>
-    <t>N_Links</t>
-  </si>
-  <si>
-    <t>O_Links</t>
-  </si>
-  <si>
-    <t>P_Links</t>
-  </si>
-  <si>
     <t>Opslaan en mailen naar janou.debuyser@kuleuven.be. Laat het bestand daarna op de laptop staan - verwijder het nooit zelf.</t>
   </si>
   <si>
@@ -430,13 +349,7 @@
     <t>4. Drie regio's per voet - de vorige voetzweer eerst</t>
   </si>
   <si>
-    <t>Eerst de regio van de vorige voetzweer (eCRF 06), ook als de druk daar laag is; vul aan met de regio's met de hoogste piekdruk. De topkleur betekent: op of boven 200 kPa. Regionamen: zie blok 7.</t>
-  </si>
-  <si>
     <t>Norm: piekdruk met zool onder 200 kPa, OF minstens 25% lager dan de referentie. De referentie is de meting zonder zool op visite 2 en blijft op maand 6, 12 en 18 dezelfde. Op visite 2 vul je in kolom D dezelfde waarde in als in kolom E; op maand 6, 12 en 18 de waarde van visite 2.</t>
-  </si>
-  <si>
-    <t>In te vullen zodra het masker beschikbaar is; tot dan blijven blok 4 en 5 de werkwijze. De codes A tot P zijn de zestien maskervelden. Kolom D: de referentie zonder zool van visite 2.</t>
   </si>
   <si>
     <t>Visite 2 - aflevering CMFO (referentie)</t>
@@ -508,15 +421,6 @@
     <t>H_Rechts Hiel</t>
   </si>
   <si>
-    <t>RAW DATA EXPORT - VISITE 2, ZONDER ZOOL</t>
-  </si>
-  <si>
-    <t>Plak de maskerexport: zestien regio's in deze volgorde, A-H rechts (boven) en I-P links (onder). Kolom J = piekdruk (kPa).</t>
-  </si>
-  <si>
-    <t>RAW DATA EXPORT - VISITE 2, MET ZOOL (SESSIE 1)</t>
-  </si>
-  <si>
     <t>Doelregio: top-2 voor-/middenvoet &gt;200 kPa + vorige voetzweer</t>
   </si>
   <si>
@@ -524,6 +428,18 @@
   </si>
   <si>
     <t>Op visite 2 aanduiden, per voet: de regio van de vorige voetzweer, plus de twee regio's in voorvoet of middenvoet met de hoogste piekdruk boven 200 kPa zonder zool. De hiel telt alleen mee als daar de vorige voetzweer zat.</t>
+  </si>
+  <si>
+    <t>Eerst de regio van de vorige voetzweer (eCRF 06), ook als de druk daar laag is; vul aan met de regio's met de hoogste piekdruk. De topkleur betekent: op of boven 200 kPa. Regio's: hiel, mediale middenvoet, laterale middenvoet, metatarsaal 1, metatarsaal 2-3, metatarsaal 4-5, hallux, tenen 2-5.</t>
+  </si>
+  <si>
+    <t>PIEKDRUK PER REGIO - VISITE 2, ZONDER ZOOL</t>
+  </si>
+  <si>
+    <t>PIEKDRUK PER REGIO - VISITE 2, MET ZOOL (SESSIE 1)</t>
+  </si>
+  <si>
+    <t>In te vullen door het studieteam. Rechts A-H (boven), links I-P (onder); kolom J = piekdruk (kPa).</t>
   </si>
 </sst>
 </file>
@@ -1259,32 +1175,26 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1304,20 +1214,26 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1365,6 +1281,30 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC78C"/>
@@ -1399,30 +1339,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC78C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFB3261E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFDE7E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE9F7EE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1498,9 +1414,13 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC78C"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE9F7EE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1518,13 +1438,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE9F7EE"/>
+        <patternFill>
+          <bgColor rgb="FFFFC78C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1569,6 +1485,30 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC78C"/>
@@ -1600,33 +1540,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE9F7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC78C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFB3261E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFDE7E9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1636,84 +1552,6 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFDE7E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE9F7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE9F7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFB3261E"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDE7E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFB3261E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFDE7E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE9F7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE9F7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFB3261E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
           <bgColor rgb="FFFDE7E9"/>
         </patternFill>
       </fill>
@@ -1745,16 +1583,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFE9F7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFB3261E"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDE7E9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1808,6 +1636,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF0F6B33"/>
       </font>
       <fill>
@@ -1838,11 +1676,89 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFB3261E"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE9F7EE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1946,77 +1862,6 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFB3261E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFDE7E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE9F7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFB3261E"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDE7E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE9F7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFB3261E"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDE7E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE9F7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC78C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF0F6B33"/>
       </font>
       <fill>
@@ -2036,37 +1881,6 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FFFDE7E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC78C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFB3261E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFDE7E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE9F7EE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2142,9 +1956,13 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC78C"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE9F7EE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2162,13 +1980,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE9F7EE"/>
+        <patternFill>
+          <bgColor rgb="FFFFC78C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2213,6 +2027,30 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC78C"/>
@@ -2244,33 +2082,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE9F7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC78C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFB3261E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFDE7E9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2280,84 +2094,6 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFDE7E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE9F7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE9F7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFB3261E"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDE7E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFB3261E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFDE7E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE9F7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE9F7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFB3261E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
           <bgColor rgb="FFFDE7E9"/>
         </patternFill>
       </fill>
@@ -2394,11 +2130,103 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC78C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC78C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFB3261E"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE9F7EE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2452,6 +2280,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF0F6B33"/>
       </font>
       <fill>
@@ -2482,11 +2320,89 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFB3261E"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE9F7EE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2590,6 +2506,17 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <color rgb="FFB3261E"/>
@@ -2598,17 +2525,6 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FFFDE7E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE9F7EE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8094,243 +8010,243 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8095213D-9ECD-435C-B0AC-E2163E82B419}">
-  <dimension ref="A1:I91"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I69"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
-    <col min="8" max="9" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="26.7265625" customWidth="1"/>
+    <col min="2" max="2" width="22.7265625" customWidth="1"/>
+    <col min="3" max="3" width="20.7265625" customWidth="1"/>
+    <col min="4" max="4" width="17.7265625" customWidth="1"/>
+    <col min="5" max="5" width="15.7265625" customWidth="1"/>
+    <col min="6" max="6" width="12.7265625" customWidth="1"/>
+    <col min="7" max="7" width="13.7265625" customWidth="1"/>
+    <col min="8" max="9" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="70" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="18" x14ac:dyDescent="0.4">
       <c r="A2" s="71" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="72" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="72" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="73" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="73" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="75" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="75" t="s">
-        <v>24</v>
       </c>
       <c r="B6" s="76"/>
       <c r="D6" s="75" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" s="76"/>
       <c r="G6" s="75" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="76"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="75" t="s">
         <v>26</v>
-      </c>
-      <c r="H6" s="76"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="75" t="s">
-        <v>27</v>
       </c>
       <c r="B7" s="76"/>
       <c r="D7" s="75" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7" s="76"/>
       <c r="G7" s="75" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="76" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="75" t="s">
         <v>29</v>
-      </c>
-      <c r="H7" s="76" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="75" t="s">
-        <v>30</v>
       </c>
       <c r="B8" s="76"/>
       <c r="D8" s="75" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" s="76"/>
       <c r="G8" s="75" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H8" s="76" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="72" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="72" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="72" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="72" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="73" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="73" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="75" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="75" t="s">
+      <c r="B13" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="75" t="s">
+      <c r="D13" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="75" t="s">
+      <c r="F13" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="75" t="s">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="75" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="75" t="s">
+      <c r="B14" t="s">
         <v>42</v>
-      </c>
-      <c r="B14" t="s">
-        <v>43</v>
       </c>
       <c r="D14" s="76"/>
       <c r="F14" s="76"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" t="s">
         <v>44</v>
-      </c>
-      <c r="B15" t="s">
-        <v>45</v>
       </c>
       <c r="D15" s="76"/>
       <c r="F15" s="76"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="72" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="73" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="73" t="s">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B19" s="77" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="77" t="s">
+      <c r="E19" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="77" t="s">
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="75" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="75" t="s">
+      <c r="B20" s="78" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="78" t="s">
+      <c r="C20" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="78" t="s">
+      <c r="E20" s="78" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="78" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="74" t="s">
         <v>52</v>
-      </c>
-      <c r="E20" s="78" t="s">
-        <v>51</v>
-      </c>
-      <c r="F20" s="78" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="74" t="s">
-        <v>53</v>
       </c>
       <c r="B21" s="76"/>
       <c r="C21" s="76"/>
       <c r="E21" s="76"/>
       <c r="F21" s="76"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="74" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" s="76"/>
       <c r="C22" s="76"/>
       <c r="E22" s="76"/>
       <c r="F22" s="76"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="74" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B23" s="76"/>
       <c r="C23" s="76"/>
       <c r="E23" s="76"/>
       <c r="F23" s="76"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="74" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B24" s="76"/>
       <c r="C24" s="76"/>
       <c r="E24" s="76"/>
       <c r="F24" s="76"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="73" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="72" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="39" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A28" s="81" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="81" t="s">
         <v>57</v>
-      </c>
-      <c r="B28" s="81" t="s">
-        <v>58</v>
       </c>
       <c r="C28" s="82"/>
       <c r="D28" s="81" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="E28" s="81" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="F28" s="81" t="s">
+        <v>58</v>
+      </c>
+      <c r="G28" s="81" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="G28" s="81" t="s">
-        <v>104</v>
-      </c>
-      <c r="H28" s="81" t="s">
+      <c r="I28" s="82"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="74" t="s">
         <v>60</v>
-      </c>
-      <c r="I28" s="82"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="74" t="s">
-        <v>61</v>
       </c>
       <c r="B29" s="76"/>
       <c r="D29" s="76"/>
@@ -8345,9 +8261,9 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="74" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B30" s="76"/>
       <c r="D30" s="76"/>
@@ -8362,9 +8278,9 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="74" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B31" s="76"/>
       <c r="D31" s="76"/>
@@ -8379,9 +8295,9 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="74" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B32" s="76"/>
       <c r="D32" s="76"/>
@@ -8396,9 +8312,9 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="74" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B33" s="76"/>
       <c r="D33" s="76"/>
@@ -8413,9 +8329,9 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="74" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B34" s="76"/>
       <c r="D34" s="76"/>
@@ -8430,9 +8346,9 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="84" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="B35" s="84"/>
       <c r="C35" s="84"/>
@@ -8443,53 +8359,53 @@
       <c r="H35" s="84"/>
       <c r="I35" s="84"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="73" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38" s="72" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39" s="72" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="72" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="72" t="s">
+    <row r="40" spans="1:9" ht="39.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="81" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="81" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" ht="64.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="81" t="s">
-        <v>57</v>
-      </c>
-      <c r="B40" s="81" t="s">
+      <c r="C40" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C40" s="81" t="s">
+      <c r="D40" s="81" t="s">
+        <v>75</v>
+      </c>
+      <c r="E40" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="81" t="s">
+        <v>58</v>
+      </c>
+      <c r="G40" s="81" t="s">
+        <v>77</v>
+      </c>
+      <c r="H40" s="81" t="s">
+        <v>59</v>
+      </c>
+      <c r="I40" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="D40" s="81" t="s">
-        <v>102</v>
-      </c>
-      <c r="E40" s="81" t="s">
-        <v>103</v>
-      </c>
-      <c r="F40" s="81" t="s">
-        <v>59</v>
-      </c>
-      <c r="G40" s="81" t="s">
-        <v>104</v>
-      </c>
-      <c r="H40" s="81" t="s">
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41" s="74" t="s">
         <v>60</v>
-      </c>
-      <c r="I40" s="81" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="74" t="s">
-        <v>61</v>
       </c>
       <c r="B41" s="76"/>
       <c r="C41" s="76"/>
@@ -8506,9 +8422,9 @@
       </c>
       <c r="I41" s="76"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="74" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B42" s="76"/>
       <c r="C42" s="76"/>
@@ -8525,9 +8441,9 @@
       </c>
       <c r="I42" s="76"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="74" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B43" s="76"/>
       <c r="C43" s="76"/>
@@ -8544,9 +8460,9 @@
       </c>
       <c r="I43" s="76"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="74" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B44" s="76"/>
       <c r="C44" s="76"/>
@@ -8563,9 +8479,9 @@
       </c>
       <c r="I44" s="76"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="74" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B45" s="76"/>
       <c r="C45" s="76"/>
@@ -8582,9 +8498,9 @@
       </c>
       <c r="I45" s="76"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="74" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B46" s="76"/>
       <c r="C46" s="76"/>
@@ -8601,30 +8517,30 @@
       </c>
       <c r="I46" s="76"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="78" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A49" s="73" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="73" t="s">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A50" s="72" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="72" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="77" t="s">
+        <v>50</v>
+      </c>
+      <c r="E51" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="E51" s="77" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="79"/>
       <c r="B52" s="79"/>
       <c r="C52" s="79"/>
@@ -8634,7 +8550,7 @@
       <c r="G52" s="79"/>
       <c r="H52" s="79"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="79"/>
       <c r="B53" s="79"/>
       <c r="C53" s="79"/>
@@ -8644,7 +8560,7 @@
       <c r="G53" s="79"/>
       <c r="H53" s="79"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="79"/>
       <c r="B54" s="79"/>
       <c r="C54" s="79"/>
@@ -8654,7 +8570,7 @@
       <c r="G54" s="79"/>
       <c r="H54" s="79"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="79"/>
       <c r="B55" s="79"/>
       <c r="C55" s="79"/>
@@ -8664,7 +8580,7 @@
       <c r="G55" s="79"/>
       <c r="H55" s="79"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="79"/>
       <c r="B56" s="79"/>
       <c r="C56" s="79"/>
@@ -8674,7 +8590,7 @@
       <c r="G56" s="79"/>
       <c r="H56" s="79"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="79"/>
       <c r="B57" s="79"/>
       <c r="C57" s="79"/>
@@ -8684,7 +8600,7 @@
       <c r="G57" s="79"/>
       <c r="H57" s="79"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="79"/>
       <c r="B58" s="79"/>
       <c r="C58" s="79"/>
@@ -8694,7 +8610,7 @@
       <c r="G58" s="79"/>
       <c r="H58" s="79"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" s="79"/>
       <c r="B59" s="79"/>
       <c r="C59" s="79"/>
@@ -8704,7 +8620,7 @@
       <c r="G59" s="79"/>
       <c r="H59" s="79"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="79"/>
       <c r="B60" s="79"/>
       <c r="C60" s="79"/>
@@ -8714,7 +8630,7 @@
       <c r="G60" s="79"/>
       <c r="H60" s="79"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="79"/>
       <c r="B61" s="79"/>
       <c r="C61" s="79"/>
@@ -8724,7 +8640,7 @@
       <c r="G61" s="79"/>
       <c r="H61" s="79"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="79"/>
       <c r="B62" s="79"/>
       <c r="C62" s="79"/>
@@ -8734,7 +8650,7 @@
       <c r="G62" s="79"/>
       <c r="H62" s="79"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="79"/>
       <c r="B63" s="79"/>
       <c r="C63" s="79"/>
@@ -8744,7 +8660,7 @@
       <c r="G63" s="79"/>
       <c r="H63" s="79"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" s="79"/>
       <c r="B64" s="79"/>
       <c r="C64" s="79"/>
@@ -8754,7 +8670,7 @@
       <c r="G64" s="79"/>
       <c r="H64" s="79"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="79"/>
       <c r="B65" s="79"/>
       <c r="C65" s="79"/>
@@ -8764,7 +8680,7 @@
       <c r="G65" s="79"/>
       <c r="H65" s="79"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="79"/>
       <c r="B66" s="79"/>
       <c r="C66" s="79"/>
@@ -8774,7 +8690,7 @@
       <c r="G66" s="79"/>
       <c r="H66" s="79"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="79"/>
       <c r="B67" s="79"/>
       <c r="C67" s="79"/>
@@ -8784,358 +8700,9 @@
       <c r="G67" s="79"/>
       <c r="H67" s="79"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="73" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="72" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="39" x14ac:dyDescent="0.25">
-      <c r="A71" s="81" t="s">
-        <v>76</v>
-      </c>
-      <c r="B71" s="81" t="s">
-        <v>58</v>
-      </c>
-      <c r="C71" s="82"/>
-      <c r="D71" s="81" t="s">
-        <v>102</v>
-      </c>
-      <c r="E71" s="81" t="s">
-        <v>103</v>
-      </c>
-      <c r="F71" s="81" t="s">
-        <v>59</v>
-      </c>
-      <c r="G71" s="81" t="s">
-        <v>104</v>
-      </c>
-      <c r="H71" s="81" t="s">
-        <v>60</v>
-      </c>
-      <c r="I71" s="82"/>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="77" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="74" t="s">
-        <v>77</v>
-      </c>
-      <c r="B73" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="D73" s="76"/>
-      <c r="E73" s="76"/>
-      <c r="F73" s="76"/>
-      <c r="G73" s="80" t="str">
-        <f t="shared" ref="G73:G80" si="4">IF(OR(D73="",F73=""),"",(D73-F73)/D73)</f>
-        <v/>
-      </c>
-      <c r="H73" s="12" t="str">
-        <f t="shared" ref="H73:H80" si="5">IF(F73="","",IF(F73&lt;200,"JA",IF(D73="","referentie ontbreekt",IF((D73-F73)/D73&gt;=0.25,"JA","NEE"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="74" t="s">
-        <v>79</v>
-      </c>
-      <c r="B74" s="74" t="s">
-        <v>80</v>
-      </c>
-      <c r="D74" s="76"/>
-      <c r="E74" s="76"/>
-      <c r="F74" s="76"/>
-      <c r="G74" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H74" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="74" t="s">
-        <v>81</v>
-      </c>
-      <c r="B75" s="74" t="s">
-        <v>82</v>
-      </c>
-      <c r="D75" s="76"/>
-      <c r="E75" s="76"/>
-      <c r="F75" s="76"/>
-      <c r="G75" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H75" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="74" t="s">
-        <v>83</v>
-      </c>
-      <c r="B76" s="74" t="s">
-        <v>84</v>
-      </c>
-      <c r="D76" s="76"/>
-      <c r="E76" s="76"/>
-      <c r="F76" s="76"/>
-      <c r="G76" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H76" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="74" t="s">
-        <v>85</v>
-      </c>
-      <c r="B77" s="74" t="s">
-        <v>86</v>
-      </c>
-      <c r="D77" s="76"/>
-      <c r="E77" s="76"/>
-      <c r="F77" s="76"/>
-      <c r="G77" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H77" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="74" t="s">
-        <v>87</v>
-      </c>
-      <c r="B78" s="74" t="s">
-        <v>88</v>
-      </c>
-      <c r="D78" s="76"/>
-      <c r="E78" s="76"/>
-      <c r="F78" s="76"/>
-      <c r="G78" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H78" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="74" t="s">
-        <v>89</v>
-      </c>
-      <c r="B79" s="74" t="s">
-        <v>90</v>
-      </c>
-      <c r="D79" s="76"/>
-      <c r="E79" s="76"/>
-      <c r="F79" s="76"/>
-      <c r="G79" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H79" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="74" t="s">
-        <v>91</v>
-      </c>
-      <c r="B80" s="74" t="s">
-        <v>92</v>
-      </c>
-      <c r="D80" s="76"/>
-      <c r="E80" s="76"/>
-      <c r="F80" s="76"/>
-      <c r="G80" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H80" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="77" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="74" t="s">
-        <v>93</v>
-      </c>
-      <c r="B82" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="D82" s="76"/>
-      <c r="E82" s="76"/>
-      <c r="F82" s="76"/>
-      <c r="G82" s="80" t="str">
-        <f t="shared" ref="G82:G89" si="6">IF(OR(D82="",F82=""),"",(D82-F82)/D82)</f>
-        <v/>
-      </c>
-      <c r="H82" s="12" t="str">
-        <f t="shared" ref="H82:H89" si="7">IF(F82="","",IF(F82&lt;200,"JA",IF(D82="","referentie ontbreekt",IF((D82-F82)/D82&gt;=0.25,"JA","NEE"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="74" t="s">
-        <v>94</v>
-      </c>
-      <c r="B83" s="74" t="s">
-        <v>80</v>
-      </c>
-      <c r="D83" s="76"/>
-      <c r="E83" s="76"/>
-      <c r="F83" s="76"/>
-      <c r="G83" s="80" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H83" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="74" t="s">
-        <v>95</v>
-      </c>
-      <c r="B84" s="74" t="s">
-        <v>82</v>
-      </c>
-      <c r="D84" s="76"/>
-      <c r="E84" s="76"/>
-      <c r="F84" s="76"/>
-      <c r="G84" s="80" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H84" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="74" t="s">
-        <v>96</v>
-      </c>
-      <c r="B85" s="74" t="s">
-        <v>84</v>
-      </c>
-      <c r="D85" s="76"/>
-      <c r="E85" s="76"/>
-      <c r="F85" s="76"/>
-      <c r="G85" s="80" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H85" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="B86" s="74" t="s">
-        <v>86</v>
-      </c>
-      <c r="D86" s="76"/>
-      <c r="E86" s="76"/>
-      <c r="F86" s="76"/>
-      <c r="G86" s="80" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H86" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="74" t="s">
-        <v>98</v>
-      </c>
-      <c r="B87" s="74" t="s">
-        <v>88</v>
-      </c>
-      <c r="D87" s="76"/>
-      <c r="E87" s="76"/>
-      <c r="F87" s="76"/>
-      <c r="G87" s="80" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H87" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="74" t="s">
-        <v>99</v>
-      </c>
-      <c r="B88" s="74" t="s">
-        <v>90</v>
-      </c>
-      <c r="D88" s="76"/>
-      <c r="E88" s="76"/>
-      <c r="F88" s="76"/>
-      <c r="G88" s="80" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H88" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="74" t="s">
-        <v>100</v>
-      </c>
-      <c r="B89" s="74" t="s">
-        <v>92</v>
-      </c>
-      <c r="D89" s="76"/>
-      <c r="E89" s="76"/>
-      <c r="F89" s="76"/>
-      <c r="G89" s="80" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H89" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="75" t="s">
-        <v>101</v>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A69" s="75" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -9153,26 +8720,26 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:CT85"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="6" width="12.140625" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" customWidth="1"/>
-    <col min="9" max="11" width="12.140625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.7265625" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" customWidth="1"/>
+    <col min="3" max="3" width="23.81640625" customWidth="1"/>
+    <col min="4" max="4" width="10.7265625" customWidth="1"/>
+    <col min="5" max="6" width="12.1796875" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" customWidth="1"/>
+    <col min="9" max="11" width="12.1796875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="12.1796875" customWidth="1"/>
     <col min="13" max="13" width="3" customWidth="1"/>
-    <col min="14" max="20" width="12.140625" customWidth="1"/>
-    <col min="21" max="21" width="8.85546875" style="7"/>
+    <col min="14" max="20" width="12.1796875" customWidth="1"/>
+    <col min="21" max="21" width="8.81640625" style="7"/>
     <col min="22" max="22" width="21" style="7" customWidth="1"/>
-    <col min="23" max="25" width="13.28515625" style="7" customWidth="1"/>
-    <col min="26" max="98" width="8.85546875" style="7"/>
+    <col min="23" max="25" width="13.26953125" style="7" customWidth="1"/>
+    <col min="26" max="98" width="8.81640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:98" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:98" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="14"/>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -9194,21 +8761,21 @@
       <c r="S1" s="14"/>
       <c r="T1" s="14"/>
     </row>
-    <row r="2" spans="1:98" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:98" ht="34" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
-      <c r="E2" s="85" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="86"/>
-      <c r="L2" s="86"/>
+      <c r="E2" s="101" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="102"/>
+      <c r="L2" s="102"/>
       <c r="M2" s="13"/>
       <c r="N2" s="13"/>
       <c r="O2" s="13"/>
@@ -9218,21 +8785,21 @@
       <c r="S2" s="13"/>
       <c r="T2" s="13"/>
     </row>
-    <row r="3" spans="1:98" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:98" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
-      <c r="E3" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
+      <c r="E3" s="103" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
       <c r="M3" s="13"/>
       <c r="N3" s="13"/>
       <c r="O3" s="13"/>
@@ -9242,7 +8809,7 @@
       <c r="S3" s="13"/>
       <c r="T3" s="13"/>
     </row>
-    <row r="4" spans="1:98" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:98" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="14"/>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -9264,25 +8831,25 @@
       <c r="S4" s="14"/>
       <c r="T4" s="14"/>
       <c r="V4" s="69" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:98" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:98" x14ac:dyDescent="0.35">
       <c r="U5" s="5"/>
       <c r="X5" s="57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y5" s="56">
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:98" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:98" ht="16" x14ac:dyDescent="0.35">
       <c r="A6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="93"/>
-      <c r="C6" s="94"/>
-      <c r="D6" s="95"/>
+      <c r="B6" s="104"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="106"/>
       <c r="E6" s="64"/>
       <c r="F6" s="64"/>
       <c r="G6" s="58" t="s">
@@ -9303,13 +8870,13 @@
       <c r="T6" s="66"/>
       <c r="U6" s="5"/>
       <c r="V6" s="68" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6" s="67"/>
       <c r="X6" s="67"/>
       <c r="Y6" s="67"/>
     </row>
-    <row r="7" spans="1:98" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:98" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="16"/>
       <c r="E7" s="15"/>
       <c r="F7" s="15"/>
@@ -9317,43 +8884,43 @@
       <c r="H7" s="18"/>
       <c r="U7" s="5"/>
       <c r="V7" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="W7" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="X7" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="W7" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="X7" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y7" s="68" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:98" s="5" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:98" s="5" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8"/>
       <c r="B8"/>
       <c r="C8"/>
-      <c r="D8" s="88" t="s">
-        <v>109</v>
-      </c>
-      <c r="E8" s="89"/>
-      <c r="F8" s="89"/>
-      <c r="G8" s="89"/>
-      <c r="H8" s="89"/>
-      <c r="I8" s="89"/>
-      <c r="J8" s="89"/>
-      <c r="K8" s="89"/>
-      <c r="L8" s="90"/>
+      <c r="D8" s="98" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="99"/>
+      <c r="K8" s="99"/>
+      <c r="L8" s="100"/>
       <c r="M8"/>
-      <c r="N8" s="88" t="s">
-        <v>110</v>
-      </c>
-      <c r="O8" s="89"/>
-      <c r="P8" s="89"/>
-      <c r="Q8" s="89"/>
-      <c r="R8" s="89"/>
-      <c r="S8" s="89"/>
-      <c r="T8" s="90"/>
+      <c r="N8" s="98" t="s">
+        <v>81</v>
+      </c>
+      <c r="O8" s="99"/>
+      <c r="P8" s="99"/>
+      <c r="Q8" s="99"/>
+      <c r="R8" s="99"/>
+      <c r="S8" s="99"/>
+      <c r="T8" s="100"/>
       <c r="V8" s="67" t="str">
         <f t="shared" ref="V8:V15" si="0">C11</f>
         <v>I_Links Hallux</v>
@@ -9444,47 +9011,47 @@
       <c r="CS8" s="7"/>
       <c r="CT8" s="7"/>
     </row>
-    <row r="9" spans="1:98" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="96" t="s">
+    <row r="9" spans="1:98" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="97"/>
+      <c r="B9" s="93"/>
       <c r="C9" s="34"/>
       <c r="D9" s="35"/>
       <c r="E9" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="61" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" s="91" t="s">
+      <c r="H9" s="86"/>
+      <c r="I9" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="92"/>
-      <c r="I9" s="91" t="s">
+      <c r="J9" s="86"/>
+      <c r="K9" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="92"/>
-      <c r="K9" s="91" t="s">
-        <v>20</v>
-      </c>
-      <c r="L9" s="92"/>
+      <c r="L9" s="86"/>
       <c r="M9" s="62"/>
       <c r="N9" s="59" t="s">
-        <v>111</v>
-      </c>
-      <c r="O9" s="91" t="s">
+        <v>82</v>
+      </c>
+      <c r="O9" s="85" t="s">
+        <v>17</v>
+      </c>
+      <c r="P9" s="86"/>
+      <c r="Q9" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="P9" s="92"/>
-      <c r="Q9" s="91" t="s">
+      <c r="R9" s="86"/>
+      <c r="S9" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="R9" s="92"/>
-      <c r="S9" s="91" t="s">
-        <v>20</v>
-      </c>
-      <c r="T9" s="92"/>
+      <c r="T9" s="86"/>
       <c r="V9" s="67" t="str">
         <f t="shared" si="0"/>
         <v>J_Links Tenen 2-5</v>
@@ -9575,34 +9142,34 @@
       <c r="CS9" s="7"/>
       <c r="CT9" s="7"/>
     </row>
-    <row r="10" spans="1:98" s="5" customFormat="1" ht="72" x14ac:dyDescent="0.25">
-      <c r="A10" s="98"/>
-      <c r="B10" s="99"/>
+    <row r="10" spans="1:98" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.35">
+      <c r="A10" s="94"/>
+      <c r="B10" s="95"/>
       <c r="C10" s="34"/>
       <c r="D10" s="35"/>
       <c r="E10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="G10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="H10" s="36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="J10" s="36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="L10" s="36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M10" s="62"/>
       <c r="N10" s="36" t="s">
@@ -9612,19 +9179,19 @@
         <v>1</v>
       </c>
       <c r="P10" s="36" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="Q10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="R10" s="36" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="S10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="T10" s="36" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="V10" s="67" t="str">
         <f t="shared" si="0"/>
@@ -9716,11 +9283,11 @@
       <c r="CS10" s="7"/>
       <c r="CT10" s="7"/>
     </row>
-    <row r="11" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="98"/>
-      <c r="B11" s="99"/>
+    <row r="11" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="94"/>
+      <c r="B11" s="95"/>
       <c r="C11" s="83" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="D11" s="37"/>
       <c r="E11" s="38" t="str">
@@ -9728,45 +9295,45 @@
         <v/>
       </c>
       <c r="F11" s="39" t="str">
-        <f>IF($C$20=C11,"TARGET",IF(E11="","",IF(AND(E11&gt;200,RANK(E11,$E$11:$E$17)&lt;=2),"TARGET","")))</f>
+        <f t="shared" ref="F11:F17" si="5">IF($C$20=C11,"TARGET",IF(E11="","",IF(AND(E11&gt;200,RANK(E11,$E$11:$E$17)&lt;=2),"TARGET","")))</f>
         <v/>
       </c>
       <c r="G11" s="40" t="str">
-        <f t="shared" ref="G11:G18" si="5">IF(J78="","",J78)</f>
+        <f t="shared" ref="G11:G18" si="6">IF(J78="","",J78)</f>
         <v/>
       </c>
       <c r="H11" s="43" t="str">
-        <f t="shared" ref="H11:H18" si="6">IF(OR($E11="",G11=""),"",((G11-$E11)/$E11)*100)</f>
+        <f t="shared" ref="H11:H18" si="7">IF(OR($E11="",G11=""),"",((G11-$E11)/$E11)*100)</f>
         <v/>
       </c>
       <c r="I11" s="40"/>
       <c r="J11" s="43" t="str">
-        <f t="shared" ref="J11:J18" si="7">IF(OR($E11="",I11=""),"",((I11-$E11)/$E11)*100)</f>
+        <f t="shared" ref="J11:J18" si="8">IF(OR($E11="",I11=""),"",((I11-$E11)/$E11)*100)</f>
         <v/>
       </c>
       <c r="K11" s="40"/>
       <c r="L11" s="43" t="str">
-        <f t="shared" ref="L11:L18" si="8">IF(OR($E11="",K11=""),"",((K11-$E11)/$E11)*100)</f>
+        <f t="shared" ref="L11:L18" si="9">IF(OR($E11="",K11=""),"",((K11-$E11)/$E11)*100)</f>
         <v/>
       </c>
       <c r="M11" s="33"/>
       <c r="N11" s="40" t="str">
-        <f t="shared" ref="N11:N18" si="9">IF(E11="","",E11)</f>
+        <f t="shared" ref="N11:N18" si="10">IF(E11="","",E11)</f>
         <v/>
       </c>
       <c r="O11" s="40"/>
       <c r="P11" s="43" t="str">
-        <f t="shared" ref="P11:P18" si="10">IF(OR($N11="",O11=""),"",((O11-$N11)/$N11)*100)</f>
+        <f t="shared" ref="P11:P18" si="11">IF(OR($N11="",O11=""),"",((O11-$N11)/$N11)*100)</f>
         <v/>
       </c>
       <c r="Q11" s="40"/>
       <c r="R11" s="43" t="str">
-        <f t="shared" ref="R11:R18" si="11">IF(OR($N11="",Q11=""),"",((Q11-$N11)/$N11)*100)</f>
+        <f t="shared" ref="R11:R18" si="12">IF(OR($N11="",Q11=""),"",((Q11-$N11)/$N11)*100)</f>
         <v/>
       </c>
       <c r="S11" s="40"/>
       <c r="T11" s="43" t="str">
-        <f t="shared" ref="T11:T18" si="12">IF(OR($N11="",S11=""),"",((S11-$N11)/$N11)*100)</f>
+        <f t="shared" ref="T11:T18" si="13">IF(OR($N11="",S11=""),"",((S11-$N11)/$N11)*100)</f>
         <v/>
       </c>
       <c r="V11" s="67" t="str">
@@ -9859,11 +9426,11 @@
       <c r="CS11" s="7"/>
       <c r="CT11" s="7"/>
     </row>
-    <row r="12" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="98"/>
-      <c r="B12" s="99"/>
+    <row r="12" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
       <c r="C12" s="83" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="D12" s="37"/>
       <c r="E12" s="38" t="str">
@@ -9871,45 +9438,45 @@
         <v/>
       </c>
       <c r="F12" s="39" t="str">
-        <f>IF($C$20=C12,"TARGET",IF(E12="","",IF(AND(E12&gt;200,RANK(E12,$E$11:$E$17)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G12" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H12" s="43" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="I12" s="40"/>
       <c r="J12" s="43" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K12" s="40"/>
       <c r="L12" s="43" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="M12" s="33"/>
       <c r="N12" s="40" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="O12" s="40"/>
       <c r="P12" s="43" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="Q12" s="40"/>
       <c r="R12" s="43" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S12" s="40"/>
       <c r="T12" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="V12" s="67" t="str">
@@ -10002,11 +9569,11 @@
       <c r="CS12" s="7"/>
       <c r="CT12" s="7"/>
     </row>
-    <row r="13" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="98"/>
-      <c r="B13" s="99"/>
+    <row r="13" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
       <c r="C13" s="83" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="38" t="str">
@@ -10014,45 +9581,45 @@
         <v/>
       </c>
       <c r="F13" s="39" t="str">
-        <f>IF($C$20=C13,"TARGET",IF(E13="","",IF(AND(E13&gt;200,RANK(E13,$E$11:$E$17)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G13" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H13" s="43" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="I13" s="40"/>
       <c r="J13" s="43" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K13" s="40"/>
       <c r="L13" s="43" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="M13" s="33"/>
       <c r="N13" s="40" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="O13" s="40"/>
       <c r="P13" s="43" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="Q13" s="40"/>
       <c r="R13" s="43" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S13" s="40"/>
       <c r="T13" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="V13" s="67" t="str">
@@ -10145,11 +9712,11 @@
       <c r="CS13" s="7"/>
       <c r="CT13" s="7"/>
     </row>
-    <row r="14" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="98"/>
-      <c r="B14" s="99"/>
+    <row r="14" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
       <c r="C14" s="83" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="38" t="str">
@@ -10157,45 +9724,45 @@
         <v/>
       </c>
       <c r="F14" s="39" t="str">
-        <f>IF($C$20=C14,"TARGET",IF(E14="","",IF(AND(E14&gt;200,RANK(E14,$E$11:$E$17)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G14" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H14" s="43" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="I14" s="40"/>
       <c r="J14" s="43" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K14" s="40"/>
       <c r="L14" s="43" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="M14" s="33"/>
       <c r="N14" s="40" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="O14" s="40"/>
       <c r="P14" s="43" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="Q14" s="40"/>
       <c r="R14" s="43" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S14" s="40"/>
       <c r="T14" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="V14" s="67" t="str">
@@ -10288,11 +9855,11 @@
       <c r="CS14" s="7"/>
       <c r="CT14" s="7"/>
     </row>
-    <row r="15" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="98"/>
-      <c r="B15" s="99"/>
+    <row r="15" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
       <c r="C15" s="83" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="38" t="str">
@@ -10300,45 +9867,45 @@
         <v/>
       </c>
       <c r="F15" s="39" t="str">
-        <f>IF($C$20=C15,"TARGET",IF(E15="","",IF(AND(E15&gt;200,RANK(E15,$E$11:$E$17)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G15" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H15" s="43" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="I15" s="40"/>
       <c r="J15" s="43" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K15" s="40"/>
       <c r="L15" s="43" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="M15" s="33"/>
       <c r="N15" s="40" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="O15" s="40"/>
       <c r="P15" s="43" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="Q15" s="40"/>
       <c r="R15" s="43" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S15" s="40"/>
       <c r="T15" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="V15" s="67" t="str">
@@ -10431,11 +9998,11 @@
       <c r="CS15" s="7"/>
       <c r="CT15" s="7"/>
     </row>
-    <row r="16" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="98"/>
-      <c r="B16" s="99"/>
+    <row r="16" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
       <c r="C16" s="83" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="41" t="str">
@@ -10443,45 +10010,45 @@
         <v/>
       </c>
       <c r="F16" s="39" t="str">
-        <f>IF($C$20=C16,"TARGET",IF(E16="","",IF(AND(E16&gt;200,RANK(E16,$E$11:$E$17)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G16" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H16" s="43" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="I16" s="40"/>
       <c r="J16" s="43" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K16" s="40"/>
       <c r="L16" s="43" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="M16" s="33"/>
       <c r="N16" s="40" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="O16" s="40"/>
       <c r="P16" s="43" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="Q16" s="40"/>
       <c r="R16" s="43" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S16" s="40"/>
       <c r="T16" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="V16" s="67"/>
@@ -10562,11 +10129,11 @@
       <c r="CS16" s="7"/>
       <c r="CT16" s="7"/>
     </row>
-    <row r="17" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="98"/>
-      <c r="B17" s="99"/>
+    <row r="17" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
       <c r="C17" s="83" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="41" t="str">
@@ -10574,45 +10141,45 @@
         <v/>
       </c>
       <c r="F17" s="39" t="str">
-        <f>IF($C$20=C17,"TARGET",IF(E17="","",IF(AND(E17&gt;200,RANK(E17,$E$11:$E$17)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G17" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H17" s="43" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="I17" s="40"/>
       <c r="J17" s="43" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K17" s="40"/>
       <c r="L17" s="43" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="M17" s="33"/>
       <c r="N17" s="40" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="O17" s="40"/>
       <c r="P17" s="43" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="Q17" s="40"/>
       <c r="R17" s="43" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S17" s="40"/>
       <c r="T17" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="V17" s="67"/>
@@ -10693,11 +10260,11 @@
       <c r="CS17" s="7"/>
       <c r="CT17" s="7"/>
     </row>
-    <row r="18" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="100"/>
-      <c r="B18" s="101"/>
+    <row r="18" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="96"/>
+      <c r="B18" s="97"/>
       <c r="C18" s="83" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="D18" s="37"/>
       <c r="E18" s="41" t="str">
@@ -10709,45 +10276,45 @@
         <v/>
       </c>
       <c r="G18" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H18" s="43" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="I18" s="40"/>
       <c r="J18" s="43" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K18" s="40"/>
       <c r="L18" s="43" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="M18" s="33"/>
       <c r="N18" s="40" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="O18" s="40"/>
       <c r="P18" s="43" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="Q18" s="40"/>
       <c r="R18" s="43" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S18" s="40"/>
       <c r="T18" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="V18" s="68" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W18" s="67"/>
       <c r="X18" s="67"/>
@@ -10826,7 +10393,7 @@
       <c r="CS18" s="7"/>
       <c r="CT18" s="7"/>
     </row>
-    <row r="19" spans="1:98" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:98" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="21"/>
       <c r="B19" s="21"/>
       <c r="C19" s="48"/>
@@ -10848,16 +10415,16 @@
       <c r="S19" s="27"/>
       <c r="T19" s="42"/>
       <c r="V19" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="W19" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="X19" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y19" s="68" t="s">
         <v>11</v>
-      </c>
-      <c r="W19" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="X19" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y19" s="68" t="s">
-        <v>12</v>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
@@ -10933,43 +10500,43 @@
       <c r="CS19" s="3"/>
       <c r="CT19" s="3"/>
     </row>
-    <row r="20" spans="1:98" s="5" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="102" t="s">
-        <v>114</v>
-      </c>
-      <c r="B20" s="103"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="105"/>
-      <c r="E20" s="105"/>
-      <c r="F20" s="105"/>
-      <c r="G20" s="105"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="105"/>
-      <c r="J20" s="105"/>
-      <c r="K20" s="105"/>
-      <c r="L20" s="105"/>
-      <c r="M20" s="105"/>
-      <c r="N20" s="105"/>
-      <c r="O20" s="105"/>
-      <c r="P20" s="105"/>
-      <c r="Q20" s="105"/>
-      <c r="R20" s="105"/>
-      <c r="S20" s="105"/>
-      <c r="T20" s="105"/>
+    <row r="20" spans="1:98" s="5" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="87" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="88"/>
+      <c r="C20" s="89"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="90"/>
+      <c r="K20" s="90"/>
+      <c r="L20" s="90"/>
+      <c r="M20" s="90"/>
+      <c r="N20" s="90"/>
+      <c r="O20" s="90"/>
+      <c r="P20" s="90"/>
+      <c r="Q20" s="90"/>
+      <c r="R20" s="90"/>
+      <c r="S20" s="90"/>
+      <c r="T20" s="90"/>
       <c r="V20" s="67" t="str">
-        <f t="shared" ref="V20:V27" si="13">C27</f>
+        <f t="shared" ref="V20:V27" si="14">C27</f>
         <v>A_Rechts Hallux</v>
       </c>
       <c r="W20" s="67" t="str">
-        <f t="shared" ref="W20:W27" si="14">E27</f>
+        <f t="shared" ref="W20:W27" si="15">E27</f>
         <v/>
       </c>
       <c r="X20" s="67" t="str">
-        <f t="shared" ref="X20:X27" si="15">G27</f>
+        <f t="shared" ref="X20:X27" si="16">G27</f>
         <v/>
       </c>
       <c r="Y20" s="67">
-        <f t="shared" ref="Y20:Y27" si="16">$Y$5</f>
+        <f t="shared" ref="Y20:Y27" si="17">$Y$5</f>
         <v>200</v>
       </c>
       <c r="Z20" s="7"/>
@@ -11046,7 +10613,7 @@
       <c r="CS20" s="7"/>
       <c r="CT20" s="7"/>
     </row>
-    <row r="21" spans="1:98" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:98" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="19"/>
       <c r="B21" s="19"/>
       <c r="C21" s="28"/>
@@ -11068,19 +10635,19 @@
       <c r="S21" s="30"/>
       <c r="T21" s="32"/>
       <c r="V21" s="67" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>B_Rechts Tenen 2-5</v>
       </c>
       <c r="W21" s="67" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="X21" s="67" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Y21" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>200</v>
       </c>
       <c r="Z21" s="7"/>
@@ -11157,7 +10724,7 @@
       <c r="CS21" s="7"/>
       <c r="CT21" s="7"/>
     </row>
-    <row r="22" spans="1:98" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:98" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22"/>
@@ -11179,19 +10746,19 @@
       <c r="S22"/>
       <c r="T22"/>
       <c r="V22" s="67" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>C_Rechts Metatarsaal 1</v>
       </c>
       <c r="W22" s="67" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="X22" s="67" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Y22" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>200</v>
       </c>
       <c r="Z22" s="7"/>
@@ -11268,7 +10835,7 @@
       <c r="CS22" s="7"/>
       <c r="CT22" s="7"/>
     </row>
-    <row r="23" spans="1:98" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:98" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23"/>
       <c r="B23"/>
       <c r="C23"/>
@@ -11290,19 +10857,19 @@
       <c r="S23"/>
       <c r="T23"/>
       <c r="V23" s="67" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>D_Rechts Metatarsaal 2-3</v>
       </c>
       <c r="W23" s="67" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="X23" s="67" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Y23" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>200</v>
       </c>
       <c r="Z23" s="7"/>
@@ -11379,45 +10946,45 @@
       <c r="CS23" s="7"/>
       <c r="CT23" s="7"/>
     </row>
-    <row r="24" spans="1:98" s="5" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:98" s="5" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24"/>
       <c r="B24"/>
       <c r="C24"/>
-      <c r="D24" s="88" t="s">
-        <v>109</v>
-      </c>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="89"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="89"/>
-      <c r="K24" s="89"/>
-      <c r="L24" s="90"/>
+      <c r="D24" s="98" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="99"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="99"/>
+      <c r="H24" s="99"/>
+      <c r="I24" s="99"/>
+      <c r="J24" s="99"/>
+      <c r="K24" s="99"/>
+      <c r="L24" s="100"/>
       <c r="M24"/>
-      <c r="N24" s="88" t="s">
-        <v>110</v>
-      </c>
-      <c r="O24" s="89"/>
-      <c r="P24" s="89"/>
-      <c r="Q24" s="89"/>
-      <c r="R24" s="89"/>
-      <c r="S24" s="89"/>
-      <c r="T24" s="90"/>
+      <c r="N24" s="98" t="s">
+        <v>81</v>
+      </c>
+      <c r="O24" s="99"/>
+      <c r="P24" s="99"/>
+      <c r="Q24" s="99"/>
+      <c r="R24" s="99"/>
+      <c r="S24" s="99"/>
+      <c r="T24" s="100"/>
       <c r="V24" s="67" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>E_Rechts Metatarsaal 4-5</v>
       </c>
       <c r="W24" s="67" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="X24" s="67" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Y24" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>200</v>
       </c>
       <c r="Z24" s="7"/>
@@ -11494,61 +11061,61 @@
       <c r="CS24" s="7"/>
       <c r="CT24" s="7"/>
     </row>
-    <row r="25" spans="1:98" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="96" t="s">
+    <row r="25" spans="1:98" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="97"/>
+      <c r="B25" s="93"/>
       <c r="C25" s="34"/>
       <c r="D25" s="35"/>
       <c r="E25" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="61" t="s">
+        <v>6</v>
+      </c>
+      <c r="G25" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="F25" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" s="91" t="s">
+      <c r="H25" s="86"/>
+      <c r="I25" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="H25" s="92"/>
-      <c r="I25" s="91" t="s">
+      <c r="J25" s="86"/>
+      <c r="K25" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="92"/>
-      <c r="K25" s="91" t="s">
-        <v>20</v>
-      </c>
-      <c r="L25" s="92"/>
+      <c r="L25" s="86"/>
       <c r="M25" s="62"/>
       <c r="N25" s="59" t="s">
-        <v>111</v>
-      </c>
-      <c r="O25" s="91" t="s">
+        <v>82</v>
+      </c>
+      <c r="O25" s="85" t="s">
+        <v>17</v>
+      </c>
+      <c r="P25" s="86"/>
+      <c r="Q25" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="P25" s="92"/>
-      <c r="Q25" s="91" t="s">
+      <c r="R25" s="86"/>
+      <c r="S25" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="R25" s="92"/>
-      <c r="S25" s="91" t="s">
-        <v>20</v>
-      </c>
-      <c r="T25" s="92"/>
+      <c r="T25" s="86"/>
       <c r="V25" s="67" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>F_Rechts Mediale middenvoet</v>
       </c>
       <c r="W25" s="67" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="X25" s="67" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Y25" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>200</v>
       </c>
       <c r="Z25" s="7"/>
@@ -11625,34 +11192,34 @@
       <c r="CS25" s="7"/>
       <c r="CT25" s="7"/>
     </row>
-    <row r="26" spans="1:98" s="5" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="98"/>
-      <c r="B26" s="99"/>
+    <row r="26" spans="1:98" s="5" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="94"/>
+      <c r="B26" s="95"/>
       <c r="C26" s="34"/>
       <c r="D26" s="35"/>
       <c r="E26" s="36" t="s">
         <v>1</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="G26" s="36" t="s">
         <v>1</v>
       </c>
       <c r="H26" s="36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I26" s="36" t="s">
         <v>1</v>
       </c>
       <c r="J26" s="36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K26" s="36" t="s">
         <v>1</v>
       </c>
       <c r="L26" s="36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M26" s="62"/>
       <c r="N26" s="36" t="s">
@@ -11662,34 +11229,34 @@
         <v>1</v>
       </c>
       <c r="P26" s="36" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="Q26" s="36" t="s">
         <v>1</v>
       </c>
       <c r="R26" s="36" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="S26" s="36" t="s">
         <v>1</v>
       </c>
       <c r="T26" s="36" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="V26" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>G_Rechts Laterale middenvoet</v>
       </c>
       <c r="W26" s="7" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="X26" s="7" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Y26" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>200</v>
       </c>
       <c r="Z26" s="7"/>
@@ -11766,73 +11333,73 @@
       <c r="CS26" s="7"/>
       <c r="CT26" s="7"/>
     </row>
-    <row r="27" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="98"/>
-      <c r="B27" s="99"/>
+    <row r="27" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="94"/>
+      <c r="B27" s="95"/>
       <c r="C27" s="83" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="D27" s="37"/>
       <c r="E27" s="38" t="str">
-        <f t="shared" ref="E27:E34" si="17">IF(J47="","",J47)</f>
+        <f t="shared" ref="E27:E34" si="18">IF(J47="","",J47)</f>
         <v/>
       </c>
       <c r="F27" s="39" t="str">
-        <f>IF($C$36=C27,"TARGET",IF(E27="","",IF(AND(E27&gt;200,RANK(E27,$E$27:$E$33)&lt;=2),"TARGET","")))</f>
+        <f t="shared" ref="F27:F33" si="19">IF($C$36=C27,"TARGET",IF(E27="","",IF(AND(E27&gt;200,RANK(E27,$E$27:$E$33)&lt;=2),"TARGET","")))</f>
         <v/>
       </c>
       <c r="G27" s="40" t="str">
-        <f t="shared" ref="G27:G34" si="18">IF(J68="","",J68)</f>
+        <f t="shared" ref="G27:G34" si="20">IF(J68="","",J68)</f>
         <v/>
       </c>
       <c r="H27" s="43" t="str">
-        <f t="shared" ref="H27:H34" si="19">IF(OR($E27="",G27=""),"",((G27-$E27)/$E27)*100)</f>
+        <f t="shared" ref="H27:H34" si="21">IF(OR($E27="",G27=""),"",((G27-$E27)/$E27)*100)</f>
         <v/>
       </c>
       <c r="I27" s="40"/>
       <c r="J27" s="43" t="str">
-        <f t="shared" ref="J27:J34" si="20">IF(OR($E27="",I27=""),"",((I27-$E27)/$E27)*100)</f>
+        <f t="shared" ref="J27:J34" si="22">IF(OR($E27="",I27=""),"",((I27-$E27)/$E27)*100)</f>
         <v/>
       </c>
       <c r="K27" s="40"/>
       <c r="L27" s="43" t="str">
-        <f t="shared" ref="L27:L34" si="21">IF(OR($E27="",K27=""),"",((K27-$E27)/$E27)*100)</f>
+        <f t="shared" ref="L27:L34" si="23">IF(OR($E27="",K27=""),"",((K27-$E27)/$E27)*100)</f>
         <v/>
       </c>
       <c r="M27" s="33"/>
       <c r="N27" s="40" t="str">
-        <f t="shared" ref="N27:N34" si="22">IF(E27="","",E27)</f>
+        <f t="shared" ref="N27:N34" si="24">IF(E27="","",E27)</f>
         <v/>
       </c>
       <c r="O27" s="40"/>
       <c r="P27" s="43" t="str">
-        <f t="shared" ref="P27:P34" si="23">IF(OR($N27="",O27=""),"",((O27-$N27)/$N27)*100)</f>
+        <f t="shared" ref="P27:P34" si="25">IF(OR($N27="",O27=""),"",((O27-$N27)/$N27)*100)</f>
         <v/>
       </c>
       <c r="Q27" s="40"/>
       <c r="R27" s="43" t="str">
-        <f t="shared" ref="R27:R34" si="24">IF(OR($N27="",Q27=""),"",((Q27-$N27)/$N27)*100)</f>
+        <f t="shared" ref="R27:R34" si="26">IF(OR($N27="",Q27=""),"",((Q27-$N27)/$N27)*100)</f>
         <v/>
       </c>
       <c r="S27" s="40"/>
       <c r="T27" s="43" t="str">
-        <f t="shared" ref="T27:T34" si="25">IF(OR($N27="",S27=""),"",((S27-$N27)/$N27)*100)</f>
+        <f t="shared" ref="T27:T34" si="27">IF(OR($N27="",S27=""),"",((S27-$N27)/$N27)*100)</f>
         <v/>
       </c>
       <c r="V27" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>H_Rechts Hiel</v>
       </c>
       <c r="W27" s="7" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="X27" s="7" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Y27" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>200</v>
       </c>
       <c r="Z27" s="7"/>
@@ -11909,57 +11476,57 @@
       <c r="CS27" s="7"/>
       <c r="CT27" s="7"/>
     </row>
-    <row r="28" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="98"/>
-      <c r="B28" s="99"/>
+    <row r="28" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="94"/>
+      <c r="B28" s="95"/>
       <c r="C28" s="83" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="D28" s="37"/>
       <c r="E28" s="38" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="F28" s="39" t="str">
-        <f>IF($C$36=C28,"TARGET",IF(E28="","",IF(AND(E28&gt;200,RANK(E28,$E$27:$E$33)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="G28" s="40" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H28" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I28" s="40"/>
       <c r="J28" s="43" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="K28" s="40"/>
       <c r="L28" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M28" s="33"/>
       <c r="N28" s="40" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="O28" s="40"/>
       <c r="P28" s="43" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q28" s="40"/>
       <c r="R28" s="43" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="S28" s="40"/>
       <c r="T28" s="43" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="V28" s="7"/>
@@ -12040,57 +11607,57 @@
       <c r="CS28" s="7"/>
       <c r="CT28" s="7"/>
     </row>
-    <row r="29" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="98"/>
-      <c r="B29" s="99"/>
+    <row r="29" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="94"/>
+      <c r="B29" s="95"/>
       <c r="C29" s="83" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="D29" s="37"/>
       <c r="E29" s="38" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="F29" s="39" t="str">
-        <f>IF($C$36=C29,"TARGET",IF(E29="","",IF(AND(E29&gt;200,RANK(E29,$E$27:$E$33)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="G29" s="40" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H29" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I29" s="40"/>
       <c r="J29" s="43" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="K29" s="40"/>
       <c r="L29" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M29" s="33"/>
       <c r="N29" s="40" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="O29" s="40"/>
       <c r="P29" s="43" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q29" s="40"/>
       <c r="R29" s="43" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="S29" s="40"/>
       <c r="T29" s="43" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="V29" s="7"/>
@@ -12171,57 +11738,57 @@
       <c r="CS29" s="7"/>
       <c r="CT29" s="7"/>
     </row>
-    <row r="30" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="98"/>
-      <c r="B30" s="99"/>
+    <row r="30" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="94"/>
+      <c r="B30" s="95"/>
       <c r="C30" s="83" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="D30" s="37"/>
       <c r="E30" s="38" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="F30" s="39" t="str">
-        <f>IF($C$36=C30,"TARGET",IF(E30="","",IF(AND(E30&gt;200,RANK(E30,$E$27:$E$33)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="G30" s="40" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H30" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I30" s="40"/>
       <c r="J30" s="43" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="K30" s="40"/>
       <c r="L30" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M30" s="33"/>
       <c r="N30" s="40" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="O30" s="40"/>
       <c r="P30" s="43" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q30" s="40"/>
       <c r="R30" s="43" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="S30" s="40"/>
       <c r="T30" s="43" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="V30" s="7"/>
@@ -12302,57 +11869,57 @@
       <c r="CS30" s="7"/>
       <c r="CT30" s="7"/>
     </row>
-    <row r="31" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="98"/>
-      <c r="B31" s="99"/>
+    <row r="31" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="94"/>
+      <c r="B31" s="95"/>
       <c r="C31" s="83" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="D31" s="37"/>
       <c r="E31" s="38" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="F31" s="39" t="str">
-        <f>IF($C$36=C31,"TARGET",IF(E31="","",IF(AND(E31&gt;200,RANK(E31,$E$27:$E$33)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="G31" s="40" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H31" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I31" s="40"/>
       <c r="J31" s="43" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="K31" s="40"/>
       <c r="L31" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M31" s="33"/>
       <c r="N31" s="40" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="O31" s="40"/>
       <c r="P31" s="43" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q31" s="40"/>
       <c r="R31" s="43" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="S31" s="40"/>
       <c r="T31" s="43" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="V31" s="7"/>
@@ -12433,57 +12000,57 @@
       <c r="CS31" s="7"/>
       <c r="CT31" s="7"/>
     </row>
-    <row r="32" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="98"/>
-      <c r="B32" s="99"/>
+    <row r="32" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="94"/>
+      <c r="B32" s="95"/>
       <c r="C32" s="83" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="D32" s="37"/>
       <c r="E32" s="41" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="F32" s="39" t="str">
-        <f>IF($C$36=C32,"TARGET",IF(E32="","",IF(AND(E32&gt;200,RANK(E32,$E$27:$E$33)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="G32" s="40" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H32" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I32" s="40"/>
       <c r="J32" s="43" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="K32" s="40"/>
       <c r="L32" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M32" s="33"/>
       <c r="N32" s="40" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="O32" s="40"/>
       <c r="P32" s="43" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q32" s="40"/>
       <c r="R32" s="43" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="S32" s="40"/>
       <c r="T32" s="43" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="V32" s="7"/>
@@ -12564,57 +12131,57 @@
       <c r="CS32" s="7"/>
       <c r="CT32" s="7"/>
     </row>
-    <row r="33" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="98"/>
-      <c r="B33" s="99"/>
+    <row r="33" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="94"/>
+      <c r="B33" s="95"/>
       <c r="C33" s="83" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="D33" s="37"/>
       <c r="E33" s="41" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="F33" s="39" t="str">
-        <f>IF($C$36=C33,"TARGET",IF(E33="","",IF(AND(E33&gt;200,RANK(E33,$E$27:$E$33)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="G33" s="40" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H33" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I33" s="40"/>
       <c r="J33" s="43" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="K33" s="40"/>
       <c r="L33" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M33" s="33"/>
       <c r="N33" s="40" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="O33" s="40"/>
       <c r="P33" s="43" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q33" s="40"/>
       <c r="R33" s="43" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="S33" s="40"/>
       <c r="T33" s="43" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="V33" s="7"/>
@@ -12695,15 +12262,15 @@
       <c r="CS33" s="7"/>
       <c r="CT33" s="7"/>
     </row>
-    <row r="34" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="100"/>
-      <c r="B34" s="101"/>
+    <row r="34" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="96"/>
+      <c r="B34" s="97"/>
       <c r="C34" s="83" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="D34" s="37"/>
       <c r="E34" s="41" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="F34" s="39" t="str">
@@ -12711,41 +12278,41 @@
         <v/>
       </c>
       <c r="G34" s="40" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H34" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I34" s="40"/>
       <c r="J34" s="43" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="K34" s="40"/>
       <c r="L34" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M34" s="33"/>
       <c r="N34" s="40" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="O34" s="40"/>
       <c r="P34" s="43" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q34" s="40"/>
       <c r="R34" s="43" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="S34" s="40"/>
       <c r="T34" s="43" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="V34" s="7"/>
@@ -12826,7 +12393,7 @@
       <c r="CS34" s="7"/>
       <c r="CT34" s="7"/>
     </row>
-    <row r="35" spans="1:98" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:98" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="21"/>
       <c r="B35" s="21"/>
       <c r="C35" s="48"/>
@@ -12925,29 +12492,29 @@
       <c r="CS35" s="3"/>
       <c r="CT35" s="3"/>
     </row>
-    <row r="36" spans="1:98" s="5" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="102" t="s">
-        <v>115</v>
-      </c>
-      <c r="B36" s="103"/>
-      <c r="C36" s="104"/>
-      <c r="D36" s="105"/>
-      <c r="E36" s="105"/>
-      <c r="F36" s="105"/>
-      <c r="G36" s="105"/>
-      <c r="H36" s="105"/>
-      <c r="I36" s="105"/>
-      <c r="J36" s="105"/>
-      <c r="K36" s="105"/>
-      <c r="L36" s="105"/>
-      <c r="M36" s="105"/>
-      <c r="N36" s="105"/>
-      <c r="O36" s="105"/>
-      <c r="P36" s="105"/>
-      <c r="Q36" s="105"/>
-      <c r="R36" s="105"/>
-      <c r="S36" s="105"/>
-      <c r="T36" s="106"/>
+    <row r="36" spans="1:98" s="5" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="87" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="88"/>
+      <c r="C36" s="89"/>
+      <c r="D36" s="90"/>
+      <c r="E36" s="90"/>
+      <c r="F36" s="90"/>
+      <c r="G36" s="90"/>
+      <c r="H36" s="90"/>
+      <c r="I36" s="90"/>
+      <c r="J36" s="90"/>
+      <c r="K36" s="90"/>
+      <c r="L36" s="90"/>
+      <c r="M36" s="90"/>
+      <c r="N36" s="90"/>
+      <c r="O36" s="90"/>
+      <c r="P36" s="90"/>
+      <c r="Q36" s="90"/>
+      <c r="R36" s="90"/>
+      <c r="S36" s="90"/>
+      <c r="T36" s="91"/>
       <c r="V36" s="7"/>
       <c r="W36" s="7"/>
       <c r="X36" s="7"/>
@@ -13026,7 +12593,7 @@
       <c r="CS36" s="7"/>
       <c r="CT36" s="7"/>
     </row>
-    <row r="37" spans="1:98" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:98" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="19"/>
       <c r="B37" s="19"/>
       <c r="C37" s="28"/>
@@ -13125,12 +12692,12 @@
       <c r="CS37" s="7"/>
       <c r="CT37" s="7"/>
     </row>
-    <row r="39" spans="1:98" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:98" ht="16" x14ac:dyDescent="0.4">
       <c r="A39" s="45" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:98" x14ac:dyDescent="0.35">
       <c r="A40" s="53"/>
       <c r="B40" s="47"/>
       <c r="C40" s="47"/>
@@ -13152,9 +12719,9 @@
       <c r="S40" s="47"/>
       <c r="T40" s="47"/>
     </row>
-    <row r="41" spans="1:98" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:98" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="54" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="B41" s="50"/>
       <c r="C41" s="50"/>
@@ -13254,7 +12821,7 @@
       <c r="CS41" s="9"/>
       <c r="CT41" s="9"/>
     </row>
-    <row r="42" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:98" x14ac:dyDescent="0.35">
       <c r="A42" s="53"/>
       <c r="B42" s="47"/>
       <c r="C42" s="47"/>
@@ -13276,9 +12843,9 @@
       <c r="S42" s="47"/>
       <c r="T42" s="47"/>
     </row>
-    <row r="43" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:98" x14ac:dyDescent="0.35">
       <c r="A43" s="55" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="B43" s="50"/>
       <c r="C43" s="50"/>
@@ -13300,14 +12867,14 @@
       <c r="S43" s="47"/>
       <c r="T43" s="47"/>
     </row>
-    <row r="45" spans="1:98" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:98" ht="16" x14ac:dyDescent="0.4">
       <c r="A45" s="45" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="46" spans="1:98" ht="45" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="46" spans="1:98" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A46" s="44" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -13321,15 +12888,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:98" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:98" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -13337,15 +12902,13 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
     </row>
-    <row r="48" spans="1:98" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:98" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -13353,15 +12916,13 @@
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -13369,15 +12930,13 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -13385,15 +12944,13 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
     </row>
-    <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -13401,15 +12958,13 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
@@ -13417,15 +12972,13 @@
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
     </row>
-    <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -13433,15 +12986,13 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
     </row>
-    <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -13449,7 +13000,7 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -13459,7 +13010,7 @@
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -13469,14 +13020,12 @@
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
     </row>
-    <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B57" s="1"/>
       <c r="C57" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -13484,14 +13033,12 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
     </row>
-    <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B58" s="1"/>
       <c r="C58" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
@@ -13499,14 +13046,12 @@
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
     </row>
-    <row r="59" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B59" s="1"/>
       <c r="C59" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -13514,14 +13059,12 @@
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
     </row>
-    <row r="60" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B60" s="1"/>
       <c r="C60" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
@@ -13529,14 +13072,12 @@
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
     </row>
-    <row r="61" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B61" s="1"/>
       <c r="C61" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
@@ -13544,13 +13085,11 @@
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
     </row>
-    <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C62" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
@@ -13558,13 +13097,11 @@
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
     </row>
-    <row r="63" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C63" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
@@ -13572,13 +13109,11 @@
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
     </row>
-    <row r="64" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C64" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -13586,26 +13121,24 @@
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
     </row>
-    <row r="66" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" ht="16" x14ac:dyDescent="0.4">
       <c r="A66" s="45" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" s="44" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="J67" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C68" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
@@ -13613,13 +13146,11 @@
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
     </row>
-    <row r="69" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C69" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
@@ -13627,13 +13158,11 @@
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
     </row>
-    <row r="70" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C70" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
@@ -13641,13 +13170,11 @@
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
     </row>
-    <row r="71" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C71" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="D71" s="1"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
@@ -13655,13 +13182,11 @@
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
     </row>
-    <row r="72" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C72" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="D72" s="1"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
@@ -13669,13 +13194,11 @@
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
     </row>
-    <row r="73" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C73" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
@@ -13683,13 +13206,11 @@
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
     </row>
-    <row r="74" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C74" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
@@ -13697,13 +13218,11 @@
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
     </row>
-    <row r="75" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C75" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
@@ -13711,13 +13230,11 @@
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
     </row>
-    <row r="78" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C78" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
@@ -13725,13 +13242,11 @@
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
     </row>
-    <row r="79" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C79" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
@@ -13739,13 +13254,11 @@
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
     </row>
-    <row r="80" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C80" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
@@ -13753,13 +13266,11 @@
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
     </row>
-    <row r="81" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C81" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
@@ -13767,13 +13278,11 @@
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
     </row>
-    <row r="82" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C82" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
@@ -13781,13 +13290,11 @@
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
     </row>
-    <row r="83" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C83" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
@@ -13795,13 +13302,11 @@
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
     </row>
-    <row r="84" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C84" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
@@ -13809,13 +13314,11 @@
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
     </row>
-    <row r="85" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C85" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
@@ -13825,6 +13328,18 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="E3:L3"/>
+    <mergeCell ref="N8:T8"/>
+    <mergeCell ref="D8:L8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A9:B18"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="S9:T9"/>
     <mergeCell ref="S25:T25"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="C20:T20"/>
@@ -13838,26 +13353,14 @@
     <mergeCell ref="D24:L24"/>
     <mergeCell ref="N24:T24"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="E2:L2"/>
-    <mergeCell ref="E3:L3"/>
-    <mergeCell ref="N8:T8"/>
-    <mergeCell ref="D8:L8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="A9:B18"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="S9:T9"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="E11:E18">
-    <cfRule type="expression" dxfId="119" priority="8">
+    <cfRule type="expression" dxfId="119" priority="7">
+      <formula>AND(E11&lt;&gt;"",E11&gt;=200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="118" priority="8">
       <formula>AND(E11&lt;&gt;"",E11&lt;200)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="118" priority="7">
-      <formula>AND(E11&lt;&gt;"",E11&gt;=200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E27:E34">
@@ -13895,19 +13398,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:H18">
-    <cfRule type="expression" dxfId="109" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="109" priority="43" stopIfTrue="1">
+      <formula>AND(H11&lt;&gt;"",OR(G11&lt;200,H11&lt;=-25))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="108" priority="44" stopIfTrue="1">
       <formula>AND(H11&lt;&gt;"",G11&gt;=200,H11&gt;-25)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="108" priority="43" stopIfTrue="1">
-      <formula>AND(H11&lt;&gt;"",OR(G11&lt;200,H11&lt;=-25))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H34">
-    <cfRule type="expression" dxfId="107" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="45" stopIfTrue="1">
+      <formula>AND(H27&lt;&gt;"",OR(G27&lt;200,H27&lt;=-25))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="106" priority="46" stopIfTrue="1">
       <formula>AND(H27&lt;&gt;"",G27&gt;=200,H27&gt;-25)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="106" priority="45" stopIfTrue="1">
-      <formula>AND(H27&lt;&gt;"",OR(G27&lt;200,H27&lt;=-25))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I11:I18">
@@ -13927,19 +13430,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J18">
-    <cfRule type="expression" dxfId="101" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="47" stopIfTrue="1">
+      <formula>AND(J11&lt;&gt;"",OR(I11&lt;200,J11&lt;=-25))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="100" priority="48" stopIfTrue="1">
       <formula>AND(J11&lt;&gt;"",I11&gt;=200,J11&gt;-25)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="100" priority="47" stopIfTrue="1">
-      <formula>AND(J11&lt;&gt;"",OR(I11&lt;200,J11&lt;=-25))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J27:J34">
-    <cfRule type="expression" dxfId="99" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="49" stopIfTrue="1">
+      <formula>AND(J27&lt;&gt;"",OR(I27&lt;200,J27&lt;=-25))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="50" stopIfTrue="1">
       <formula>AND(J27&lt;&gt;"",I27&gt;=200,J27&gt;-25)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="98" priority="49" stopIfTrue="1">
-      <formula>AND(J27&lt;&gt;"",OR(I27&lt;200,J27&lt;=-25))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:K18">
@@ -13951,19 +13454,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K34">
-    <cfRule type="expression" dxfId="95" priority="32">
+    <cfRule type="expression" dxfId="95" priority="31">
+      <formula>AND(K27&lt;&gt;"",K27&gt;=200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="94" priority="32">
       <formula>AND(K27&lt;&gt;"",K27&lt;200)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="94" priority="31">
-      <formula>AND(K27&lt;&gt;"",K27&gt;=200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L11:L18">
-    <cfRule type="expression" dxfId="93" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="51" stopIfTrue="1">
+      <formula>AND(L11&lt;&gt;"",OR(K11&lt;200,L11&lt;=-25))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="92" priority="52" stopIfTrue="1">
       <formula>AND(L11&lt;&gt;"",K11&gt;=200,L11&gt;-25)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="92" priority="51" stopIfTrue="1">
-      <formula>AND(L11&lt;&gt;"",OR(K11&lt;200,L11&lt;=-25))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L27:L34">
@@ -13975,25 +13478,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O11:O18">
-    <cfRule type="expression" dxfId="89" priority="15">
+    <cfRule type="expression" dxfId="89" priority="6" stopIfTrue="1">
+      <formula>AND(O11&lt;&gt;"",O11&gt;=1.05*IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="88" priority="15">
       <formula>AND(O11&lt;&gt;"",O11&gt;=200)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="88" priority="6" stopIfTrue="1">
-      <formula>AND(O11&lt;&gt;"",O11&gt;=1.05*IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11)))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="87" priority="16">
       <formula>AND(O11&lt;&gt;"",O11&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O27:O34">
-    <cfRule type="expression" dxfId="86" priority="33">
+    <cfRule type="expression" dxfId="86" priority="3" stopIfTrue="1">
+      <formula>AND(O27&lt;&gt;"",O27&gt;=1.05*IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="85" priority="33">
       <formula>AND(O27&lt;&gt;"",O27&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="34">
+    <cfRule type="expression" dxfId="84" priority="34">
       <formula>AND(O27&lt;&gt;"",O27&lt;200)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="84" priority="3" stopIfTrue="1">
-      <formula>AND(O27&lt;&gt;"",O27&gt;=1.05*IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P11:P18">
@@ -14013,14 +13516,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q11:Q18">
-    <cfRule type="expression" dxfId="79" priority="18">
-      <formula>AND(Q11&lt;&gt;"",Q11&lt;200)</formula>
+    <cfRule type="expression" dxfId="79" priority="5" stopIfTrue="1">
+      <formula>AND(Q11&lt;&gt;"",Q11&gt;=1.05*IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11)))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="78" priority="17">
       <formula>AND(Q11&lt;&gt;"",Q11&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="5" stopIfTrue="1">
-      <formula>AND(Q11&lt;&gt;"",Q11&gt;=1.05*IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11)))</formula>
+    <cfRule type="expression" dxfId="77" priority="18">
+      <formula>AND(Q11&lt;&gt;"",Q11&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q27:Q34">
@@ -14051,25 +13554,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S11:S18">
-    <cfRule type="expression" dxfId="69" priority="20">
-      <formula>AND(S11&lt;&gt;"",S11&lt;200)</formula>
+    <cfRule type="expression" dxfId="69" priority="4" stopIfTrue="1">
+      <formula>AND(S11&lt;&gt;"",S11&gt;=1.05*IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11)))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="68" priority="19">
       <formula>AND(S11&lt;&gt;"",S11&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="4" stopIfTrue="1">
-      <formula>AND(S11&lt;&gt;"",S11&gt;=1.05*IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11)))</formula>
+    <cfRule type="expression" dxfId="67" priority="20">
+      <formula>AND(S11&lt;&gt;"",S11&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S27:S34">
-    <cfRule type="expression" dxfId="66" priority="37">
+    <cfRule type="expression" dxfId="66" priority="1" stopIfTrue="1">
+      <formula>AND(S27&lt;&gt;"",S27&gt;=1.05*IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="37">
       <formula>AND(S27&lt;&gt;"",S27&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="38">
+    <cfRule type="expression" dxfId="64" priority="38">
       <formula>AND(S27&lt;&gt;"",S27&lt;200)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="64" priority="1" stopIfTrue="1">
-      <formula>AND(S27&lt;&gt;"",S27&gt;=1.05*IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T11:T18">
@@ -14110,26 +13613,26 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:CT85"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="6" width="12.140625" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" customWidth="1"/>
-    <col min="9" max="11" width="12.140625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.7265625" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" customWidth="1"/>
+    <col min="3" max="3" width="23.81640625" customWidth="1"/>
+    <col min="4" max="4" width="10.7265625" customWidth="1"/>
+    <col min="5" max="6" width="12.1796875" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" customWidth="1"/>
+    <col min="9" max="11" width="12.1796875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="12.1796875" customWidth="1"/>
     <col min="13" max="13" width="3" customWidth="1"/>
-    <col min="14" max="20" width="12.140625" customWidth="1"/>
-    <col min="21" max="21" width="8.85546875" style="7"/>
+    <col min="14" max="20" width="12.1796875" customWidth="1"/>
+    <col min="21" max="21" width="8.81640625" style="7"/>
     <col min="22" max="22" width="21" style="7" customWidth="1"/>
-    <col min="23" max="25" width="13.28515625" style="7" customWidth="1"/>
-    <col min="26" max="98" width="8.85546875" style="7"/>
+    <col min="23" max="25" width="13.26953125" style="7" customWidth="1"/>
+    <col min="26" max="98" width="8.81640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:98" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:98" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="14"/>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -14151,21 +13654,21 @@
       <c r="S1" s="14"/>
       <c r="T1" s="14"/>
     </row>
-    <row r="2" spans="1:98" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:98" ht="34" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
-      <c r="E2" s="85" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="86"/>
-      <c r="L2" s="86"/>
+      <c r="E2" s="101" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="102"/>
+      <c r="L2" s="102"/>
       <c r="M2" s="13"/>
       <c r="N2" s="13"/>
       <c r="O2" s="13"/>
@@ -14175,21 +13678,21 @@
       <c r="S2" s="13"/>
       <c r="T2" s="13"/>
     </row>
-    <row r="3" spans="1:98" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:98" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
-      <c r="E3" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
+      <c r="E3" s="103" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
       <c r="M3" s="13"/>
       <c r="N3" s="13"/>
       <c r="O3" s="13"/>
@@ -14199,7 +13702,7 @@
       <c r="S3" s="13"/>
       <c r="T3" s="13"/>
     </row>
-    <row r="4" spans="1:98" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:98" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="14"/>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -14221,25 +13724,25 @@
       <c r="S4" s="14"/>
       <c r="T4" s="14"/>
       <c r="V4" s="69" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:98" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:98" x14ac:dyDescent="0.35">
       <c r="U5" s="5"/>
       <c r="X5" s="57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y5" s="56">
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:98" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:98" ht="16" x14ac:dyDescent="0.35">
       <c r="A6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="93"/>
-      <c r="C6" s="94"/>
-      <c r="D6" s="95"/>
+      <c r="B6" s="104"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="106"/>
       <c r="E6" s="64"/>
       <c r="F6" s="64"/>
       <c r="G6" s="58" t="s">
@@ -14260,13 +13763,13 @@
       <c r="T6" s="66"/>
       <c r="U6" s="5"/>
       <c r="V6" s="68" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6" s="67"/>
       <c r="X6" s="67"/>
       <c r="Y6" s="67"/>
     </row>
-    <row r="7" spans="1:98" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:98" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="16"/>
       <c r="E7" s="15"/>
       <c r="F7" s="15"/>
@@ -14274,43 +13777,43 @@
       <c r="H7" s="18"/>
       <c r="U7" s="5"/>
       <c r="V7" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="W7" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="X7" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="W7" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="X7" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y7" s="68" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:98" s="5" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:98" s="5" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8"/>
       <c r="B8"/>
       <c r="C8"/>
-      <c r="D8" s="88" t="s">
-        <v>109</v>
-      </c>
-      <c r="E8" s="89"/>
-      <c r="F8" s="89"/>
-      <c r="G8" s="89"/>
-      <c r="H8" s="89"/>
-      <c r="I8" s="89"/>
-      <c r="J8" s="89"/>
-      <c r="K8" s="89"/>
-      <c r="L8" s="90"/>
+      <c r="D8" s="98" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="99"/>
+      <c r="K8" s="99"/>
+      <c r="L8" s="100"/>
       <c r="M8"/>
-      <c r="N8" s="88" t="s">
-        <v>110</v>
-      </c>
-      <c r="O8" s="89"/>
-      <c r="P8" s="89"/>
-      <c r="Q8" s="89"/>
-      <c r="R8" s="89"/>
-      <c r="S8" s="89"/>
-      <c r="T8" s="90"/>
+      <c r="N8" s="98" t="s">
+        <v>81</v>
+      </c>
+      <c r="O8" s="99"/>
+      <c r="P8" s="99"/>
+      <c r="Q8" s="99"/>
+      <c r="R8" s="99"/>
+      <c r="S8" s="99"/>
+      <c r="T8" s="100"/>
       <c r="V8" s="67" t="str">
         <f t="shared" ref="V8:V15" si="0">C11</f>
         <v>I_Links Hallux</v>
@@ -14401,47 +13904,47 @@
       <c r="CS8" s="7"/>
       <c r="CT8" s="7"/>
     </row>
-    <row r="9" spans="1:98" s="5" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A9" s="96" t="s">
+    <row r="9" spans="1:98" s="5" customFormat="1" ht="36" x14ac:dyDescent="0.35">
+      <c r="A9" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="97"/>
+      <c r="B9" s="93"/>
       <c r="C9" s="34"/>
       <c r="D9" s="35"/>
       <c r="E9" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="61" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" s="91" t="s">
+      <c r="H9" s="86"/>
+      <c r="I9" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="92"/>
-      <c r="I9" s="91" t="s">
+      <c r="J9" s="86"/>
+      <c r="K9" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="92"/>
-      <c r="K9" s="91" t="s">
-        <v>20</v>
-      </c>
-      <c r="L9" s="92"/>
+      <c r="L9" s="86"/>
       <c r="M9" s="62"/>
       <c r="N9" s="59" t="s">
-        <v>111</v>
-      </c>
-      <c r="O9" s="91" t="s">
+        <v>82</v>
+      </c>
+      <c r="O9" s="85" t="s">
+        <v>17</v>
+      </c>
+      <c r="P9" s="86"/>
+      <c r="Q9" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="P9" s="92"/>
-      <c r="Q9" s="91" t="s">
+      <c r="R9" s="86"/>
+      <c r="S9" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="R9" s="92"/>
-      <c r="S9" s="91" t="s">
-        <v>20</v>
-      </c>
-      <c r="T9" s="92"/>
+      <c r="T9" s="86"/>
       <c r="V9" s="67" t="str">
         <f t="shared" si="0"/>
         <v>J_Links Tenen 2-5</v>
@@ -14532,34 +14035,34 @@
       <c r="CS9" s="7"/>
       <c r="CT9" s="7"/>
     </row>
-    <row r="10" spans="1:98" s="5" customFormat="1" ht="72" x14ac:dyDescent="0.25">
-      <c r="A10" s="98"/>
-      <c r="B10" s="99"/>
+    <row r="10" spans="1:98" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.35">
+      <c r="A10" s="94"/>
+      <c r="B10" s="95"/>
       <c r="C10" s="34"/>
       <c r="D10" s="35"/>
       <c r="E10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="G10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="H10" s="36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="J10" s="36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="L10" s="36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M10" s="62"/>
       <c r="N10" s="36" t="s">
@@ -14569,19 +14072,19 @@
         <v>1</v>
       </c>
       <c r="P10" s="36" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="Q10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="R10" s="36" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="S10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="T10" s="36" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="V10" s="67" t="str">
         <f t="shared" si="0"/>
@@ -14673,11 +14176,11 @@
       <c r="CS10" s="7"/>
       <c r="CT10" s="7"/>
     </row>
-    <row r="11" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="98"/>
-      <c r="B11" s="99"/>
+    <row r="11" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="94"/>
+      <c r="B11" s="95"/>
       <c r="C11" s="83" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="D11" s="37"/>
       <c r="E11" s="38" t="str">
@@ -14685,45 +14188,45 @@
         <v/>
       </c>
       <c r="F11" s="39" t="str">
-        <f>IF($C$20=C11,"TARGET",IF(E11="","",IF(AND(E11&gt;200,RANK(E11,$E$11:$E$17)&lt;=2),"TARGET","")))</f>
+        <f t="shared" ref="F11:F17" si="5">IF($C$20=C11,"TARGET",IF(E11="","",IF(AND(E11&gt;200,RANK(E11,$E$11:$E$17)&lt;=2),"TARGET","")))</f>
         <v/>
       </c>
       <c r="G11" s="40" t="str">
-        <f t="shared" ref="G11:G18" si="5">IF(J78="","",J78)</f>
+        <f t="shared" ref="G11:G18" si="6">IF(J78="","",J78)</f>
         <v/>
       </c>
       <c r="H11" s="43" t="str">
-        <f t="shared" ref="H11:H18" si="6">IF(OR($E11="",G11=""),"",((G11-$E11)/$E11)*100)</f>
+        <f t="shared" ref="H11:H18" si="7">IF(OR($E11="",G11=""),"",((G11-$E11)/$E11)*100)</f>
         <v/>
       </c>
       <c r="I11" s="40"/>
       <c r="J11" s="43" t="str">
-        <f t="shared" ref="J11:J18" si="7">IF(OR($E11="",I11=""),"",((I11-$E11)/$E11)*100)</f>
+        <f t="shared" ref="J11:J18" si="8">IF(OR($E11="",I11=""),"",((I11-$E11)/$E11)*100)</f>
         <v/>
       </c>
       <c r="K11" s="40"/>
       <c r="L11" s="43" t="str">
-        <f t="shared" ref="L11:L18" si="8">IF(OR($E11="",K11=""),"",((K11-$E11)/$E11)*100)</f>
+        <f t="shared" ref="L11:L18" si="9">IF(OR($E11="",K11=""),"",((K11-$E11)/$E11)*100)</f>
         <v/>
       </c>
       <c r="M11" s="33"/>
       <c r="N11" s="40" t="str">
-        <f t="shared" ref="N11:N18" si="9">IF(E11="","",E11)</f>
+        <f t="shared" ref="N11:N18" si="10">IF(E11="","",E11)</f>
         <v/>
       </c>
       <c r="O11" s="40"/>
       <c r="P11" s="43" t="str">
-        <f t="shared" ref="P11:P18" si="10">IF(OR($N11="",O11=""),"",((O11-$N11)/$N11)*100)</f>
+        <f t="shared" ref="P11:P18" si="11">IF(OR($N11="",O11=""),"",((O11-$N11)/$N11)*100)</f>
         <v/>
       </c>
       <c r="Q11" s="40"/>
       <c r="R11" s="43" t="str">
-        <f t="shared" ref="R11:R18" si="11">IF(OR($N11="",Q11=""),"",((Q11-$N11)/$N11)*100)</f>
+        <f t="shared" ref="R11:R18" si="12">IF(OR($N11="",Q11=""),"",((Q11-$N11)/$N11)*100)</f>
         <v/>
       </c>
       <c r="S11" s="40"/>
       <c r="T11" s="43" t="str">
-        <f t="shared" ref="T11:T18" si="12">IF(OR($N11="",S11=""),"",((S11-$N11)/$N11)*100)</f>
+        <f t="shared" ref="T11:T18" si="13">IF(OR($N11="",S11=""),"",((S11-$N11)/$N11)*100)</f>
         <v/>
       </c>
       <c r="V11" s="67" t="str">
@@ -14816,11 +14319,11 @@
       <c r="CS11" s="7"/>
       <c r="CT11" s="7"/>
     </row>
-    <row r="12" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="98"/>
-      <c r="B12" s="99"/>
+    <row r="12" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
       <c r="C12" s="83" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="D12" s="37"/>
       <c r="E12" s="38" t="str">
@@ -14828,45 +14331,45 @@
         <v/>
       </c>
       <c r="F12" s="39" t="str">
-        <f>IF($C$20=C12,"TARGET",IF(E12="","",IF(AND(E12&gt;200,RANK(E12,$E$11:$E$17)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G12" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H12" s="43" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="I12" s="40"/>
       <c r="J12" s="43" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K12" s="40"/>
       <c r="L12" s="43" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="M12" s="33"/>
       <c r="N12" s="40" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="O12" s="40"/>
       <c r="P12" s="43" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="Q12" s="40"/>
       <c r="R12" s="43" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S12" s="40"/>
       <c r="T12" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="V12" s="67" t="str">
@@ -14959,11 +14462,11 @@
       <c r="CS12" s="7"/>
       <c r="CT12" s="7"/>
     </row>
-    <row r="13" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="98"/>
-      <c r="B13" s="99"/>
+    <row r="13" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
       <c r="C13" s="83" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="38" t="str">
@@ -14971,45 +14474,45 @@
         <v/>
       </c>
       <c r="F13" s="39" t="str">
-        <f>IF($C$20=C13,"TARGET",IF(E13="","",IF(AND(E13&gt;200,RANK(E13,$E$11:$E$17)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G13" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H13" s="43" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="I13" s="40"/>
       <c r="J13" s="43" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K13" s="40"/>
       <c r="L13" s="43" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="M13" s="33"/>
       <c r="N13" s="40" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="O13" s="40"/>
       <c r="P13" s="43" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="Q13" s="40"/>
       <c r="R13" s="43" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S13" s="40"/>
       <c r="T13" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="V13" s="67" t="str">
@@ -15102,11 +14605,11 @@
       <c r="CS13" s="7"/>
       <c r="CT13" s="7"/>
     </row>
-    <row r="14" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="98"/>
-      <c r="B14" s="99"/>
+    <row r="14" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
       <c r="C14" s="83" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="38" t="str">
@@ -15114,45 +14617,45 @@
         <v/>
       </c>
       <c r="F14" s="39" t="str">
-        <f>IF($C$20=C14,"TARGET",IF(E14="","",IF(AND(E14&gt;200,RANK(E14,$E$11:$E$17)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G14" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H14" s="43" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="I14" s="40"/>
       <c r="J14" s="43" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K14" s="40"/>
       <c r="L14" s="43" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="M14" s="33"/>
       <c r="N14" s="40" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="O14" s="40"/>
       <c r="P14" s="43" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="Q14" s="40"/>
       <c r="R14" s="43" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S14" s="40"/>
       <c r="T14" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="V14" s="67" t="str">
@@ -15245,11 +14748,11 @@
       <c r="CS14" s="7"/>
       <c r="CT14" s="7"/>
     </row>
-    <row r="15" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="98"/>
-      <c r="B15" s="99"/>
+    <row r="15" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
       <c r="C15" s="83" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="38" t="str">
@@ -15257,45 +14760,45 @@
         <v/>
       </c>
       <c r="F15" s="39" t="str">
-        <f>IF($C$20=C15,"TARGET",IF(E15="","",IF(AND(E15&gt;200,RANK(E15,$E$11:$E$17)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G15" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H15" s="43" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="I15" s="40"/>
       <c r="J15" s="43" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K15" s="40"/>
       <c r="L15" s="43" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="M15" s="33"/>
       <c r="N15" s="40" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="O15" s="40"/>
       <c r="P15" s="43" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="Q15" s="40"/>
       <c r="R15" s="43" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S15" s="40"/>
       <c r="T15" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="V15" s="67" t="str">
@@ -15388,11 +14891,11 @@
       <c r="CS15" s="7"/>
       <c r="CT15" s="7"/>
     </row>
-    <row r="16" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="98"/>
-      <c r="B16" s="99"/>
+    <row r="16" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
       <c r="C16" s="83" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="41" t="str">
@@ -15400,45 +14903,45 @@
         <v/>
       </c>
       <c r="F16" s="39" t="str">
-        <f>IF($C$20=C16,"TARGET",IF(E16="","",IF(AND(E16&gt;200,RANK(E16,$E$11:$E$17)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G16" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H16" s="43" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="I16" s="40"/>
       <c r="J16" s="43" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K16" s="40"/>
       <c r="L16" s="43" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="M16" s="33"/>
       <c r="N16" s="40" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="O16" s="40"/>
       <c r="P16" s="43" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="Q16" s="40"/>
       <c r="R16" s="43" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S16" s="40"/>
       <c r="T16" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="V16" s="67"/>
@@ -15519,11 +15022,11 @@
       <c r="CS16" s="7"/>
       <c r="CT16" s="7"/>
     </row>
-    <row r="17" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="98"/>
-      <c r="B17" s="99"/>
+    <row r="17" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
       <c r="C17" s="83" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="41" t="str">
@@ -15531,45 +15034,45 @@
         <v/>
       </c>
       <c r="F17" s="39" t="str">
-        <f>IF($C$20=C17,"TARGET",IF(E17="","",IF(AND(E17&gt;200,RANK(E17,$E$11:$E$17)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G17" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H17" s="43" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="I17" s="40"/>
       <c r="J17" s="43" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K17" s="40"/>
       <c r="L17" s="43" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="M17" s="33"/>
       <c r="N17" s="40" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="O17" s="40"/>
       <c r="P17" s="43" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="Q17" s="40"/>
       <c r="R17" s="43" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S17" s="40"/>
       <c r="T17" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="V17" s="67"/>
@@ -15650,11 +15153,11 @@
       <c r="CS17" s="7"/>
       <c r="CT17" s="7"/>
     </row>
-    <row r="18" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="100"/>
-      <c r="B18" s="101"/>
+    <row r="18" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="96"/>
+      <c r="B18" s="97"/>
       <c r="C18" s="83" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="D18" s="37"/>
       <c r="E18" s="41" t="str">
@@ -15666,45 +15169,45 @@
         <v/>
       </c>
       <c r="G18" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H18" s="43" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="I18" s="40"/>
       <c r="J18" s="43" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K18" s="40"/>
       <c r="L18" s="43" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="M18" s="33"/>
       <c r="N18" s="40" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="O18" s="40"/>
       <c r="P18" s="43" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="Q18" s="40"/>
       <c r="R18" s="43" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S18" s="40"/>
       <c r="T18" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="V18" s="68" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W18" s="67"/>
       <c r="X18" s="67"/>
@@ -15783,7 +15286,7 @@
       <c r="CS18" s="7"/>
       <c r="CT18" s="7"/>
     </row>
-    <row r="19" spans="1:98" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:98" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="21"/>
       <c r="B19" s="21"/>
       <c r="C19" s="48"/>
@@ -15805,16 +15308,16 @@
       <c r="S19" s="27"/>
       <c r="T19" s="42"/>
       <c r="V19" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="W19" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="X19" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y19" s="68" t="s">
         <v>11</v>
-      </c>
-      <c r="W19" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="X19" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y19" s="68" t="s">
-        <v>12</v>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
@@ -15890,43 +15393,43 @@
       <c r="CS19" s="3"/>
       <c r="CT19" s="3"/>
     </row>
-    <row r="20" spans="1:98" s="5" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="102" t="s">
-        <v>114</v>
-      </c>
-      <c r="B20" s="103"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="105"/>
-      <c r="E20" s="105"/>
-      <c r="F20" s="105"/>
-      <c r="G20" s="105"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="105"/>
-      <c r="J20" s="105"/>
-      <c r="K20" s="105"/>
-      <c r="L20" s="105"/>
-      <c r="M20" s="105"/>
-      <c r="N20" s="105"/>
-      <c r="O20" s="105"/>
-      <c r="P20" s="105"/>
-      <c r="Q20" s="105"/>
-      <c r="R20" s="105"/>
-      <c r="S20" s="105"/>
-      <c r="T20" s="105"/>
+    <row r="20" spans="1:98" s="5" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="87" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="88"/>
+      <c r="C20" s="89"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="90"/>
+      <c r="K20" s="90"/>
+      <c r="L20" s="90"/>
+      <c r="M20" s="90"/>
+      <c r="N20" s="90"/>
+      <c r="O20" s="90"/>
+      <c r="P20" s="90"/>
+      <c r="Q20" s="90"/>
+      <c r="R20" s="90"/>
+      <c r="S20" s="90"/>
+      <c r="T20" s="90"/>
       <c r="V20" s="67" t="str">
-        <f t="shared" ref="V20:V27" si="13">C27</f>
+        <f t="shared" ref="V20:V27" si="14">C27</f>
         <v>A_Rechts Hallux</v>
       </c>
       <c r="W20" s="67" t="str">
-        <f t="shared" ref="W20:W27" si="14">E27</f>
+        <f t="shared" ref="W20:W27" si="15">E27</f>
         <v/>
       </c>
       <c r="X20" s="67" t="str">
-        <f t="shared" ref="X20:X27" si="15">G27</f>
+        <f t="shared" ref="X20:X27" si="16">G27</f>
         <v/>
       </c>
       <c r="Y20" s="67">
-        <f t="shared" ref="Y20:Y27" si="16">$Y$5</f>
+        <f t="shared" ref="Y20:Y27" si="17">$Y$5</f>
         <v>200</v>
       </c>
       <c r="Z20" s="7"/>
@@ -16003,7 +15506,7 @@
       <c r="CS20" s="7"/>
       <c r="CT20" s="7"/>
     </row>
-    <row r="21" spans="1:98" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:98" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="19"/>
       <c r="B21" s="19"/>
       <c r="C21" s="28"/>
@@ -16025,19 +15528,19 @@
       <c r="S21" s="30"/>
       <c r="T21" s="32"/>
       <c r="V21" s="67" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>B_Rechts Tenen 2-5</v>
       </c>
       <c r="W21" s="67" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="X21" s="67" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Y21" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>200</v>
       </c>
       <c r="Z21" s="7"/>
@@ -16114,7 +15617,7 @@
       <c r="CS21" s="7"/>
       <c r="CT21" s="7"/>
     </row>
-    <row r="22" spans="1:98" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:98" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22"/>
@@ -16136,19 +15639,19 @@
       <c r="S22"/>
       <c r="T22"/>
       <c r="V22" s="67" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>C_Rechts Metatarsaal 1</v>
       </c>
       <c r="W22" s="67" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="X22" s="67" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Y22" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>200</v>
       </c>
       <c r="Z22" s="7"/>
@@ -16225,7 +15728,7 @@
       <c r="CS22" s="7"/>
       <c r="CT22" s="7"/>
     </row>
-    <row r="23" spans="1:98" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:98" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23"/>
       <c r="B23"/>
       <c r="C23"/>
@@ -16247,19 +15750,19 @@
       <c r="S23"/>
       <c r="T23"/>
       <c r="V23" s="67" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>D_Rechts Metatarsaal 2-3</v>
       </c>
       <c r="W23" s="67" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="X23" s="67" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Y23" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>200</v>
       </c>
       <c r="Z23" s="7"/>
@@ -16336,45 +15839,45 @@
       <c r="CS23" s="7"/>
       <c r="CT23" s="7"/>
     </row>
-    <row r="24" spans="1:98" s="5" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:98" s="5" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24"/>
       <c r="B24"/>
       <c r="C24"/>
-      <c r="D24" s="88" t="s">
-        <v>109</v>
-      </c>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="89"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="89"/>
-      <c r="K24" s="89"/>
-      <c r="L24" s="90"/>
+      <c r="D24" s="98" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="99"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="99"/>
+      <c r="H24" s="99"/>
+      <c r="I24" s="99"/>
+      <c r="J24" s="99"/>
+      <c r="K24" s="99"/>
+      <c r="L24" s="100"/>
       <c r="M24"/>
-      <c r="N24" s="88" t="s">
-        <v>110</v>
-      </c>
-      <c r="O24" s="89"/>
-      <c r="P24" s="89"/>
-      <c r="Q24" s="89"/>
-      <c r="R24" s="89"/>
-      <c r="S24" s="89"/>
-      <c r="T24" s="90"/>
+      <c r="N24" s="98" t="s">
+        <v>81</v>
+      </c>
+      <c r="O24" s="99"/>
+      <c r="P24" s="99"/>
+      <c r="Q24" s="99"/>
+      <c r="R24" s="99"/>
+      <c r="S24" s="99"/>
+      <c r="T24" s="100"/>
       <c r="V24" s="67" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>E_Rechts Metatarsaal 4-5</v>
       </c>
       <c r="W24" s="67" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="X24" s="67" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Y24" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>200</v>
       </c>
       <c r="Z24" s="7"/>
@@ -16451,61 +15954,61 @@
       <c r="CS24" s="7"/>
       <c r="CT24" s="7"/>
     </row>
-    <row r="25" spans="1:98" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="96" t="s">
+    <row r="25" spans="1:98" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="97"/>
+      <c r="B25" s="93"/>
       <c r="C25" s="34"/>
       <c r="D25" s="35"/>
       <c r="E25" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="61" t="s">
+        <v>6</v>
+      </c>
+      <c r="G25" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="F25" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" s="91" t="s">
+      <c r="H25" s="86"/>
+      <c r="I25" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="H25" s="92"/>
-      <c r="I25" s="91" t="s">
+      <c r="J25" s="86"/>
+      <c r="K25" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="92"/>
-      <c r="K25" s="91" t="s">
-        <v>20</v>
-      </c>
-      <c r="L25" s="92"/>
+      <c r="L25" s="86"/>
       <c r="M25" s="62"/>
       <c r="N25" s="59" t="s">
-        <v>111</v>
-      </c>
-      <c r="O25" s="91" t="s">
+        <v>82</v>
+      </c>
+      <c r="O25" s="85" t="s">
+        <v>17</v>
+      </c>
+      <c r="P25" s="86"/>
+      <c r="Q25" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="P25" s="92"/>
-      <c r="Q25" s="91" t="s">
+      <c r="R25" s="86"/>
+      <c r="S25" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="R25" s="92"/>
-      <c r="S25" s="91" t="s">
-        <v>20</v>
-      </c>
-      <c r="T25" s="92"/>
+      <c r="T25" s="86"/>
       <c r="V25" s="67" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>F_Rechts Mediale middenvoet</v>
       </c>
       <c r="W25" s="67" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="X25" s="67" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Y25" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>200</v>
       </c>
       <c r="Z25" s="7"/>
@@ -16582,34 +16085,34 @@
       <c r="CS25" s="7"/>
       <c r="CT25" s="7"/>
     </row>
-    <row r="26" spans="1:98" s="5" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="98"/>
-      <c r="B26" s="99"/>
+    <row r="26" spans="1:98" s="5" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="94"/>
+      <c r="B26" s="95"/>
       <c r="C26" s="34"/>
       <c r="D26" s="35"/>
       <c r="E26" s="36" t="s">
         <v>1</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="G26" s="36" t="s">
         <v>1</v>
       </c>
       <c r="H26" s="36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I26" s="36" t="s">
         <v>1</v>
       </c>
       <c r="J26" s="36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K26" s="36" t="s">
         <v>1</v>
       </c>
       <c r="L26" s="36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M26" s="62"/>
       <c r="N26" s="36" t="s">
@@ -16619,34 +16122,34 @@
         <v>1</v>
       </c>
       <c r="P26" s="36" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="Q26" s="36" t="s">
         <v>1</v>
       </c>
       <c r="R26" s="36" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="S26" s="36" t="s">
         <v>1</v>
       </c>
       <c r="T26" s="36" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="V26" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>G_Rechts Laterale middenvoet</v>
       </c>
       <c r="W26" s="7" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="X26" s="7" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Y26" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>200</v>
       </c>
       <c r="Z26" s="7"/>
@@ -16723,73 +16226,73 @@
       <c r="CS26" s="7"/>
       <c r="CT26" s="7"/>
     </row>
-    <row r="27" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="98"/>
-      <c r="B27" s="99"/>
+    <row r="27" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="94"/>
+      <c r="B27" s="95"/>
       <c r="C27" s="83" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="D27" s="37"/>
       <c r="E27" s="38" t="str">
-        <f t="shared" ref="E27:E34" si="17">IF(J47="","",J47)</f>
+        <f t="shared" ref="E27:E34" si="18">IF(J47="","",J47)</f>
         <v/>
       </c>
       <c r="F27" s="39" t="str">
-        <f>IF($C$36=C27,"TARGET",IF(E27="","",IF(AND(E27&gt;200,RANK(E27,$E$27:$E$33)&lt;=2),"TARGET","")))</f>
+        <f t="shared" ref="F27:F33" si="19">IF($C$36=C27,"TARGET",IF(E27="","",IF(AND(E27&gt;200,RANK(E27,$E$27:$E$33)&lt;=2),"TARGET","")))</f>
         <v/>
       </c>
       <c r="G27" s="40" t="str">
-        <f t="shared" ref="G27:G34" si="18">IF(J68="","",J68)</f>
+        <f t="shared" ref="G27:G34" si="20">IF(J68="","",J68)</f>
         <v/>
       </c>
       <c r="H27" s="43" t="str">
-        <f t="shared" ref="H27:H34" si="19">IF(OR($E27="",G27=""),"",((G27-$E27)/$E27)*100)</f>
+        <f t="shared" ref="H27:H34" si="21">IF(OR($E27="",G27=""),"",((G27-$E27)/$E27)*100)</f>
         <v/>
       </c>
       <c r="I27" s="40"/>
       <c r="J27" s="43" t="str">
-        <f t="shared" ref="J27:J34" si="20">IF(OR($E27="",I27=""),"",((I27-$E27)/$E27)*100)</f>
+        <f t="shared" ref="J27:J34" si="22">IF(OR($E27="",I27=""),"",((I27-$E27)/$E27)*100)</f>
         <v/>
       </c>
       <c r="K27" s="40"/>
       <c r="L27" s="43" t="str">
-        <f t="shared" ref="L27:L34" si="21">IF(OR($E27="",K27=""),"",((K27-$E27)/$E27)*100)</f>
+        <f t="shared" ref="L27:L34" si="23">IF(OR($E27="",K27=""),"",((K27-$E27)/$E27)*100)</f>
         <v/>
       </c>
       <c r="M27" s="33"/>
       <c r="N27" s="40" t="str">
-        <f t="shared" ref="N27:N34" si="22">IF(E27="","",E27)</f>
+        <f t="shared" ref="N27:N34" si="24">IF(E27="","",E27)</f>
         <v/>
       </c>
       <c r="O27" s="40"/>
       <c r="P27" s="43" t="str">
-        <f t="shared" ref="P27:P34" si="23">IF(OR($N27="",O27=""),"",((O27-$N27)/$N27)*100)</f>
+        <f t="shared" ref="P27:P34" si="25">IF(OR($N27="",O27=""),"",((O27-$N27)/$N27)*100)</f>
         <v/>
       </c>
       <c r="Q27" s="40"/>
       <c r="R27" s="43" t="str">
-        <f t="shared" ref="R27:R34" si="24">IF(OR($N27="",Q27=""),"",((Q27-$N27)/$N27)*100)</f>
+        <f t="shared" ref="R27:R34" si="26">IF(OR($N27="",Q27=""),"",((Q27-$N27)/$N27)*100)</f>
         <v/>
       </c>
       <c r="S27" s="40"/>
       <c r="T27" s="43" t="str">
-        <f t="shared" ref="T27:T34" si="25">IF(OR($N27="",S27=""),"",((S27-$N27)/$N27)*100)</f>
+        <f t="shared" ref="T27:T34" si="27">IF(OR($N27="",S27=""),"",((S27-$N27)/$N27)*100)</f>
         <v/>
       </c>
       <c r="V27" s="7" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>H_Rechts Hiel</v>
       </c>
       <c r="W27" s="7" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="X27" s="7" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Y27" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>200</v>
       </c>
       <c r="Z27" s="7"/>
@@ -16866,57 +16369,57 @@
       <c r="CS27" s="7"/>
       <c r="CT27" s="7"/>
     </row>
-    <row r="28" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="98"/>
-      <c r="B28" s="99"/>
+    <row r="28" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="94"/>
+      <c r="B28" s="95"/>
       <c r="C28" s="83" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="D28" s="37"/>
       <c r="E28" s="38" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="F28" s="39" t="str">
-        <f>IF($C$36=C28,"TARGET",IF(E28="","",IF(AND(E28&gt;200,RANK(E28,$E$27:$E$33)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="G28" s="40" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H28" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I28" s="40"/>
       <c r="J28" s="43" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="K28" s="40"/>
       <c r="L28" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M28" s="33"/>
       <c r="N28" s="40" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="O28" s="40"/>
       <c r="P28" s="43" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q28" s="40"/>
       <c r="R28" s="43" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="S28" s="40"/>
       <c r="T28" s="43" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="V28" s="7"/>
@@ -16997,57 +16500,57 @@
       <c r="CS28" s="7"/>
       <c r="CT28" s="7"/>
     </row>
-    <row r="29" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="98"/>
-      <c r="B29" s="99"/>
+    <row r="29" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="94"/>
+      <c r="B29" s="95"/>
       <c r="C29" s="83" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="D29" s="37"/>
       <c r="E29" s="38" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="F29" s="39" t="str">
-        <f>IF($C$36=C29,"TARGET",IF(E29="","",IF(AND(E29&gt;200,RANK(E29,$E$27:$E$33)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="G29" s="40" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H29" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I29" s="40"/>
       <c r="J29" s="43" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="K29" s="40"/>
       <c r="L29" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M29" s="33"/>
       <c r="N29" s="40" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="O29" s="40"/>
       <c r="P29" s="43" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q29" s="40"/>
       <c r="R29" s="43" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="S29" s="40"/>
       <c r="T29" s="43" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="V29" s="7"/>
@@ -17128,57 +16631,57 @@
       <c r="CS29" s="7"/>
       <c r="CT29" s="7"/>
     </row>
-    <row r="30" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="98"/>
-      <c r="B30" s="99"/>
+    <row r="30" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="94"/>
+      <c r="B30" s="95"/>
       <c r="C30" s="83" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="D30" s="37"/>
       <c r="E30" s="38" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="F30" s="39" t="str">
-        <f>IF($C$36=C30,"TARGET",IF(E30="","",IF(AND(E30&gt;200,RANK(E30,$E$27:$E$33)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="G30" s="40" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H30" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I30" s="40"/>
       <c r="J30" s="43" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="K30" s="40"/>
       <c r="L30" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M30" s="33"/>
       <c r="N30" s="40" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="O30" s="40"/>
       <c r="P30" s="43" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q30" s="40"/>
       <c r="R30" s="43" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="S30" s="40"/>
       <c r="T30" s="43" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="V30" s="7"/>
@@ -17259,57 +16762,57 @@
       <c r="CS30" s="7"/>
       <c r="CT30" s="7"/>
     </row>
-    <row r="31" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="98"/>
-      <c r="B31" s="99"/>
+    <row r="31" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="94"/>
+      <c r="B31" s="95"/>
       <c r="C31" s="83" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="D31" s="37"/>
       <c r="E31" s="38" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="F31" s="39" t="str">
-        <f>IF($C$36=C31,"TARGET",IF(E31="","",IF(AND(E31&gt;200,RANK(E31,$E$27:$E$33)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="G31" s="40" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H31" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I31" s="40"/>
       <c r="J31" s="43" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="K31" s="40"/>
       <c r="L31" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M31" s="33"/>
       <c r="N31" s="40" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="O31" s="40"/>
       <c r="P31" s="43" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q31" s="40"/>
       <c r="R31" s="43" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="S31" s="40"/>
       <c r="T31" s="43" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="V31" s="7"/>
@@ -17390,57 +16893,57 @@
       <c r="CS31" s="7"/>
       <c r="CT31" s="7"/>
     </row>
-    <row r="32" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="98"/>
-      <c r="B32" s="99"/>
+    <row r="32" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="94"/>
+      <c r="B32" s="95"/>
       <c r="C32" s="83" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="D32" s="37"/>
       <c r="E32" s="41" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="F32" s="39" t="str">
-        <f>IF($C$36=C32,"TARGET",IF(E32="","",IF(AND(E32&gt;200,RANK(E32,$E$27:$E$33)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="G32" s="40" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H32" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I32" s="40"/>
       <c r="J32" s="43" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="K32" s="40"/>
       <c r="L32" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M32" s="33"/>
       <c r="N32" s="40" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="O32" s="40"/>
       <c r="P32" s="43" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q32" s="40"/>
       <c r="R32" s="43" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="S32" s="40"/>
       <c r="T32" s="43" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="V32" s="7"/>
@@ -17521,57 +17024,57 @@
       <c r="CS32" s="7"/>
       <c r="CT32" s="7"/>
     </row>
-    <row r="33" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="98"/>
-      <c r="B33" s="99"/>
+    <row r="33" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="94"/>
+      <c r="B33" s="95"/>
       <c r="C33" s="83" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="D33" s="37"/>
       <c r="E33" s="41" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="F33" s="39" t="str">
-        <f>IF($C$36=C33,"TARGET",IF(E33="","",IF(AND(E33&gt;200,RANK(E33,$E$27:$E$33)&lt;=2),"TARGET","")))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="G33" s="40" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H33" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I33" s="40"/>
       <c r="J33" s="43" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="K33" s="40"/>
       <c r="L33" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M33" s="33"/>
       <c r="N33" s="40" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="O33" s="40"/>
       <c r="P33" s="43" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q33" s="40"/>
       <c r="R33" s="43" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="S33" s="40"/>
       <c r="T33" s="43" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="V33" s="7"/>
@@ -17652,15 +17155,15 @@
       <c r="CS33" s="7"/>
       <c r="CT33" s="7"/>
     </row>
-    <row r="34" spans="1:98" s="5" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="100"/>
-      <c r="B34" s="101"/>
+    <row r="34" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="96"/>
+      <c r="B34" s="97"/>
       <c r="C34" s="83" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="D34" s="37"/>
       <c r="E34" s="41" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="F34" s="39" t="str">
@@ -17668,41 +17171,41 @@
         <v/>
       </c>
       <c r="G34" s="40" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H34" s="43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I34" s="40"/>
       <c r="J34" s="43" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="K34" s="40"/>
       <c r="L34" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M34" s="33"/>
       <c r="N34" s="40" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="O34" s="40"/>
       <c r="P34" s="43" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q34" s="40"/>
       <c r="R34" s="43" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="S34" s="40"/>
       <c r="T34" s="43" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="V34" s="7"/>
@@ -17783,7 +17286,7 @@
       <c r="CS34" s="7"/>
       <c r="CT34" s="7"/>
     </row>
-    <row r="35" spans="1:98" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:98" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="21"/>
       <c r="B35" s="21"/>
       <c r="C35" s="48"/>
@@ -17882,29 +17385,29 @@
       <c r="CS35" s="3"/>
       <c r="CT35" s="3"/>
     </row>
-    <row r="36" spans="1:98" s="5" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="102" t="s">
-        <v>115</v>
-      </c>
-      <c r="B36" s="103"/>
-      <c r="C36" s="104"/>
-      <c r="D36" s="105"/>
-      <c r="E36" s="105"/>
-      <c r="F36" s="105"/>
-      <c r="G36" s="105"/>
-      <c r="H36" s="105"/>
-      <c r="I36" s="105"/>
-      <c r="J36" s="105"/>
-      <c r="K36" s="105"/>
-      <c r="L36" s="105"/>
-      <c r="M36" s="105"/>
-      <c r="N36" s="105"/>
-      <c r="O36" s="105"/>
-      <c r="P36" s="105"/>
-      <c r="Q36" s="105"/>
-      <c r="R36" s="105"/>
-      <c r="S36" s="105"/>
-      <c r="T36" s="106"/>
+    <row r="36" spans="1:98" s="5" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="87" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="88"/>
+      <c r="C36" s="89"/>
+      <c r="D36" s="90"/>
+      <c r="E36" s="90"/>
+      <c r="F36" s="90"/>
+      <c r="G36" s="90"/>
+      <c r="H36" s="90"/>
+      <c r="I36" s="90"/>
+      <c r="J36" s="90"/>
+      <c r="K36" s="90"/>
+      <c r="L36" s="90"/>
+      <c r="M36" s="90"/>
+      <c r="N36" s="90"/>
+      <c r="O36" s="90"/>
+      <c r="P36" s="90"/>
+      <c r="Q36" s="90"/>
+      <c r="R36" s="90"/>
+      <c r="S36" s="90"/>
+      <c r="T36" s="91"/>
       <c r="V36" s="7"/>
       <c r="W36" s="7"/>
       <c r="X36" s="7"/>
@@ -17983,7 +17486,7 @@
       <c r="CS36" s="7"/>
       <c r="CT36" s="7"/>
     </row>
-    <row r="37" spans="1:98" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:98" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="19"/>
       <c r="B37" s="19"/>
       <c r="C37" s="28"/>
@@ -18082,12 +17585,12 @@
       <c r="CS37" s="7"/>
       <c r="CT37" s="7"/>
     </row>
-    <row r="39" spans="1:98" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:98" ht="16" x14ac:dyDescent="0.4">
       <c r="A39" s="45" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:98" x14ac:dyDescent="0.35">
       <c r="A40" s="53"/>
       <c r="B40" s="47"/>
       <c r="C40" s="47"/>
@@ -18109,9 +17612,9 @@
       <c r="S40" s="47"/>
       <c r="T40" s="47"/>
     </row>
-    <row r="41" spans="1:98" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:98" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="54" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="B41" s="50"/>
       <c r="C41" s="50"/>
@@ -18211,7 +17714,7 @@
       <c r="CS41" s="9"/>
       <c r="CT41" s="9"/>
     </row>
-    <row r="42" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:98" x14ac:dyDescent="0.35">
       <c r="A42" s="53"/>
       <c r="B42" s="47"/>
       <c r="C42" s="47"/>
@@ -18233,9 +17736,9 @@
       <c r="S42" s="47"/>
       <c r="T42" s="47"/>
     </row>
-    <row r="43" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:98" x14ac:dyDescent="0.35">
       <c r="A43" s="55" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="B43" s="50"/>
       <c r="C43" s="50"/>
@@ -18257,14 +17760,14 @@
       <c r="S43" s="47"/>
       <c r="T43" s="47"/>
     </row>
-    <row r="45" spans="1:98" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:98" ht="16" x14ac:dyDescent="0.4">
       <c r="A45" s="45" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="46" spans="1:98" ht="45" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="46" spans="1:98" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A46" s="44" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -18278,15 +17781,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:98" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:98" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -18294,15 +17795,13 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
     </row>
-    <row r="48" spans="1:98" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:98" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -18310,15 +17809,13 @@
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -18326,15 +17823,13 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -18342,15 +17837,13 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
     </row>
-    <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -18358,15 +17851,13 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
@@ -18374,15 +17865,13 @@
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
     </row>
-    <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -18390,15 +17879,13 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
     </row>
-    <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -18406,7 +17893,7 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -18416,7 +17903,7 @@
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -18426,14 +17913,12 @@
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
     </row>
-    <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B57" s="1"/>
       <c r="C57" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -18441,14 +17926,12 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
     </row>
-    <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B58" s="1"/>
       <c r="C58" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
@@ -18456,14 +17939,12 @@
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
     </row>
-    <row r="59" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B59" s="1"/>
       <c r="C59" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -18471,14 +17952,12 @@
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
     </row>
-    <row r="60" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B60" s="1"/>
       <c r="C60" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
@@ -18486,14 +17965,12 @@
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
     </row>
-    <row r="61" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B61" s="1"/>
       <c r="C61" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
@@ -18501,13 +17978,11 @@
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
     </row>
-    <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C62" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
@@ -18515,13 +17990,11 @@
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
     </row>
-    <row r="63" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C63" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
@@ -18529,13 +18002,11 @@
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
     </row>
-    <row r="64" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C64" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -18543,26 +18014,24 @@
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
     </row>
-    <row r="66" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" ht="16" x14ac:dyDescent="0.4">
       <c r="A66" s="45" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" s="44" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="J67" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C68" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
@@ -18570,13 +18039,11 @@
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
     </row>
-    <row r="69" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C69" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
@@ -18584,13 +18051,11 @@
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
     </row>
-    <row r="70" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C70" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
@@ -18598,13 +18063,11 @@
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
     </row>
-    <row r="71" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C71" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="D71" s="1"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
@@ -18612,13 +18075,11 @@
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
     </row>
-    <row r="72" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C72" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="D72" s="1"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
@@ -18626,13 +18087,11 @@
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
     </row>
-    <row r="73" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C73" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
@@ -18640,13 +18099,11 @@
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
     </row>
-    <row r="74" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C74" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
@@ -18654,13 +18111,11 @@
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
     </row>
-    <row r="75" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C75" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
@@ -18668,13 +18123,11 @@
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
     </row>
-    <row r="78" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C78" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
@@ -18682,13 +18135,11 @@
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
     </row>
-    <row r="79" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C79" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
@@ -18696,13 +18147,11 @@
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
     </row>
-    <row r="80" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C80" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
@@ -18710,13 +18159,11 @@
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
     </row>
-    <row r="81" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C81" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
@@ -18724,13 +18171,11 @@
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
     </row>
-    <row r="82" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C82" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
@@ -18738,13 +18183,11 @@
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
     </row>
-    <row r="83" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C83" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
@@ -18752,13 +18195,11 @@
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
     </row>
-    <row r="84" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C84" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
@@ -18766,13 +18207,11 @@
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
     </row>
-    <row r="85" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C85" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
@@ -18782,11 +18221,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="E2:L2"/>
-    <mergeCell ref="E3:L3"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="D8:L8"/>
-    <mergeCell ref="N8:T8"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:T36"/>
+    <mergeCell ref="A25:B34"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="Q25:R25"/>
     <mergeCell ref="Q9:R9"/>
     <mergeCell ref="S9:T9"/>
     <mergeCell ref="A20:B20"/>
@@ -18798,22 +18241,18 @@
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="O9:P9"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:T36"/>
-    <mergeCell ref="A25:B34"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="E3:L3"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="D8:L8"/>
+    <mergeCell ref="N8:T8"/>
   </mergeCells>
   <conditionalFormatting sqref="E11:E18">
-    <cfRule type="expression" dxfId="59" priority="8">
+    <cfRule type="expression" dxfId="59" priority="7">
+      <formula>AND(E11&lt;&gt;"",E11&gt;=200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="8">
       <formula>AND(E11&lt;&gt;"",E11&lt;200)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="58" priority="7">
-      <formula>AND(E11&lt;&gt;"",E11&gt;=200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E27:E34">
@@ -18851,19 +18290,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:H18">
-    <cfRule type="expression" dxfId="49" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="43" stopIfTrue="1">
+      <formula>AND(H11&lt;&gt;"",OR(G11&lt;200,H11&lt;=-25))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="48" priority="44" stopIfTrue="1">
       <formula>AND(H11&lt;&gt;"",G11&gt;=200,H11&gt;-25)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="43" stopIfTrue="1">
-      <formula>AND(H11&lt;&gt;"",OR(G11&lt;200,H11&lt;=-25))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H34">
-    <cfRule type="expression" dxfId="47" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="45" stopIfTrue="1">
+      <formula>AND(H27&lt;&gt;"",OR(G27&lt;200,H27&lt;=-25))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="46" priority="46" stopIfTrue="1">
       <formula>AND(H27&lt;&gt;"",G27&gt;=200,H27&gt;-25)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="46" priority="45" stopIfTrue="1">
-      <formula>AND(H27&lt;&gt;"",OR(G27&lt;200,H27&lt;=-25))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I11:I18">
@@ -18883,19 +18322,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J18">
-    <cfRule type="expression" dxfId="41" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="47" stopIfTrue="1">
+      <formula>AND(J11&lt;&gt;"",OR(I11&lt;200,J11&lt;=-25))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="48" stopIfTrue="1">
       <formula>AND(J11&lt;&gt;"",I11&gt;=200,J11&gt;-25)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="47" stopIfTrue="1">
-      <formula>AND(J11&lt;&gt;"",OR(I11&lt;200,J11&lt;=-25))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J27:J34">
-    <cfRule type="expression" dxfId="39" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="49" stopIfTrue="1">
+      <formula>AND(J27&lt;&gt;"",OR(I27&lt;200,J27&lt;=-25))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="50" stopIfTrue="1">
       <formula>AND(J27&lt;&gt;"",I27&gt;=200,J27&gt;-25)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="38" priority="49" stopIfTrue="1">
-      <formula>AND(J27&lt;&gt;"",OR(I27&lt;200,J27&lt;=-25))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:K18">
@@ -18907,19 +18346,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K34">
-    <cfRule type="expression" dxfId="35" priority="32">
+    <cfRule type="expression" dxfId="35" priority="31">
+      <formula>AND(K27&lt;&gt;"",K27&gt;=200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="32">
       <formula>AND(K27&lt;&gt;"",K27&lt;200)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="31">
-      <formula>AND(K27&lt;&gt;"",K27&gt;=200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L11:L18">
-    <cfRule type="expression" dxfId="33" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="51" stopIfTrue="1">
+      <formula>AND(L11&lt;&gt;"",OR(K11&lt;200,L11&lt;=-25))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="52" stopIfTrue="1">
       <formula>AND(L11&lt;&gt;"",K11&gt;=200,L11&gt;-25)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="51" stopIfTrue="1">
-      <formula>AND(L11&lt;&gt;"",OR(K11&lt;200,L11&lt;=-25))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L27:L34">
@@ -18931,25 +18370,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O11:O18">
-    <cfRule type="expression" dxfId="29" priority="15">
+    <cfRule type="expression" dxfId="29" priority="6" stopIfTrue="1">
+      <formula>AND(O11&lt;&gt;"",O11&gt;=1.05*IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="15">
       <formula>AND(O11&lt;&gt;"",O11&gt;=200)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="6" stopIfTrue="1">
-      <formula>AND(O11&lt;&gt;"",O11&gt;=1.05*IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11)))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="27" priority="16">
       <formula>AND(O11&lt;&gt;"",O11&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O27:O34">
-    <cfRule type="expression" dxfId="26" priority="33">
+    <cfRule type="expression" dxfId="26" priority="3" stopIfTrue="1">
+      <formula>AND(O27&lt;&gt;"",O27&gt;=1.05*IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="33">
       <formula>AND(O27&lt;&gt;"",O27&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="34">
+    <cfRule type="expression" dxfId="24" priority="34">
       <formula>AND(O27&lt;&gt;"",O27&lt;200)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="3" stopIfTrue="1">
-      <formula>AND(O27&lt;&gt;"",O27&gt;=1.05*IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P11:P18">
@@ -18969,14 +18408,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q11:Q18">
-    <cfRule type="expression" dxfId="19" priority="18">
-      <formula>AND(Q11&lt;&gt;"",Q11&lt;200)</formula>
+    <cfRule type="expression" dxfId="19" priority="5" stopIfTrue="1">
+      <formula>AND(Q11&lt;&gt;"",Q11&gt;=1.05*IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11)))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="18" priority="17">
       <formula>AND(Q11&lt;&gt;"",Q11&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="5" stopIfTrue="1">
-      <formula>AND(Q11&lt;&gt;"",Q11&gt;=1.05*IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11)))</formula>
+    <cfRule type="expression" dxfId="17" priority="18">
+      <formula>AND(Q11&lt;&gt;"",Q11&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q27:Q34">
@@ -19007,25 +18446,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S11:S18">
-    <cfRule type="expression" dxfId="9" priority="20">
-      <formula>AND(S11&lt;&gt;"",S11&lt;200)</formula>
+    <cfRule type="expression" dxfId="9" priority="4" stopIfTrue="1">
+      <formula>AND(S11&lt;&gt;"",S11&gt;=1.05*IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11)))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>AND(S11&lt;&gt;"",S11&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="4" stopIfTrue="1">
-      <formula>AND(S11&lt;&gt;"",S11&gt;=1.05*IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11)))</formula>
+    <cfRule type="expression" dxfId="7" priority="20">
+      <formula>AND(S11&lt;&gt;"",S11&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S27:S34">
-    <cfRule type="expression" dxfId="6" priority="37">
+    <cfRule type="expression" dxfId="6" priority="1" stopIfTrue="1">
+      <formula>AND(S27&lt;&gt;"",S27&gt;=1.05*IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="37">
       <formula>AND(S27&lt;&gt;"",S27&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="38">
+    <cfRule type="expression" dxfId="4" priority="38">
       <formula>AND(S27&lt;&gt;"",S27&lt;200)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="1" stopIfTrue="1">
-      <formula>AND(S27&lt;&gt;"",S27&gt;=1.05*IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T11:T18">

--- a/(e)CRF/Per visite/V2 - Aanmeting voetorthese/Metingen en klinische registratie/Pressure monitoring tool_patient.xlsx
+++ b/(e)CRF/Per visite/V2 - Aanmeting voetorthese/Metingen en klinische registratie/Pressure monitoring tool_patient.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kuleuven-my.sharepoint.com/personal/janou_debuyser_kuleuven_be1/Documents/Documents/PhD Brugge/Site/(e)CRF/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janou\AppData\Local\Temp\claude\c--Users-janou-OneDrive---KU-Leuven-Documents-PhD-Brugge-Site\bc4ac141-32fc-489e-b2c3-e6515fecc0f9\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1111" documentId="8_{ED26CC68-7C05-4D39-8592-D9D42AE93F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63045DD7-530C-4D1B-BFA4-67F3C321410A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E09ED5-F868-4469-975F-DCBA29911680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="14400" windowHeight="7450" xr2:uid="{D8186157-3417-4030-89A9-46AA9F0BACB5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{D8186157-3417-4030-89A9-46AA9F0BACB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Meting" sheetId="4" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="TEMPLATE (blank)" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'TEMPLATE (blank)'!$A$1:$T$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Visit!$A$1:$T$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'TEMPLATE (blank)'!$A$1:$X$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Visit!$A$1:$X$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
     <author>Janou De Buyser</author>
   </authors>
   <commentList>
-    <comment ref="Y5" authorId="0" shapeId="0" xr:uid="{D437B22C-0D45-43E3-8A69-D88E244ADEDD}">
+    <comment ref="AC5" authorId="0" shapeId="0" xr:uid="{D437B22C-0D45-43E3-8A69-D88E244ADEDD}">
       <text>
         <r>
           <rPr>
@@ -81,7 +81,7 @@
     <author>Janou De Buyser</author>
   </authors>
   <commentList>
-    <comment ref="Y5" authorId="0" shapeId="0" xr:uid="{78D46782-F8B6-4D36-963B-CF4613E88FFA}">
+    <comment ref="AC5" authorId="0" shapeId="0" xr:uid="{78D46782-F8B6-4D36-963B-CF4613E88FFA}">
       <text>
         <r>
           <rPr>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="112">
   <si>
     <t>LEFT</t>
   </si>
@@ -286,9 +286,6 @@
     <t>Regio</t>
   </si>
   <si>
-    <t>Met zool (kPa)</t>
-  </si>
-  <si>
     <t>Norm gehaald?</t>
   </si>
   <si>
@@ -322,12 +319,6 @@
     <t>Reden</t>
   </si>
   <si>
-    <t>Stijging &gt;= 5% t.o.v. vorige keer?</t>
-  </si>
-  <si>
-    <t>Bij NEE, of bij een stijging van 5% of meer: de pedorthist past de zool aan en je meet opnieuw. Noteer de extra ontlastingstest op eCRF 24.</t>
-  </si>
-  <si>
     <t>6. Schermafbeelding van het MPP-beeld</t>
   </si>
   <si>
@@ -337,34 +328,13 @@
     <t>Opslaan en mailen naar janou.debuyser@kuleuven.be. Laat het bestand daarna op de laptop staan - verwijder het nooit zelf.</t>
   </si>
   <si>
-    <t>Referentie: zonder zool op visite 2 (kPa)</t>
-  </si>
-  <si>
     <t>Zonder zool vandaag (kPa)</t>
-  </si>
-  <si>
-    <t>% lager dan referentie</t>
   </si>
   <si>
     <t>4. Drie regio's per voet - de vorige voetzweer eerst</t>
   </si>
   <si>
-    <t>Norm: piekdruk met zool onder 200 kPa, OF minstens 25% lager dan de referentie. De referentie is de meting zonder zool op visite 2 en blijft op maand 6, 12 en 18 dezelfde. Op visite 2 vul je in kolom D dezelfde waarde in als in kolom E; op maand 6, 12 en 18 de waarde van visite 2.</t>
-  </si>
-  <si>
-    <t>Visite 2 - aflevering CMFO (referentie)</t>
-  </si>
-  <si>
     <t>Opvolging - maand 6, 12 of 18</t>
-  </si>
-  <si>
-    <t>Referentie: zonder zool visite 2</t>
-  </si>
-  <si>
-    <t>% t.o.v. zonder zool V2</t>
-  </si>
-  <si>
-    <t>Norm per doelregio: piekdruk met zool onder 200 kPa, of minstens 25% lager dan de referentie zonder zool op visite 2. Die referentie blijft op maand 6, 12 en 18 dezelfde. Pas de zool ook aan als de piekdruk met zool 5% of meer hoger ligt dan na de laatste aanpassing op visite 2: die cel kleurt oranje.</t>
   </si>
   <si>
     <t>Vorige voetzweer links (kies uit de lijst):</t>
@@ -440,6 +410,42 @@
   </si>
   <si>
     <t>In te vullen door het studieteam. Rechts A-H (boven), links I-P (onder); kolom J = piekdruk (kPa).</t>
+  </si>
+  <si>
+    <t>Met zool, vorige meting (kPa)</t>
+  </si>
+  <si>
+    <t>Met zool vandaag (kPa)</t>
+  </si>
+  <si>
+    <t>% lager dan zonder zool vandaag</t>
+  </si>
+  <si>
+    <t>Stijging &gt;= 5% t.o.v. vorige meting?</t>
+  </si>
+  <si>
+    <t>Norm: piekdruk met zool onder 200 kPa, OF minstens 25% lager dan zonder zool in dezelfde sessie (kolom E). Eén van beide volstaat. Kolom D is de piekdruk met zool van de vorige meting (leeg op visite 2): daarmee zie je een stijging van 5% of meer.</t>
+  </si>
+  <si>
+    <t>Bij NEE, of bij een stijging van 5% of meer: de pedorthist past de zool aan en je meet opnieuw met zool, tot drie aanpassingen. Noteer de extra ontlastingstesten (1 tot 3) op eCRF 24.</t>
+  </si>
+  <si>
+    <t>Usual Care: alleen op visite 1 en maand 6, geblindeerd (palet met drempel 50 kPa, waarden uit). Vul alleen blok 1 en 2 in en lees niets af; het studieteam haalt de waarden centraal uit het exportbestand.</t>
+  </si>
+  <si>
+    <t>Met zool - sessie 4</t>
+  </si>
+  <si>
+    <t>Zonder zool - deze sessie</t>
+  </si>
+  <si>
+    <t>% t.o.v. zonder zool deze sessie</t>
+  </si>
+  <si>
+    <t>Visite 2 - aflevering CMFO</t>
+  </si>
+  <si>
+    <t>Norm per doelregio: piekdruk met zool onder 200 kPa, of minstens 25% lager dan zonder zool in dezelfde sessie. Eén van beide volstaat. Tot drie aanpassingen per sessie (sessie 1 tot 4). Pas de zool ook aan als de piekdruk met zool 5% of meer hoger ligt dan na de laatste aanpassing op visite 2: die cel kleurt oranje.</t>
   </si>
 </sst>
 </file>
@@ -797,7 +803,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -881,17 +887,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -957,21 +952,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFBFD3EA"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFD3EA"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFD3EA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thick">
         <color rgb="FFF5A623"/>
       </left>
@@ -995,11 +975,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFD3EA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFD3EA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFD3EA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1070,28 +1079,28 @@
     <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1113,9 +1122,9 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1125,13 +1134,13 @@
     <xf numFmtId="0" fontId="13" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1143,7 +1152,7 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="21" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="21" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1158,10 +1167,10 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1169,32 +1178,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1208,75 +1214,68 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="120">
-    <dxf>
-      <font>
-        <color rgb="FFB3261E"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDE7E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="140">
     <dxf>
       <font>
         <color rgb="FF0F6B33"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
           <bgColor rgb="FFE9F7EE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <color rgb="FFB3261E"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
           <bgColor rgb="FFFDE7E9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFE9F7EE"/>
+          <bgColor rgb="FFFFC78C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1344,41 +1343,32 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFB3261E"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDE7E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF0F6B33"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
           <bgColor rgb="FFE9F7EE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <color rgb="FFB3261E"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
           <bgColor rgb="FFFDE7E9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFE9F7EE"/>
+          <bgColor rgb="FFFFC78C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1446,41 +1436,32 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFB3261E"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDE7E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF0F6B33"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
           <bgColor rgb="FFE9F7EE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <color rgb="FFB3261E"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
           <bgColor rgb="FFFDE7E9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFE9F7EE"/>
+          <bgColor rgb="FFFFC78C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1540,9 +1521,146 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFB3261E"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC78C"/>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE9F7EE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1885,42 +2003,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FFB3261E"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFDE7E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE9F7EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFB3261E"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDE7E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0F6B33"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE9F7EE"/>
+          <bgColor rgb="FFFFC78C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1980,9 +2065,50 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC78C"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFDE7E9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2023,6 +2149,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC78C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2082,13 +2215,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC78C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FFB3261E"/>
       </font>
@@ -2125,6 +2251,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC78C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2184,9 +2317,104 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC78C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFDE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC78C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0F6B33"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE9F7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFDE7E9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2616,7 +2844,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Visit!$W$7</c:f>
+              <c:f>Visit!$AA$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2637,7 +2865,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Visit!$V$8:$V$15</c:f>
+              <c:f>Visit!$Z$8:$Z$15</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -2669,7 +2897,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Visit!$W$8:$W$15</c:f>
+              <c:f>Visit!$AA$8:$AA$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -2711,7 +2939,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Visit!$X$7</c:f>
+              <c:f>Visit!$AB$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2732,7 +2960,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Visit!$V$8:$V$15</c:f>
+              <c:f>Visit!$Z$8:$Z$15</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -2764,7 +2992,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Visit!$X$8:$X$15</c:f>
+              <c:f>Visit!$AB$8:$AB$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -2822,7 +3050,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Visit!$Y$7</c:f>
+              <c:f>Visit!$AC$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2846,7 +3074,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Visit!$V$8:$V$15</c:f>
+              <c:f>Visit!$Z$8:$Z$15</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -2878,7 +3106,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Visit!$Y$8:$Y$15</c:f>
+              <c:f>Visit!$AC$8:$AC$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -3243,7 +3471,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Visit!$W$19</c:f>
+              <c:f>Visit!$AA$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3264,7 +3492,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Visit!$V$20:$V$27</c:f>
+              <c:f>Visit!$Z$20:$Z$27</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -3296,7 +3524,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Visit!$W$20:$W$27</c:f>
+              <c:f>Visit!$AA$20:$AA$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -3338,7 +3566,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Visit!$X$19</c:f>
+              <c:f>Visit!$AB$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3359,7 +3587,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Visit!$V$20:$V$27</c:f>
+              <c:f>Visit!$Z$20:$Z$27</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -3391,7 +3619,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Visit!$X$20:$X$27</c:f>
+              <c:f>Visit!$AB$20:$AB$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -3449,7 +3677,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Visit!$Y$19</c:f>
+              <c:f>Visit!$AC$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3473,7 +3701,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Visit!$V$20:$V$27</c:f>
+              <c:f>Visit!$Z$20:$Z$27</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -3505,7 +3733,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Visit!$Y$20:$Y$27</c:f>
+              <c:f>Visit!$AC$20:$AC$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -3870,7 +4098,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'TEMPLATE (blank)'!$W$7</c:f>
+              <c:f>'TEMPLATE (blank)'!$AA$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3891,7 +4119,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'TEMPLATE (blank)'!$V$8:$V$15</c:f>
+              <c:f>'TEMPLATE (blank)'!$Z$8:$Z$15</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -3923,7 +4151,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TEMPLATE (blank)'!$W$8:$W$15</c:f>
+              <c:f>'TEMPLATE (blank)'!$AA$8:$AA$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -3965,7 +4193,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'TEMPLATE (blank)'!$X$7</c:f>
+              <c:f>'TEMPLATE (blank)'!$AB$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3986,7 +4214,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'TEMPLATE (blank)'!$V$8:$V$15</c:f>
+              <c:f>'TEMPLATE (blank)'!$Z$8:$Z$15</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -4018,7 +4246,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TEMPLATE (blank)'!$X$8:$X$15</c:f>
+              <c:f>'TEMPLATE (blank)'!$AB$8:$AB$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -4076,7 +4304,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'TEMPLATE (blank)'!$Y$7</c:f>
+              <c:f>'TEMPLATE (blank)'!$AC$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4100,7 +4328,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'TEMPLATE (blank)'!$V$8:$V$15</c:f>
+              <c:f>'TEMPLATE (blank)'!$Z$8:$Z$15</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -4132,7 +4360,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TEMPLATE (blank)'!$Y$8:$Y$15</c:f>
+              <c:f>'TEMPLATE (blank)'!$AC$8:$AC$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -4497,7 +4725,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'TEMPLATE (blank)'!$W$19</c:f>
+              <c:f>'TEMPLATE (blank)'!$AA$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4518,7 +4746,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'TEMPLATE (blank)'!$V$20:$V$27</c:f>
+              <c:f>'TEMPLATE (blank)'!$Z$20:$Z$27</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -4550,7 +4778,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TEMPLATE (blank)'!$W$20:$W$27</c:f>
+              <c:f>'TEMPLATE (blank)'!$AA$20:$AA$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -4592,7 +4820,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'TEMPLATE (blank)'!$X$19</c:f>
+              <c:f>'TEMPLATE (blank)'!$AB$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4613,7 +4841,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'TEMPLATE (blank)'!$V$20:$V$27</c:f>
+              <c:f>'TEMPLATE (blank)'!$Z$20:$Z$27</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -4645,7 +4873,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TEMPLATE (blank)'!$X$20:$X$27</c:f>
+              <c:f>'TEMPLATE (blank)'!$AB$20:$AB$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -4703,7 +4931,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'TEMPLATE (blank)'!$Y$19</c:f>
+              <c:f>'TEMPLATE (blank)'!$AC$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4727,7 +4955,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'TEMPLATE (blank)'!$V$20:$V$27</c:f>
+              <c:f>'TEMPLATE (blank)'!$Z$20:$Z$27</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -4759,7 +4987,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'TEMPLATE (blank)'!$Y$20:$Y$27</c:f>
+              <c:f>'TEMPLATE (blank)'!$AC$20:$AC$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -7269,13 +7497,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
+      <xdr:col>29</xdr:col>
       <xdr:colOff>590549</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>190499</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
+      <xdr:col>39</xdr:col>
       <xdr:colOff>590549</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>190499</xdr:rowOff>
@@ -7305,13 +7533,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
+      <xdr:col>29</xdr:col>
       <xdr:colOff>590549</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>180974</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
+      <xdr:col>39</xdr:col>
       <xdr:colOff>590549</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>190499</xdr:rowOff>
@@ -7490,13 +7718,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
+      <xdr:col>29</xdr:col>
       <xdr:colOff>590549</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>190499</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
+      <xdr:col>39</xdr:col>
       <xdr:colOff>590549</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>190499</xdr:rowOff>
@@ -7528,13 +7756,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
+      <xdr:col>29</xdr:col>
       <xdr:colOff>590549</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>180974</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
+      <xdr:col>39</xdr:col>
       <xdr:colOff>590549</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>190499</xdr:rowOff>
@@ -7575,7 +7803,7 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>683932</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>66295</xdr:rowOff>
+      <xdr:rowOff>66296</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7665,10 +7893,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8023,27 +8247,40 @@
     <col min="8" max="9" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="70" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" ht="18" x14ac:dyDescent="0.4">
       <c r="A2" s="71" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="72" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="101" t="s">
+        <v>106</v>
+      </c>
+      <c r="B4" s="101"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="73" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="75" t="s">
         <v>23</v>
       </c>
@@ -8057,7 +8294,7 @@
       </c>
       <c r="H6" s="76"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="75" t="s">
         <v>26</v>
       </c>
@@ -8073,7 +8310,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="75" t="s">
         <v>29</v>
       </c>
@@ -8089,22 +8326,22 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="72" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="72" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="73" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="75" t="s">
         <v>37</v>
       </c>
@@ -8118,7 +8355,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="75" t="s">
         <v>41</v>
       </c>
@@ -8128,7 +8365,7 @@
       <c r="D14" s="76"/>
       <c r="F14" s="76"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="75" t="s">
         <v>43</v>
       </c>
@@ -8138,7 +8375,7 @@
       <c r="D15" s="76"/>
       <c r="F15" s="76"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="72" t="s">
         <v>45</v>
       </c>
@@ -8211,12 +8448,12 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="73" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="72" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="39.5" x14ac:dyDescent="0.35">
@@ -8228,127 +8465,153 @@
       </c>
       <c r="C28" s="82"/>
       <c r="D28" s="81" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E28" s="81" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F28" s="81" t="s">
+        <v>101</v>
+      </c>
+      <c r="G28" s="81" t="s">
+        <v>102</v>
+      </c>
+      <c r="H28" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="G28" s="81" t="s">
-        <v>77</v>
-      </c>
-      <c r="H28" s="81" t="s">
-        <v>59</v>
-      </c>
-      <c r="I28" s="82"/>
+      <c r="I28" s="81" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="74" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B29" s="76"/>
       <c r="D29" s="76"/>
       <c r="E29" s="76"/>
       <c r="F29" s="76"/>
       <c r="G29" s="80" t="str">
-        <f t="shared" ref="G29:G34" si="0">IF(OR(D29="",F29=""),"",(D29-F29)/D29)</f>
+        <f>IF(OR(E29="",F29=""),"",(E29-F29)/E29)</f>
         <v/>
       </c>
       <c r="H29" s="12" t="str">
-        <f t="shared" ref="H29:H34" si="1">IF(F29="","",IF(F29&lt;200,"JA",IF(D29="","referentie ontbreekt",IF((D29-F29)/D29&gt;=0.25,"JA","NEE"))))</f>
+        <f>IF(F29="","",IF(F29&lt;200,"JA",IF(E29="","zonder zool ontbreekt",IF((E29-F29)/E29&gt;=0.25,"JA","NEE"))))</f>
+        <v/>
+      </c>
+      <c r="I29" s="76" t="str">
+        <f>IF(OR(D29="",F29=""),"",IF((F29-D29)/D29&gt;=0.05,"JA","nee"))</f>
         <v/>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="74" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30" s="76"/>
       <c r="D30" s="76"/>
       <c r="E30" s="76"/>
       <c r="F30" s="76"/>
       <c r="G30" s="80" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E30="",F30=""),"",(E30-F30)/E30)</f>
         <v/>
       </c>
       <c r="H30" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(F30="","",IF(F30&lt;200,"JA",IF(E30="","zonder zool ontbreekt",IF((E30-F30)/E30&gt;=0.25,"JA","NEE"))))</f>
+        <v/>
+      </c>
+      <c r="I30" s="76" t="str">
+        <f>IF(OR(D30="",F30=""),"",IF((F30-D30)/D30&gt;=0.05,"JA","nee"))</f>
         <v/>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="74" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B31" s="76"/>
       <c r="D31" s="76"/>
       <c r="E31" s="76"/>
       <c r="F31" s="76"/>
       <c r="G31" s="80" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E31="",F31=""),"",(E31-F31)/E31)</f>
         <v/>
       </c>
       <c r="H31" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(F31="","",IF(F31&lt;200,"JA",IF(E31="","zonder zool ontbreekt",IF((E31-F31)/E31&gt;=0.25,"JA","NEE"))))</f>
+        <v/>
+      </c>
+      <c r="I31" s="76" t="str">
+        <f>IF(OR(D31="",F31=""),"",IF((F31-D31)/D31&gt;=0.05,"JA","nee"))</f>
         <v/>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="74" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B32" s="76"/>
       <c r="D32" s="76"/>
       <c r="E32" s="76"/>
       <c r="F32" s="76"/>
       <c r="G32" s="80" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E32="",F32=""),"",(E32-F32)/E32)</f>
         <v/>
       </c>
       <c r="H32" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(F32="","",IF(F32&lt;200,"JA",IF(E32="","zonder zool ontbreekt",IF((E32-F32)/E32&gt;=0.25,"JA","NEE"))))</f>
+        <v/>
+      </c>
+      <c r="I32" s="76" t="str">
+        <f>IF(OR(D32="",F32=""),"",IF((F32-D32)/D32&gt;=0.05,"JA","nee"))</f>
         <v/>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="74" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B33" s="76"/>
       <c r="D33" s="76"/>
       <c r="E33" s="76"/>
       <c r="F33" s="76"/>
       <c r="G33" s="80" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E33="",F33=""),"",(E33-F33)/E33)</f>
         <v/>
       </c>
       <c r="H33" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(F33="","",IF(F33&lt;200,"JA",IF(E33="","zonder zool ontbreekt",IF((E33-F33)/E33&gt;=0.25,"JA","NEE"))))</f>
+        <v/>
+      </c>
+      <c r="I33" s="76" t="str">
+        <f>IF(OR(D33="",F33=""),"",IF((F33-D33)/D33&gt;=0.05,"JA","nee"))</f>
         <v/>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="74" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B34" s="76"/>
       <c r="D34" s="76"/>
       <c r="E34" s="76"/>
       <c r="F34" s="76"/>
       <c r="G34" s="80" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E34="",F34=""),"",(E34-F34)/E34)</f>
         <v/>
       </c>
       <c r="H34" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(F34="","",IF(F34&lt;200,"JA",IF(E34="","zonder zool ontbreekt",IF((E34-F34)/E34&gt;=0.25,"JA","NEE"))))</f>
+        <v/>
+      </c>
+      <c r="I34" s="76" t="str">
+        <f>IF(OR(D34="",F34=""),"",IF((F34-D34)/D34&gt;=0.05,"JA","nee"))</f>
         <v/>
       </c>
     </row>
     <row r="35" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="84" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="B35" s="84"/>
       <c r="C35" s="84"/>
@@ -8361,17 +8624,17 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="73" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="72" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="72" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="39.5" x14ac:dyDescent="0.35">
@@ -8379,33 +8642,33 @@
         <v>56</v>
       </c>
       <c r="B40" s="81" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="C40" s="81" t="s">
-        <v>69</v>
-      </c>
       <c r="D40" s="81" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E40" s="81" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F40" s="81" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" s="81" t="s">
+        <v>102</v>
+      </c>
+      <c r="H40" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="G40" s="81" t="s">
-        <v>77</v>
-      </c>
-      <c r="H40" s="81" t="s">
-        <v>59</v>
-      </c>
       <c r="I40" s="81" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="74" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B41" s="76"/>
       <c r="C41" s="76"/>
@@ -8413,18 +8676,21 @@
       <c r="E41" s="76"/>
       <c r="F41" s="76"/>
       <c r="G41" s="80" t="str">
-        <f t="shared" ref="G41:G46" si="2">IF(OR(D41="",F41=""),"",(D41-F41)/D41)</f>
+        <f>IF(OR(E41="",F41=""),"",(E41-F41)/E41)</f>
         <v/>
       </c>
       <c r="H41" s="12" t="str">
-        <f t="shared" ref="H41:H46" si="3">IF(F41="","",IF(F41&lt;200,"JA",IF(D41="","referentie ontbreekt",IF((D41-F41)/D41&gt;=0.25,"JA","NEE"))))</f>
-        <v/>
-      </c>
-      <c r="I41" s="76"/>
+        <f>IF(F41="","",IF(F41&lt;200,"JA",IF(E41="","zonder zool ontbreekt",IF((E41-F41)/E41&gt;=0.25,"JA","NEE"))))</f>
+        <v/>
+      </c>
+      <c r="I41" s="76" t="str">
+        <f>IF(OR(D41="",F41=""),"",IF((F41-D41)/D41&gt;=0.05,"JA","nee"))</f>
+        <v/>
+      </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="74" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B42" s="76"/>
       <c r="C42" s="76"/>
@@ -8432,18 +8698,21 @@
       <c r="E42" s="76"/>
       <c r="F42" s="76"/>
       <c r="G42" s="80" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E42="",F42=""),"",(E42-F42)/E42)</f>
         <v/>
       </c>
       <c r="H42" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I42" s="76"/>
+        <f>IF(F42="","",IF(F42&lt;200,"JA",IF(E42="","zonder zool ontbreekt",IF((E42-F42)/E42&gt;=0.25,"JA","NEE"))))</f>
+        <v/>
+      </c>
+      <c r="I42" s="76" t="str">
+        <f>IF(OR(D42="",F42=""),"",IF((F42-D42)/D42&gt;=0.05,"JA","nee"))</f>
+        <v/>
+      </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="74" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B43" s="76"/>
       <c r="C43" s="76"/>
@@ -8451,18 +8720,21 @@
       <c r="E43" s="76"/>
       <c r="F43" s="76"/>
       <c r="G43" s="80" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E43="",F43=""),"",(E43-F43)/E43)</f>
         <v/>
       </c>
       <c r="H43" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I43" s="76"/>
+        <f>IF(F43="","",IF(F43&lt;200,"JA",IF(E43="","zonder zool ontbreekt",IF((E43-F43)/E43&gt;=0.25,"JA","NEE"))))</f>
+        <v/>
+      </c>
+      <c r="I43" s="76" t="str">
+        <f>IF(OR(D43="",F43=""),"",IF((F43-D43)/D43&gt;=0.05,"JA","nee"))</f>
+        <v/>
+      </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="74" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B44" s="76"/>
       <c r="C44" s="76"/>
@@ -8470,18 +8742,21 @@
       <c r="E44" s="76"/>
       <c r="F44" s="76"/>
       <c r="G44" s="80" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E44="",F44=""),"",(E44-F44)/E44)</f>
         <v/>
       </c>
       <c r="H44" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I44" s="76"/>
+        <f>IF(F44="","",IF(F44&lt;200,"JA",IF(E44="","zonder zool ontbreekt",IF((E44-F44)/E44&gt;=0.25,"JA","NEE"))))</f>
+        <v/>
+      </c>
+      <c r="I44" s="76" t="str">
+        <f>IF(OR(D44="",F44=""),"",IF((F44-D44)/D44&gt;=0.05,"JA","nee"))</f>
+        <v/>
+      </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="74" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B45" s="76"/>
       <c r="C45" s="76"/>
@@ -8489,18 +8764,21 @@
       <c r="E45" s="76"/>
       <c r="F45" s="76"/>
       <c r="G45" s="80" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E45="",F45=""),"",(E45-F45)/E45)</f>
         <v/>
       </c>
       <c r="H45" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I45" s="76"/>
+        <f>IF(F45="","",IF(F45&lt;200,"JA",IF(E45="","zonder zool ontbreekt",IF((E45-F45)/E45&gt;=0.25,"JA","NEE"))))</f>
+        <v/>
+      </c>
+      <c r="I45" s="76" t="str">
+        <f>IF(OR(D45="",F45=""),"",IF((F45-D45)/D45&gt;=0.05,"JA","nee"))</f>
+        <v/>
+      </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="74" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B46" s="76"/>
       <c r="C46" s="76"/>
@@ -8508,28 +8786,31 @@
       <c r="E46" s="76"/>
       <c r="F46" s="76"/>
       <c r="G46" s="80" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E46="",F46=""),"",(E46-F46)/E46)</f>
         <v/>
       </c>
       <c r="H46" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I46" s="76"/>
+        <f>IF(F46="","",IF(F46&lt;200,"JA",IF(E46="","zonder zool ontbreekt",IF((E46-F46)/E46&gt;=0.25,"JA","NEE"))))</f>
+        <v/>
+      </c>
+      <c r="I46" s="76" t="str">
+        <f>IF(OR(D46="",F46=""),"",IF((F46-D46)/D46&gt;=0.05,"JA","nee"))</f>
+        <v/>
+      </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="78" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="73" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="72" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
@@ -8702,12 +8983,13 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="75" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A4:I4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8719,7 +9001,7 @@
     <tabColor rgb="FF1A4F9C"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CT85"/>
+  <dimension ref="A1:CX85"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" customWidth="1"/>
@@ -8730,16 +9012,16 @@
     <col min="7" max="7" width="12.1796875" style="4" customWidth="1"/>
     <col min="8" max="8" width="12.1796875" customWidth="1"/>
     <col min="9" max="11" width="12.1796875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="12.1796875" customWidth="1"/>
-    <col min="13" max="13" width="3" customWidth="1"/>
-    <col min="14" max="20" width="12.1796875" customWidth="1"/>
-    <col min="21" max="21" width="8.81640625" style="7"/>
-    <col min="22" max="22" width="21" style="7" customWidth="1"/>
-    <col min="23" max="25" width="13.26953125" style="7" customWidth="1"/>
-    <col min="26" max="98" width="8.81640625" style="7"/>
+    <col min="12" max="14" width="12.1796875" customWidth="1"/>
+    <col min="15" max="15" width="3" customWidth="1"/>
+    <col min="16" max="24" width="12.1796875" customWidth="1"/>
+    <col min="25" max="25" width="8.81640625" style="7"/>
+    <col min="26" max="26" width="21" style="7" customWidth="1"/>
+    <col min="27" max="29" width="13.26953125" style="7" customWidth="1"/>
+    <col min="30" max="102" width="8.81640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:98" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:102" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="14"/>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -8760,56 +9042,64 @@
       <c r="R1" s="14"/>
       <c r="S1" s="14"/>
       <c r="T1" s="14"/>
-    </row>
-    <row r="2" spans="1:98" ht="34" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+    </row>
+    <row r="2" spans="1:102" ht="34" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
-      <c r="E2" s="101" t="s">
+      <c r="E2" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="86"/>
       <c r="O2" s="13"/>
       <c r="P2" s="13"/>
       <c r="Q2" s="13"/>
       <c r="R2" s="13"/>
       <c r="S2" s="13"/>
       <c r="T2" s="13"/>
-    </row>
-    <row r="3" spans="1:98" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U2" s="13"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="13"/>
+    </row>
+    <row r="3" spans="1:102" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
-      <c r="E3" s="103" t="s">
+      <c r="E3" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="86"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="86"/>
       <c r="O3" s="13"/>
       <c r="P3" s="13"/>
       <c r="Q3" s="13"/>
       <c r="R3" s="13"/>
       <c r="S3" s="13"/>
       <c r="T3" s="13"/>
-    </row>
-    <row r="4" spans="1:98" ht="4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+    </row>
+    <row r="4" spans="1:102" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="14"/>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -8830,26 +9120,30 @@
       <c r="R4" s="14"/>
       <c r="S4" s="14"/>
       <c r="T4" s="14"/>
-      <c r="V4" s="69" t="s">
+      <c r="U4" s="14"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="14"/>
+      <c r="X4" s="14"/>
+      <c r="Z4" s="69" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:98" x14ac:dyDescent="0.35">
-      <c r="U5" s="5"/>
-      <c r="X5" s="57" t="s">
+    <row r="5" spans="1:102" x14ac:dyDescent="0.35">
+      <c r="Y5" s="5"/>
+      <c r="AB5" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="Y5" s="56">
+      <c r="AC5" s="56">
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:98" ht="16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:102" ht="16" x14ac:dyDescent="0.35">
       <c r="A6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="105"/>
-      <c r="D6" s="106"/>
+      <c r="B6" s="90"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="92"/>
       <c r="E6" s="64"/>
       <c r="F6" s="64"/>
       <c r="G6" s="58" t="s">
@@ -8868,79 +9162,83 @@
       <c r="R6" s="66"/>
       <c r="S6" s="66"/>
       <c r="T6" s="66"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="68" t="s">
+      <c r="U6" s="66"/>
+      <c r="V6" s="66"/>
+      <c r="W6" s="66"/>
+      <c r="X6" s="66"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="W6" s="67"/>
-      <c r="X6" s="67"/>
-      <c r="Y6" s="67"/>
-    </row>
-    <row r="7" spans="1:98" ht="16" x14ac:dyDescent="0.4">
+      <c r="AA6" s="67"/>
+      <c r="AB6" s="67"/>
+      <c r="AC6" s="67"/>
+    </row>
+    <row r="7" spans="1:102" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="16"/>
       <c r="E7" s="15"/>
       <c r="F7" s="15"/>
       <c r="G7" s="17"/>
       <c r="H7" s="18"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="68" t="s">
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="W7" s="68" t="s">
+      <c r="AA7" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="X7" s="68" t="s">
+      <c r="AB7" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="Y7" s="68" t="s">
+      <c r="AC7" s="68" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:98" s="5" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:102" s="5" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8"/>
       <c r="B8"/>
       <c r="C8"/>
-      <c r="D8" s="98" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" s="99"/>
-      <c r="F8" s="99"/>
-      <c r="G8" s="99"/>
-      <c r="H8" s="99"/>
-      <c r="I8" s="99"/>
-      <c r="J8" s="99"/>
-      <c r="K8" s="99"/>
-      <c r="L8" s="100"/>
-      <c r="M8"/>
-      <c r="N8" s="98" t="s">
-        <v>81</v>
-      </c>
-      <c r="O8" s="99"/>
-      <c r="P8" s="99"/>
-      <c r="Q8" s="99"/>
-      <c r="R8" s="99"/>
-      <c r="S8" s="99"/>
-      <c r="T8" s="100"/>
-      <c r="V8" s="67" t="str">
-        <f t="shared" ref="V8:V15" si="0">C11</f>
+      <c r="D8" s="103" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8" s="104"/>
+      <c r="F8" s="104"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="104"/>
+      <c r="I8" s="104"/>
+      <c r="J8" s="104"/>
+      <c r="K8" s="104"/>
+      <c r="L8" s="104"/>
+      <c r="M8" s="104"/>
+      <c r="N8" s="104"/>
+      <c r="O8"/>
+      <c r="P8" s="103" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q8" s="104"/>
+      <c r="R8" s="104"/>
+      <c r="S8" s="104"/>
+      <c r="T8" s="104"/>
+      <c r="U8" s="104"/>
+      <c r="V8" s="104"/>
+      <c r="W8" s="104"/>
+      <c r="X8" s="104"/>
+      <c r="Z8" s="67" t="str">
+        <f t="shared" ref="Z8:Z15" si="0">C11</f>
         <v>I_Links Hallux</v>
       </c>
-      <c r="W8" s="67" t="str">
-        <f t="shared" ref="W8:W15" si="1">E11</f>
-        <v/>
-      </c>
-      <c r="X8" s="67" t="str">
-        <f t="shared" ref="X8:X15" si="2">G11</f>
-        <v/>
-      </c>
-      <c r="Y8" s="67">
-        <f t="shared" ref="Y8:Y15" si="3">$Y$5</f>
+      <c r="AA8" s="67" t="str">
+        <f t="shared" ref="AA8:AA15" si="1">E11</f>
+        <v/>
+      </c>
+      <c r="AB8" s="67" t="str">
+        <f t="shared" ref="AB8:AB15" si="2">G11</f>
+        <v/>
+      </c>
+      <c r="AC8" s="67">
+        <f t="shared" ref="AC8:AC15" si="3">$AC$5</f>
         <v>200</v>
       </c>
-      <c r="Z8" s="7"/>
-      <c r="AA8" s="7"/>
-      <c r="AB8" s="7"/>
-      <c r="AC8" s="7"/>
       <c r="AD8" s="7"/>
       <c r="AE8" s="7"/>
       <c r="AF8" s="7"/>
@@ -9010,12 +9308,16 @@
       <c r="CR8" s="7"/>
       <c r="CS8" s="7"/>
       <c r="CT8" s="7"/>
-    </row>
-    <row r="9" spans="1:98" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="92" t="s">
+      <c r="CU8" s="7"/>
+      <c r="CV8" s="7"/>
+      <c r="CW8" s="7"/>
+      <c r="CX8" s="7"/>
+    </row>
+    <row r="9" spans="1:102" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="93"/>
+      <c r="B9" s="94"/>
       <c r="C9" s="34"/>
       <c r="D9" s="35"/>
       <c r="E9" s="60" t="s">
@@ -9024,54 +9326,58 @@
       <c r="F9" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="85" t="s">
+      <c r="G9" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="86"/>
-      <c r="I9" s="85" t="s">
+      <c r="H9" s="89"/>
+      <c r="I9" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="86"/>
-      <c r="K9" s="85" t="s">
+      <c r="J9" s="89"/>
+      <c r="K9" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="L9" s="86"/>
-      <c r="M9" s="62"/>
-      <c r="N9" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="O9" s="85" t="s">
+      <c r="L9" s="89"/>
+      <c r="M9" s="88" t="s">
+        <v>107</v>
+      </c>
+      <c r="N9" s="89"/>
+      <c r="O9" s="62"/>
+      <c r="P9" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q9" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="P9" s="86"/>
-      <c r="Q9" s="85" t="s">
+      <c r="R9" s="89"/>
+      <c r="S9" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="R9" s="86"/>
-      <c r="S9" s="85" t="s">
+      <c r="T9" s="89"/>
+      <c r="U9" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="T9" s="86"/>
-      <c r="V9" s="67" t="str">
+      <c r="V9" s="89"/>
+      <c r="W9" s="88" t="s">
+        <v>107</v>
+      </c>
+      <c r="X9" s="89"/>
+      <c r="Z9" s="67" t="str">
         <f t="shared" si="0"/>
         <v>J_Links Tenen 2-5</v>
       </c>
-      <c r="W9" s="67" t="str">
+      <c r="AA9" s="67" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X9" s="67" t="str">
+      <c r="AB9" s="67" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y9" s="67">
+      <c r="AC9" s="67">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="Z9" s="7"/>
-      <c r="AA9" s="7"/>
-      <c r="AB9" s="7"/>
-      <c r="AC9" s="7"/>
       <c r="AD9" s="7"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="7"/>
@@ -9141,17 +9447,21 @@
       <c r="CR9" s="7"/>
       <c r="CS9" s="7"/>
       <c r="CT9" s="7"/>
-    </row>
-    <row r="10" spans="1:98" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.35">
-      <c r="A10" s="94"/>
-      <c r="B10" s="95"/>
+      <c r="CU9" s="7"/>
+      <c r="CV9" s="7"/>
+      <c r="CW9" s="7"/>
+      <c r="CX9" s="7"/>
+    </row>
+    <row r="10" spans="1:102" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.35">
+      <c r="A10" s="95"/>
+      <c r="B10" s="96"/>
       <c r="C10" s="34"/>
       <c r="D10" s="35"/>
       <c r="E10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="G10" s="36" t="s">
         <v>1</v>
@@ -9171,48 +9481,56 @@
       <c r="L10" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="M10" s="62"/>
+      <c r="M10" s="36" t="s">
+        <v>1</v>
+      </c>
       <c r="N10" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="O10" s="62"/>
+      <c r="P10" s="36" t="s">
         <v>1</v>
-      </c>
-      <c r="O10" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="P10" s="36" t="s">
-        <v>83</v>
       </c>
       <c r="Q10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="R10" s="36" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="S10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="T10" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="V10" s="67" t="str">
+        <v>109</v>
+      </c>
+      <c r="U10" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="V10" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="W10" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="X10" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z10" s="67" t="str">
         <f t="shared" si="0"/>
         <v>K_Links Metatarsaal 1</v>
       </c>
-      <c r="W10" s="67" t="str">
+      <c r="AA10" s="67" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X10" s="67" t="str">
+      <c r="AB10" s="67" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y10" s="67">
+      <c r="AC10" s="67">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="Z10" s="7"/>
-      <c r="AA10" s="7"/>
-      <c r="AB10" s="7"/>
-      <c r="AC10" s="7"/>
       <c r="AD10" s="7"/>
       <c r="AE10" s="7"/>
       <c r="AF10" s="7"/>
@@ -9282,12 +9600,16 @@
       <c r="CR10" s="7"/>
       <c r="CS10" s="7"/>
       <c r="CT10" s="7"/>
-    </row>
-    <row r="11" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="94"/>
-      <c r="B11" s="95"/>
+      <c r="CU10" s="7"/>
+      <c r="CV10" s="7"/>
+      <c r="CW10" s="7"/>
+      <c r="CX10" s="7"/>
+    </row>
+    <row r="11" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="95"/>
+      <c r="B11" s="96"/>
       <c r="C11" s="83" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D11" s="37"/>
       <c r="E11" s="38" t="str">
@@ -9316,46 +9638,49 @@
         <f t="shared" ref="L11:L18" si="9">IF(OR($E11="",K11=""),"",((K11-$E11)/$E11)*100)</f>
         <v/>
       </c>
-      <c r="M11" s="33"/>
-      <c r="N11" s="40" t="str">
-        <f t="shared" ref="N11:N18" si="10">IF(E11="","",E11)</f>
-        <v/>
-      </c>
-      <c r="O11" s="40"/>
-      <c r="P11" s="43" t="str">
-        <f t="shared" ref="P11:P18" si="11">IF(OR($N11="",O11=""),"",((O11-$N11)/$N11)*100)</f>
-        <v/>
-      </c>
+      <c r="M11" s="40"/>
+      <c r="N11" s="43" t="str">
+        <f t="shared" ref="N11:N18" si="10">IF(OR($E11="",M11=""),"",((M11-$E11)/$E11)*100)</f>
+        <v/>
+      </c>
+      <c r="O11" s="33"/>
+      <c r="P11" s="40"/>
       <c r="Q11" s="40"/>
       <c r="R11" s="43" t="str">
-        <f t="shared" ref="R11:R18" si="12">IF(OR($N11="",Q11=""),"",((Q11-$N11)/$N11)*100)</f>
+        <f t="shared" ref="R11:R18" si="11">IF(OR($P11="",Q11=""),"",((Q11-$P11)/$P11)*100)</f>
         <v/>
       </c>
       <c r="S11" s="40"/>
       <c r="T11" s="43" t="str">
-        <f t="shared" ref="T11:T18" si="13">IF(OR($N11="",S11=""),"",((S11-$N11)/$N11)*100)</f>
-        <v/>
-      </c>
-      <c r="V11" s="67" t="str">
+        <f t="shared" ref="T11:T18" si="12">IF(OR($P11="",S11=""),"",((S11-$P11)/$P11)*100)</f>
+        <v/>
+      </c>
+      <c r="U11" s="40"/>
+      <c r="V11" s="43" t="str">
+        <f t="shared" ref="V11:V18" si="13">IF(OR($P11="",U11=""),"",((U11-$P11)/$P11)*100)</f>
+        <v/>
+      </c>
+      <c r="W11" s="40"/>
+      <c r="X11" s="43" t="str">
+        <f t="shared" ref="X11:X18" si="14">IF(OR($P11="",W11=""),"",((W11-$P11)/$P11)*100)</f>
+        <v/>
+      </c>
+      <c r="Z11" s="67" t="str">
         <f t="shared" si="0"/>
         <v>L_Links Metatarsaal 2-3</v>
       </c>
-      <c r="W11" s="67" t="str">
+      <c r="AA11" s="67" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X11" s="67" t="str">
+      <c r="AB11" s="67" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y11" s="67">
+      <c r="AC11" s="67">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="Z11" s="7"/>
-      <c r="AA11" s="7"/>
-      <c r="AB11" s="7"/>
-      <c r="AC11" s="7"/>
       <c r="AD11" s="7"/>
       <c r="AE11" s="7"/>
       <c r="AF11" s="7"/>
@@ -9425,12 +9750,16 @@
       <c r="CR11" s="7"/>
       <c r="CS11" s="7"/>
       <c r="CT11" s="7"/>
-    </row>
-    <row r="12" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94"/>
-      <c r="B12" s="95"/>
+      <c r="CU11" s="7"/>
+      <c r="CV11" s="7"/>
+      <c r="CW11" s="7"/>
+      <c r="CX11" s="7"/>
+    </row>
+    <row r="12" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="95"/>
+      <c r="B12" s="96"/>
       <c r="C12" s="83" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D12" s="37"/>
       <c r="E12" s="38" t="str">
@@ -9459,46 +9788,49 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="M12" s="33"/>
-      <c r="N12" s="40" t="str">
+      <c r="M12" s="40"/>
+      <c r="N12" s="43" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O12" s="40"/>
-      <c r="P12" s="43" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
+      <c r="O12" s="33"/>
+      <c r="P12" s="40"/>
       <c r="Q12" s="40"/>
       <c r="R12" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S12" s="40"/>
       <c r="T12" s="43" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="U12" s="40"/>
+      <c r="V12" s="43" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="V12" s="67" t="str">
+      <c r="W12" s="40"/>
+      <c r="X12" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z12" s="67" t="str">
         <f t="shared" si="0"/>
         <v>M_Links Metatarsaal 4-5</v>
       </c>
-      <c r="W12" s="67" t="str">
+      <c r="AA12" s="67" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X12" s="67" t="str">
+      <c r="AB12" s="67" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y12" s="67">
+      <c r="AC12" s="67">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="Z12" s="7"/>
-      <c r="AA12" s="7"/>
-      <c r="AB12" s="7"/>
-      <c r="AC12" s="7"/>
       <c r="AD12" s="7"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="7"/>
@@ -9568,12 +9900,16 @@
       <c r="CR12" s="7"/>
       <c r="CS12" s="7"/>
       <c r="CT12" s="7"/>
-    </row>
-    <row r="13" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="94"/>
-      <c r="B13" s="95"/>
+      <c r="CU12" s="7"/>
+      <c r="CV12" s="7"/>
+      <c r="CW12" s="7"/>
+      <c r="CX12" s="7"/>
+    </row>
+    <row r="13" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="95"/>
+      <c r="B13" s="96"/>
       <c r="C13" s="83" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="38" t="str">
@@ -9602,46 +9938,49 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="M13" s="33"/>
-      <c r="N13" s="40" t="str">
+      <c r="M13" s="40"/>
+      <c r="N13" s="43" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O13" s="40"/>
-      <c r="P13" s="43" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
+      <c r="O13" s="33"/>
+      <c r="P13" s="40"/>
       <c r="Q13" s="40"/>
       <c r="R13" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S13" s="40"/>
       <c r="T13" s="43" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="U13" s="40"/>
+      <c r="V13" s="43" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="V13" s="67" t="str">
+      <c r="W13" s="40"/>
+      <c r="X13" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z13" s="67" t="str">
         <f t="shared" si="0"/>
         <v>N_Links Mediale middenvoet</v>
       </c>
-      <c r="W13" s="67" t="str">
+      <c r="AA13" s="67" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X13" s="67" t="str">
+      <c r="AB13" s="67" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y13" s="67">
+      <c r="AC13" s="67">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="Z13" s="7"/>
-      <c r="AA13" s="7"/>
-      <c r="AB13" s="7"/>
-      <c r="AC13" s="7"/>
       <c r="AD13" s="7"/>
       <c r="AE13" s="7"/>
       <c r="AF13" s="7"/>
@@ -9711,12 +10050,16 @@
       <c r="CR13" s="7"/>
       <c r="CS13" s="7"/>
       <c r="CT13" s="7"/>
-    </row>
-    <row r="14" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="94"/>
-      <c r="B14" s="95"/>
+      <c r="CU13" s="7"/>
+      <c r="CV13" s="7"/>
+      <c r="CW13" s="7"/>
+      <c r="CX13" s="7"/>
+    </row>
+    <row r="14" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="95"/>
+      <c r="B14" s="96"/>
       <c r="C14" s="83" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="38" t="str">
@@ -9745,46 +10088,49 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="M14" s="33"/>
-      <c r="N14" s="40" t="str">
+      <c r="M14" s="40"/>
+      <c r="N14" s="43" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O14" s="40"/>
-      <c r="P14" s="43" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
+      <c r="O14" s="33"/>
+      <c r="P14" s="40"/>
       <c r="Q14" s="40"/>
       <c r="R14" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S14" s="40"/>
       <c r="T14" s="43" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="U14" s="40"/>
+      <c r="V14" s="43" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="V14" s="67" t="str">
+      <c r="W14" s="40"/>
+      <c r="X14" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z14" s="67" t="str">
         <f t="shared" si="0"/>
         <v>O_Links Laterale middenvoet</v>
       </c>
-      <c r="W14" s="67" t="str">
+      <c r="AA14" s="67" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X14" s="67" t="str">
+      <c r="AB14" s="67" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y14" s="67">
+      <c r="AC14" s="67">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="Z14" s="7"/>
-      <c r="AA14" s="7"/>
-      <c r="AB14" s="7"/>
-      <c r="AC14" s="7"/>
       <c r="AD14" s="7"/>
       <c r="AE14" s="7"/>
       <c r="AF14" s="7"/>
@@ -9854,12 +10200,16 @@
       <c r="CR14" s="7"/>
       <c r="CS14" s="7"/>
       <c r="CT14" s="7"/>
-    </row>
-    <row r="15" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="94"/>
-      <c r="B15" s="95"/>
+      <c r="CU14" s="7"/>
+      <c r="CV14" s="7"/>
+      <c r="CW14" s="7"/>
+      <c r="CX14" s="7"/>
+    </row>
+    <row r="15" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="95"/>
+      <c r="B15" s="96"/>
       <c r="C15" s="83" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="38" t="str">
@@ -9888,46 +10238,49 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="M15" s="33"/>
-      <c r="N15" s="40" t="str">
+      <c r="M15" s="40"/>
+      <c r="N15" s="43" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O15" s="40"/>
-      <c r="P15" s="43" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
+      <c r="O15" s="33"/>
+      <c r="P15" s="40"/>
       <c r="Q15" s="40"/>
       <c r="R15" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S15" s="40"/>
       <c r="T15" s="43" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="U15" s="40"/>
+      <c r="V15" s="43" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="V15" s="67" t="str">
+      <c r="W15" s="40"/>
+      <c r="X15" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z15" s="67" t="str">
         <f t="shared" si="0"/>
         <v>P_Links Hiel</v>
       </c>
-      <c r="W15" s="67" t="str">
+      <c r="AA15" s="67" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X15" s="67" t="str">
+      <c r="AB15" s="67" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y15" s="67">
+      <c r="AC15" s="67">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="Z15" s="7"/>
-      <c r="AA15" s="7"/>
-      <c r="AB15" s="7"/>
-      <c r="AC15" s="7"/>
       <c r="AD15" s="7"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="7"/>
@@ -9997,12 +10350,16 @@
       <c r="CR15" s="7"/>
       <c r="CS15" s="7"/>
       <c r="CT15" s="7"/>
-    </row>
-    <row r="16" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="94"/>
-      <c r="B16" s="95"/>
+      <c r="CU15" s="7"/>
+      <c r="CV15" s="7"/>
+      <c r="CW15" s="7"/>
+      <c r="CX15" s="7"/>
+    </row>
+    <row r="16" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="95"/>
+      <c r="B16" s="96"/>
       <c r="C16" s="83" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="41" t="str">
@@ -10031,34 +10388,37 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="M16" s="33"/>
-      <c r="N16" s="40" t="str">
+      <c r="M16" s="40"/>
+      <c r="N16" s="43" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O16" s="40"/>
-      <c r="P16" s="43" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
+      <c r="O16" s="33"/>
+      <c r="P16" s="40"/>
       <c r="Q16" s="40"/>
       <c r="R16" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S16" s="40"/>
       <c r="T16" s="43" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="U16" s="40"/>
+      <c r="V16" s="43" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="V16" s="67"/>
-      <c r="W16" s="67"/>
-      <c r="X16" s="67"/>
-      <c r="Y16" s="67"/>
-      <c r="Z16" s="7"/>
-      <c r="AA16" s="7"/>
-      <c r="AB16" s="7"/>
-      <c r="AC16" s="7"/>
+      <c r="W16" s="40"/>
+      <c r="X16" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z16" s="67"/>
+      <c r="AA16" s="67"/>
+      <c r="AB16" s="67"/>
+      <c r="AC16" s="67"/>
       <c r="AD16" s="7"/>
       <c r="AE16" s="7"/>
       <c r="AF16" s="7"/>
@@ -10128,12 +10488,16 @@
       <c r="CR16" s="7"/>
       <c r="CS16" s="7"/>
       <c r="CT16" s="7"/>
-    </row>
-    <row r="17" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="94"/>
-      <c r="B17" s="95"/>
+      <c r="CU16" s="7"/>
+      <c r="CV16" s="7"/>
+      <c r="CW16" s="7"/>
+      <c r="CX16" s="7"/>
+    </row>
+    <row r="17" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="95"/>
+      <c r="B17" s="96"/>
       <c r="C17" s="83" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="41" t="str">
@@ -10162,34 +10526,37 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="M17" s="33"/>
-      <c r="N17" s="40" t="str">
+      <c r="M17" s="40"/>
+      <c r="N17" s="43" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O17" s="40"/>
-      <c r="P17" s="43" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
+      <c r="O17" s="33"/>
+      <c r="P17" s="40"/>
       <c r="Q17" s="40"/>
       <c r="R17" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S17" s="40"/>
       <c r="T17" s="43" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="U17" s="40"/>
+      <c r="V17" s="43" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="V17" s="67"/>
-      <c r="W17" s="67"/>
-      <c r="X17" s="67"/>
-      <c r="Y17" s="67"/>
-      <c r="Z17" s="7"/>
-      <c r="AA17" s="7"/>
-      <c r="AB17" s="7"/>
-      <c r="AC17" s="7"/>
+      <c r="W17" s="40"/>
+      <c r="X17" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z17" s="67"/>
+      <c r="AA17" s="67"/>
+      <c r="AB17" s="67"/>
+      <c r="AC17" s="67"/>
       <c r="AD17" s="7"/>
       <c r="AE17" s="7"/>
       <c r="AF17" s="7"/>
@@ -10259,12 +10626,16 @@
       <c r="CR17" s="7"/>
       <c r="CS17" s="7"/>
       <c r="CT17" s="7"/>
-    </row>
-    <row r="18" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="96"/>
-      <c r="B18" s="97"/>
+      <c r="CU17" s="7"/>
+      <c r="CV17" s="7"/>
+      <c r="CW17" s="7"/>
+      <c r="CX17" s="7"/>
+    </row>
+    <row r="18" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="97"/>
+      <c r="B18" s="98"/>
       <c r="C18" s="83" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D18" s="37"/>
       <c r="E18" s="41" t="str">
@@ -10293,36 +10664,39 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="M18" s="33"/>
-      <c r="N18" s="40" t="str">
+      <c r="M18" s="40"/>
+      <c r="N18" s="43" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O18" s="40"/>
-      <c r="P18" s="43" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
+      <c r="O18" s="33"/>
+      <c r="P18" s="40"/>
       <c r="Q18" s="40"/>
       <c r="R18" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S18" s="40"/>
       <c r="T18" s="43" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="U18" s="40"/>
+      <c r="V18" s="43" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="V18" s="68" t="s">
+      <c r="W18" s="40"/>
+      <c r="X18" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z18" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="W18" s="67"/>
-      <c r="X18" s="67"/>
-      <c r="Y18" s="67"/>
-      <c r="Z18" s="7"/>
-      <c r="AA18" s="7"/>
-      <c r="AB18" s="7"/>
-      <c r="AC18" s="7"/>
+      <c r="AA18" s="67"/>
+      <c r="AB18" s="67"/>
+      <c r="AC18" s="67"/>
       <c r="AD18" s="7"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="7"/>
@@ -10392,8 +10766,12 @@
       <c r="CR18" s="7"/>
       <c r="CS18" s="7"/>
       <c r="CT18" s="7"/>
-    </row>
-    <row r="19" spans="1:98" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="CU18" s="7"/>
+      <c r="CV18" s="7"/>
+      <c r="CW18" s="7"/>
+      <c r="CX18" s="7"/>
+    </row>
+    <row r="19" spans="1:102" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="21"/>
       <c r="B19" s="21"/>
       <c r="C19" s="48"/>
@@ -10406,30 +10784,30 @@
       <c r="J19" s="26"/>
       <c r="K19" s="26"/>
       <c r="L19" s="25"/>
-      <c r="M19" s="27"/>
-      <c r="N19" s="27"/>
+      <c r="M19" s="102"/>
+      <c r="N19" s="102"/>
       <c r="O19" s="27"/>
       <c r="P19" s="27"/>
       <c r="Q19" s="27"/>
       <c r="R19" s="27"/>
       <c r="S19" s="27"/>
-      <c r="T19" s="42"/>
-      <c r="V19" s="68" t="s">
+      <c r="T19" s="27"/>
+      <c r="U19" s="27"/>
+      <c r="V19" s="42"/>
+      <c r="W19" s="102"/>
+      <c r="X19" s="102"/>
+      <c r="Z19" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="W19" s="68" t="s">
+      <c r="AA19" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="X19" s="68" t="s">
+      <c r="AB19" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="Y19" s="68" t="s">
+      <c r="AC19" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="3"/>
-      <c r="AB19" s="3"/>
-      <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
@@ -10499,50 +10877,54 @@
       <c r="CR19" s="3"/>
       <c r="CS19" s="3"/>
       <c r="CT19" s="3"/>
-    </row>
-    <row r="20" spans="1:98" s="5" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="87" t="s">
-        <v>85</v>
-      </c>
-      <c r="B20" s="88"/>
-      <c r="C20" s="89"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="90"/>
-      <c r="G20" s="90"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="90"/>
-      <c r="J20" s="90"/>
-      <c r="K20" s="90"/>
-      <c r="L20" s="90"/>
-      <c r="M20" s="90"/>
-      <c r="N20" s="90"/>
-      <c r="O20" s="90"/>
-      <c r="P20" s="90"/>
-      <c r="Q20" s="90"/>
-      <c r="R20" s="90"/>
-      <c r="S20" s="90"/>
-      <c r="T20" s="90"/>
-      <c r="V20" s="67" t="str">
-        <f t="shared" ref="V20:V27" si="14">C27</f>
+      <c r="CU19" s="3"/>
+      <c r="CV19" s="3"/>
+      <c r="CW19" s="3"/>
+      <c r="CX19" s="3"/>
+    </row>
+    <row r="20" spans="1:102" s="5" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="100"/>
+      <c r="C20" s="106"/>
+      <c r="D20" s="107"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="107"/>
+      <c r="H20" s="107"/>
+      <c r="I20" s="107"/>
+      <c r="J20" s="107"/>
+      <c r="K20" s="107"/>
+      <c r="L20" s="107"/>
+      <c r="M20" s="107"/>
+      <c r="N20" s="107"/>
+      <c r="O20" s="107"/>
+      <c r="P20" s="107"/>
+      <c r="Q20" s="107"/>
+      <c r="R20" s="107"/>
+      <c r="S20" s="107"/>
+      <c r="T20" s="107"/>
+      <c r="U20" s="107"/>
+      <c r="V20" s="107"/>
+      <c r="W20" s="107"/>
+      <c r="X20" s="107"/>
+      <c r="Z20" s="67" t="str">
+        <f t="shared" ref="Z20:Z27" si="15">C27</f>
         <v>A_Rechts Hallux</v>
       </c>
-      <c r="W20" s="67" t="str">
-        <f t="shared" ref="W20:W27" si="15">E27</f>
-        <v/>
-      </c>
-      <c r="X20" s="67" t="str">
-        <f t="shared" ref="X20:X27" si="16">G27</f>
-        <v/>
-      </c>
-      <c r="Y20" s="67">
-        <f t="shared" ref="Y20:Y27" si="17">$Y$5</f>
+      <c r="AA20" s="67" t="str">
+        <f t="shared" ref="AA20:AA27" si="16">E27</f>
+        <v/>
+      </c>
+      <c r="AB20" s="67" t="str">
+        <f t="shared" ref="AB20:AB27" si="17">G27</f>
+        <v/>
+      </c>
+      <c r="AC20" s="67">
+        <f t="shared" ref="AC20:AC27" si="18">$AC$5</f>
         <v>200</v>
       </c>
-      <c r="Z20" s="7"/>
-      <c r="AA20" s="7"/>
-      <c r="AB20" s="7"/>
-      <c r="AC20" s="7"/>
       <c r="AD20" s="7"/>
       <c r="AE20" s="7"/>
       <c r="AF20" s="7"/>
@@ -10612,8 +10994,12 @@
       <c r="CR20" s="7"/>
       <c r="CS20" s="7"/>
       <c r="CT20" s="7"/>
-    </row>
-    <row r="21" spans="1:98" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="CU20" s="7"/>
+      <c r="CV20" s="7"/>
+      <c r="CW20" s="7"/>
+      <c r="CX20" s="7"/>
+    </row>
+    <row r="21" spans="1:102" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="19"/>
       <c r="B21" s="19"/>
       <c r="C21" s="28"/>
@@ -10633,27 +11019,27 @@
       <c r="Q21" s="30"/>
       <c r="R21" s="30"/>
       <c r="S21" s="30"/>
-      <c r="T21" s="32"/>
-      <c r="V21" s="67" t="str">
-        <f t="shared" si="14"/>
+      <c r="T21" s="30"/>
+      <c r="U21" s="30"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="105"/>
+      <c r="X21" s="105"/>
+      <c r="Z21" s="67" t="str">
+        <f t="shared" si="15"/>
         <v>B_Rechts Tenen 2-5</v>
       </c>
-      <c r="W21" s="67" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="X21" s="67" t="str">
+      <c r="AA21" s="67" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Y21" s="67">
+      <c r="AB21" s="67" t="str">
         <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AC21" s="67">
+        <f t="shared" si="18"/>
         <v>200</v>
       </c>
-      <c r="Z21" s="7"/>
-      <c r="AA21" s="7"/>
-      <c r="AB21" s="7"/>
-      <c r="AC21" s="7"/>
       <c r="AD21" s="7"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="7"/>
@@ -10723,8 +11109,12 @@
       <c r="CR21" s="7"/>
       <c r="CS21" s="7"/>
       <c r="CT21" s="7"/>
-    </row>
-    <row r="22" spans="1:98" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="CU21" s="7"/>
+      <c r="CV21" s="7"/>
+      <c r="CW21" s="7"/>
+      <c r="CX21" s="7"/>
+    </row>
+    <row r="22" spans="1:102" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22"/>
@@ -10745,26 +11135,26 @@
       <c r="R22"/>
       <c r="S22"/>
       <c r="T22"/>
-      <c r="V22" s="67" t="str">
-        <f t="shared" si="14"/>
+      <c r="U22"/>
+      <c r="V22"/>
+      <c r="W22"/>
+      <c r="X22"/>
+      <c r="Z22" s="67" t="str">
+        <f t="shared" si="15"/>
         <v>C_Rechts Metatarsaal 1</v>
       </c>
-      <c r="W22" s="67" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="X22" s="67" t="str">
+      <c r="AA22" s="67" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Y22" s="67">
+      <c r="AB22" s="67" t="str">
         <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AC22" s="67">
+        <f t="shared" si="18"/>
         <v>200</v>
       </c>
-      <c r="Z22" s="7"/>
-      <c r="AA22" s="7"/>
-      <c r="AB22" s="7"/>
-      <c r="AC22" s="7"/>
       <c r="AD22" s="7"/>
       <c r="AE22" s="7"/>
       <c r="AF22" s="7"/>
@@ -10834,8 +11224,12 @@
       <c r="CR22" s="7"/>
       <c r="CS22" s="7"/>
       <c r="CT22" s="7"/>
-    </row>
-    <row r="23" spans="1:98" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="CU22" s="7"/>
+      <c r="CV22" s="7"/>
+      <c r="CW22" s="7"/>
+      <c r="CX22" s="7"/>
+    </row>
+    <row r="23" spans="1:102" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23"/>
       <c r="B23"/>
       <c r="C23"/>
@@ -10856,26 +11250,26 @@
       <c r="R23"/>
       <c r="S23"/>
       <c r="T23"/>
-      <c r="V23" s="67" t="str">
-        <f t="shared" si="14"/>
+      <c r="U23"/>
+      <c r="V23"/>
+      <c r="W23"/>
+      <c r="X23"/>
+      <c r="Z23" s="67" t="str">
+        <f t="shared" si="15"/>
         <v>D_Rechts Metatarsaal 2-3</v>
       </c>
-      <c r="W23" s="67" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="X23" s="67" t="str">
+      <c r="AA23" s="67" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Y23" s="67">
+      <c r="AB23" s="67" t="str">
         <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AC23" s="67">
+        <f t="shared" si="18"/>
         <v>200</v>
       </c>
-      <c r="Z23" s="7"/>
-      <c r="AA23" s="7"/>
-      <c r="AB23" s="7"/>
-      <c r="AC23" s="7"/>
       <c r="AD23" s="7"/>
       <c r="AE23" s="7"/>
       <c r="AF23" s="7"/>
@@ -10945,52 +11339,56 @@
       <c r="CR23" s="7"/>
       <c r="CS23" s="7"/>
       <c r="CT23" s="7"/>
-    </row>
-    <row r="24" spans="1:98" s="5" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="CU23" s="7"/>
+      <c r="CV23" s="7"/>
+      <c r="CW23" s="7"/>
+      <c r="CX23" s="7"/>
+    </row>
+    <row r="24" spans="1:102" s="5" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24"/>
       <c r="B24"/>
       <c r="C24"/>
-      <c r="D24" s="98" t="s">
-        <v>80</v>
-      </c>
-      <c r="E24" s="99"/>
-      <c r="F24" s="99"/>
-      <c r="G24" s="99"/>
-      <c r="H24" s="99"/>
-      <c r="I24" s="99"/>
-      <c r="J24" s="99"/>
-      <c r="K24" s="99"/>
-      <c r="L24" s="100"/>
-      <c r="M24"/>
-      <c r="N24" s="98" t="s">
-        <v>81</v>
-      </c>
-      <c r="O24" s="99"/>
-      <c r="P24" s="99"/>
-      <c r="Q24" s="99"/>
-      <c r="R24" s="99"/>
-      <c r="S24" s="99"/>
-      <c r="T24" s="100"/>
-      <c r="V24" s="67" t="str">
-        <f t="shared" si="14"/>
+      <c r="D24" s="103" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="104"/>
+      <c r="F24" s="104"/>
+      <c r="G24" s="104"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="104"/>
+      <c r="J24" s="104"/>
+      <c r="K24" s="104"/>
+      <c r="L24" s="104"/>
+      <c r="M24" s="104"/>
+      <c r="N24" s="104"/>
+      <c r="O24"/>
+      <c r="P24" s="103" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q24" s="104"/>
+      <c r="R24" s="104"/>
+      <c r="S24" s="104"/>
+      <c r="T24" s="104"/>
+      <c r="U24" s="104"/>
+      <c r="V24" s="104"/>
+      <c r="W24" s="104"/>
+      <c r="X24" s="104"/>
+      <c r="Z24" s="67" t="str">
+        <f t="shared" si="15"/>
         <v>E_Rechts Metatarsaal 4-5</v>
       </c>
-      <c r="W24" s="67" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="X24" s="67" t="str">
+      <c r="AA24" s="67" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Y24" s="67">
+      <c r="AB24" s="67" t="str">
         <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AC24" s="67">
+        <f t="shared" si="18"/>
         <v>200</v>
       </c>
-      <c r="Z24" s="7"/>
-      <c r="AA24" s="7"/>
-      <c r="AB24" s="7"/>
-      <c r="AC24" s="7"/>
       <c r="AD24" s="7"/>
       <c r="AE24" s="7"/>
       <c r="AF24" s="7"/>
@@ -11060,12 +11458,16 @@
       <c r="CR24" s="7"/>
       <c r="CS24" s="7"/>
       <c r="CT24" s="7"/>
-    </row>
-    <row r="25" spans="1:98" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="92" t="s">
+      <c r="CU24" s="7"/>
+      <c r="CV24" s="7"/>
+      <c r="CW24" s="7"/>
+      <c r="CX24" s="7"/>
+    </row>
+    <row r="25" spans="1:102" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="93"/>
+      <c r="B25" s="94"/>
       <c r="C25" s="34"/>
       <c r="D25" s="35"/>
       <c r="E25" s="60" t="s">
@@ -11074,54 +11476,58 @@
       <c r="F25" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="G25" s="85" t="s">
+      <c r="G25" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="86"/>
-      <c r="I25" s="85" t="s">
+      <c r="H25" s="89"/>
+      <c r="I25" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="J25" s="86"/>
-      <c r="K25" s="85" t="s">
+      <c r="J25" s="89"/>
+      <c r="K25" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="L25" s="86"/>
-      <c r="M25" s="62"/>
-      <c r="N25" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="O25" s="85" t="s">
+      <c r="L25" s="89"/>
+      <c r="M25" s="88" t="s">
+        <v>107</v>
+      </c>
+      <c r="N25" s="89"/>
+      <c r="O25" s="62"/>
+      <c r="P25" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q25" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="P25" s="86"/>
-      <c r="Q25" s="85" t="s">
+      <c r="R25" s="89"/>
+      <c r="S25" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="R25" s="86"/>
-      <c r="S25" s="85" t="s">
+      <c r="T25" s="89"/>
+      <c r="U25" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="T25" s="86"/>
-      <c r="V25" s="67" t="str">
-        <f t="shared" si="14"/>
+      <c r="V25" s="89"/>
+      <c r="W25" s="88" t="s">
+        <v>107</v>
+      </c>
+      <c r="X25" s="89"/>
+      <c r="Z25" s="67" t="str">
+        <f t="shared" si="15"/>
         <v>F_Rechts Mediale middenvoet</v>
       </c>
-      <c r="W25" s="67" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="X25" s="67" t="str">
+      <c r="AA25" s="67" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Y25" s="67">
+      <c r="AB25" s="67" t="str">
         <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AC25" s="67">
+        <f t="shared" si="18"/>
         <v>200</v>
       </c>
-      <c r="Z25" s="7"/>
-      <c r="AA25" s="7"/>
-      <c r="AB25" s="7"/>
-      <c r="AC25" s="7"/>
       <c r="AD25" s="7"/>
       <c r="AE25" s="7"/>
       <c r="AF25" s="7"/>
@@ -11191,17 +11597,21 @@
       <c r="CR25" s="7"/>
       <c r="CS25" s="7"/>
       <c r="CT25" s="7"/>
-    </row>
-    <row r="26" spans="1:98" s="5" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="94"/>
-      <c r="B26" s="95"/>
+      <c r="CU25" s="7"/>
+      <c r="CV25" s="7"/>
+      <c r="CW25" s="7"/>
+      <c r="CX25" s="7"/>
+    </row>
+    <row r="26" spans="1:102" s="5" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="95"/>
+      <c r="B26" s="96"/>
       <c r="C26" s="34"/>
       <c r="D26" s="35"/>
       <c r="E26" s="36" t="s">
         <v>1</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="G26" s="36" t="s">
         <v>1</v>
@@ -11221,48 +11631,56 @@
       <c r="L26" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="M26" s="62"/>
+      <c r="M26" s="36" t="s">
+        <v>1</v>
+      </c>
       <c r="N26" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="O26" s="62"/>
+      <c r="P26" s="36" t="s">
         <v>1</v>
-      </c>
-      <c r="O26" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="P26" s="36" t="s">
-        <v>83</v>
       </c>
       <c r="Q26" s="36" t="s">
         <v>1</v>
       </c>
       <c r="R26" s="36" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="S26" s="36" t="s">
         <v>1</v>
       </c>
       <c r="T26" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="V26" s="7" t="str">
-        <f t="shared" si="14"/>
+        <v>109</v>
+      </c>
+      <c r="U26" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="V26" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="W26" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="X26" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z26" s="7" t="str">
+        <f t="shared" si="15"/>
         <v>G_Rechts Laterale middenvoet</v>
       </c>
-      <c r="W26" s="7" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="X26" s="7" t="str">
+      <c r="AA26" s="7" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Y26" s="7">
+      <c r="AB26" s="7" t="str">
         <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AC26" s="7">
+        <f t="shared" si="18"/>
         <v>200</v>
       </c>
-      <c r="Z26" s="7"/>
-      <c r="AA26" s="7"/>
-      <c r="AB26" s="7"/>
-      <c r="AC26" s="7"/>
       <c r="AD26" s="7"/>
       <c r="AE26" s="7"/>
       <c r="AF26" s="7"/>
@@ -11332,80 +11750,87 @@
       <c r="CR26" s="7"/>
       <c r="CS26" s="7"/>
       <c r="CT26" s="7"/>
-    </row>
-    <row r="27" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="94"/>
-      <c r="B27" s="95"/>
+      <c r="CU26" s="7"/>
+      <c r="CV26" s="7"/>
+      <c r="CW26" s="7"/>
+      <c r="CX26" s="7"/>
+    </row>
+    <row r="27" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="95"/>
+      <c r="B27" s="96"/>
       <c r="C27" s="83" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D27" s="37"/>
       <c r="E27" s="38" t="str">
-        <f t="shared" ref="E27:E34" si="18">IF(J47="","",J47)</f>
+        <f t="shared" ref="E27:E34" si="19">IF(J47="","",J47)</f>
         <v/>
       </c>
       <c r="F27" s="39" t="str">
-        <f t="shared" ref="F27:F33" si="19">IF($C$36=C27,"TARGET",IF(E27="","",IF(AND(E27&gt;200,RANK(E27,$E$27:$E$33)&lt;=2),"TARGET","")))</f>
+        <f t="shared" ref="F27:F33" si="20">IF($C$36=C27,"TARGET",IF(E27="","",IF(AND(E27&gt;200,RANK(E27,$E$27:$E$33)&lt;=2),"TARGET","")))</f>
         <v/>
       </c>
       <c r="G27" s="40" t="str">
-        <f t="shared" ref="G27:G34" si="20">IF(J68="","",J68)</f>
+        <f t="shared" ref="G27:G34" si="21">IF(J68="","",J68)</f>
         <v/>
       </c>
       <c r="H27" s="43" t="str">
-        <f t="shared" ref="H27:H34" si="21">IF(OR($E27="",G27=""),"",((G27-$E27)/$E27)*100)</f>
+        <f t="shared" ref="H27:H34" si="22">IF(OR($E27="",G27=""),"",((G27-$E27)/$E27)*100)</f>
         <v/>
       </c>
       <c r="I27" s="40"/>
       <c r="J27" s="43" t="str">
-        <f t="shared" ref="J27:J34" si="22">IF(OR($E27="",I27=""),"",((I27-$E27)/$E27)*100)</f>
+        <f t="shared" ref="J27:J34" si="23">IF(OR($E27="",I27=""),"",((I27-$E27)/$E27)*100)</f>
         <v/>
       </c>
       <c r="K27" s="40"/>
       <c r="L27" s="43" t="str">
-        <f t="shared" ref="L27:L34" si="23">IF(OR($E27="",K27=""),"",((K27-$E27)/$E27)*100)</f>
-        <v/>
-      </c>
-      <c r="M27" s="33"/>
-      <c r="N27" s="40" t="str">
-        <f t="shared" ref="N27:N34" si="24">IF(E27="","",E27)</f>
-        <v/>
-      </c>
-      <c r="O27" s="40"/>
-      <c r="P27" s="43" t="str">
-        <f t="shared" ref="P27:P34" si="25">IF(OR($N27="",O27=""),"",((O27-$N27)/$N27)*100)</f>
-        <v/>
-      </c>
+        <f t="shared" ref="L27:L34" si="24">IF(OR($E27="",K27=""),"",((K27-$E27)/$E27)*100)</f>
+        <v/>
+      </c>
+      <c r="M27" s="40"/>
+      <c r="N27" s="43" t="str">
+        <f t="shared" ref="N27:N34" si="25">IF(OR($E27="",M27=""),"",((M27-$E27)/$E27)*100)</f>
+        <v/>
+      </c>
+      <c r="O27" s="33"/>
+      <c r="P27" s="40"/>
       <c r="Q27" s="40"/>
       <c r="R27" s="43" t="str">
-        <f t="shared" ref="R27:R34" si="26">IF(OR($N27="",Q27=""),"",((Q27-$N27)/$N27)*100)</f>
+        <f t="shared" ref="R27:R34" si="26">IF(OR($P27="",Q27=""),"",((Q27-$P27)/$P27)*100)</f>
         <v/>
       </c>
       <c r="S27" s="40"/>
       <c r="T27" s="43" t="str">
-        <f t="shared" ref="T27:T34" si="27">IF(OR($N27="",S27=""),"",((S27-$N27)/$N27)*100)</f>
-        <v/>
-      </c>
-      <c r="V27" s="7" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="T27:T34" si="27">IF(OR($P27="",S27=""),"",((S27-$P27)/$P27)*100)</f>
+        <v/>
+      </c>
+      <c r="U27" s="40"/>
+      <c r="V27" s="43" t="str">
+        <f t="shared" ref="V27:V34" si="28">IF(OR($P27="",U27=""),"",((U27-$P27)/$P27)*100)</f>
+        <v/>
+      </c>
+      <c r="W27" s="40"/>
+      <c r="X27" s="43" t="str">
+        <f t="shared" ref="X27:X34" si="29">IF(OR($P27="",W27=""),"",((W27-$P27)/$P27)*100)</f>
+        <v/>
+      </c>
+      <c r="Z27" s="7" t="str">
+        <f t="shared" si="15"/>
         <v>H_Rechts Hiel</v>
       </c>
-      <c r="W27" s="7" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="X27" s="7" t="str">
+      <c r="AA27" s="7" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Y27" s="7">
+      <c r="AB27" s="7" t="str">
         <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AC27" s="7">
+        <f t="shared" si="18"/>
         <v>200</v>
       </c>
-      <c r="Z27" s="7"/>
-      <c r="AA27" s="7"/>
-      <c r="AB27" s="7"/>
-      <c r="AC27" s="7"/>
       <c r="AD27" s="7"/>
       <c r="AE27" s="7"/>
       <c r="AF27" s="7"/>
@@ -11475,50 +11900,51 @@
       <c r="CR27" s="7"/>
       <c r="CS27" s="7"/>
       <c r="CT27" s="7"/>
-    </row>
-    <row r="28" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="94"/>
-      <c r="B28" s="95"/>
+      <c r="CU27" s="7"/>
+      <c r="CV27" s="7"/>
+      <c r="CW27" s="7"/>
+      <c r="CX27" s="7"/>
+    </row>
+    <row r="28" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="95"/>
+      <c r="B28" s="96"/>
       <c r="C28" s="83" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D28" s="37"/>
       <c r="E28" s="38" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="F28" s="39" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G28" s="40" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H28" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I28" s="40"/>
       <c r="J28" s="43" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K28" s="40"/>
       <c r="L28" s="43" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M28" s="33"/>
-      <c r="N28" s="40" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="O28" s="40"/>
-      <c r="P28" s="43" t="str">
+      <c r="M28" s="40"/>
+      <c r="N28" s="43" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
+      <c r="O28" s="33"/>
+      <c r="P28" s="40"/>
       <c r="Q28" s="40"/>
       <c r="R28" s="43" t="str">
         <f t="shared" si="26"/>
@@ -11529,10 +11955,16 @@
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="V28" s="7"/>
-      <c r="W28" s="7"/>
-      <c r="X28" s="7"/>
-      <c r="Y28" s="7"/>
+      <c r="U28" s="40"/>
+      <c r="V28" s="43" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="W28" s="40"/>
+      <c r="X28" s="43" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
       <c r="Z28" s="7"/>
       <c r="AA28" s="7"/>
       <c r="AB28" s="7"/>
@@ -11606,50 +12038,51 @@
       <c r="CR28" s="7"/>
       <c r="CS28" s="7"/>
       <c r="CT28" s="7"/>
-    </row>
-    <row r="29" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="94"/>
-      <c r="B29" s="95"/>
+      <c r="CU28" s="7"/>
+      <c r="CV28" s="7"/>
+      <c r="CW28" s="7"/>
+      <c r="CX28" s="7"/>
+    </row>
+    <row r="29" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="95"/>
+      <c r="B29" s="96"/>
       <c r="C29" s="83" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D29" s="37"/>
       <c r="E29" s="38" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="F29" s="39" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G29" s="40" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H29" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I29" s="40"/>
       <c r="J29" s="43" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K29" s="40"/>
       <c r="L29" s="43" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M29" s="33"/>
-      <c r="N29" s="40" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="O29" s="40"/>
-      <c r="P29" s="43" t="str">
+      <c r="M29" s="40"/>
+      <c r="N29" s="43" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
+      <c r="O29" s="33"/>
+      <c r="P29" s="40"/>
       <c r="Q29" s="40"/>
       <c r="R29" s="43" t="str">
         <f t="shared" si="26"/>
@@ -11660,10 +12093,16 @@
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="V29" s="7"/>
-      <c r="W29" s="7"/>
-      <c r="X29" s="7"/>
-      <c r="Y29" s="7"/>
+      <c r="U29" s="40"/>
+      <c r="V29" s="43" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="W29" s="40"/>
+      <c r="X29" s="43" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
       <c r="Z29" s="7"/>
       <c r="AA29" s="7"/>
       <c r="AB29" s="7"/>
@@ -11737,50 +12176,51 @@
       <c r="CR29" s="7"/>
       <c r="CS29" s="7"/>
       <c r="CT29" s="7"/>
-    </row>
-    <row r="30" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="94"/>
-      <c r="B30" s="95"/>
+      <c r="CU29" s="7"/>
+      <c r="CV29" s="7"/>
+      <c r="CW29" s="7"/>
+      <c r="CX29" s="7"/>
+    </row>
+    <row r="30" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="95"/>
+      <c r="B30" s="96"/>
       <c r="C30" s="83" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D30" s="37"/>
       <c r="E30" s="38" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="F30" s="39" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G30" s="40" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H30" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I30" s="40"/>
       <c r="J30" s="43" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K30" s="40"/>
       <c r="L30" s="43" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M30" s="33"/>
-      <c r="N30" s="40" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="O30" s="40"/>
-      <c r="P30" s="43" t="str">
+      <c r="M30" s="40"/>
+      <c r="N30" s="43" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
+      <c r="O30" s="33"/>
+      <c r="P30" s="40"/>
       <c r="Q30" s="40"/>
       <c r="R30" s="43" t="str">
         <f t="shared" si="26"/>
@@ -11791,10 +12231,16 @@
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="V30" s="7"/>
-      <c r="W30" s="7"/>
-      <c r="X30" s="7"/>
-      <c r="Y30" s="7"/>
+      <c r="U30" s="40"/>
+      <c r="V30" s="43" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="W30" s="40"/>
+      <c r="X30" s="43" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
       <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
       <c r="AB30" s="7"/>
@@ -11868,50 +12314,51 @@
       <c r="CR30" s="7"/>
       <c r="CS30" s="7"/>
       <c r="CT30" s="7"/>
-    </row>
-    <row r="31" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="94"/>
-      <c r="B31" s="95"/>
+      <c r="CU30" s="7"/>
+      <c r="CV30" s="7"/>
+      <c r="CW30" s="7"/>
+      <c r="CX30" s="7"/>
+    </row>
+    <row r="31" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="95"/>
+      <c r="B31" s="96"/>
       <c r="C31" s="83" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D31" s="37"/>
       <c r="E31" s="38" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="F31" s="39" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G31" s="40" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H31" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I31" s="40"/>
       <c r="J31" s="43" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K31" s="40"/>
       <c r="L31" s="43" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M31" s="33"/>
-      <c r="N31" s="40" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="O31" s="40"/>
-      <c r="P31" s="43" t="str">
+      <c r="M31" s="40"/>
+      <c r="N31" s="43" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
+      <c r="O31" s="33"/>
+      <c r="P31" s="40"/>
       <c r="Q31" s="40"/>
       <c r="R31" s="43" t="str">
         <f t="shared" si="26"/>
@@ -11922,10 +12369,16 @@
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="V31" s="7"/>
-      <c r="W31" s="7"/>
-      <c r="X31" s="7"/>
-      <c r="Y31" s="7"/>
+      <c r="U31" s="40"/>
+      <c r="V31" s="43" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="W31" s="40"/>
+      <c r="X31" s="43" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
       <c r="Z31" s="7"/>
       <c r="AA31" s="7"/>
       <c r="AB31" s="7"/>
@@ -11999,50 +12452,51 @@
       <c r="CR31" s="7"/>
       <c r="CS31" s="7"/>
       <c r="CT31" s="7"/>
-    </row>
-    <row r="32" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="94"/>
-      <c r="B32" s="95"/>
+      <c r="CU31" s="7"/>
+      <c r="CV31" s="7"/>
+      <c r="CW31" s="7"/>
+      <c r="CX31" s="7"/>
+    </row>
+    <row r="32" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="95"/>
+      <c r="B32" s="96"/>
       <c r="C32" s="83" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D32" s="37"/>
       <c r="E32" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="F32" s="39" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G32" s="40" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H32" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I32" s="40"/>
       <c r="J32" s="43" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K32" s="40"/>
       <c r="L32" s="43" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M32" s="33"/>
-      <c r="N32" s="40" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="O32" s="40"/>
-      <c r="P32" s="43" t="str">
+      <c r="M32" s="40"/>
+      <c r="N32" s="43" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
+      <c r="O32" s="33"/>
+      <c r="P32" s="40"/>
       <c r="Q32" s="40"/>
       <c r="R32" s="43" t="str">
         <f t="shared" si="26"/>
@@ -12053,10 +12507,16 @@
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="V32" s="7"/>
-      <c r="W32" s="7"/>
-      <c r="X32" s="7"/>
-      <c r="Y32" s="7"/>
+      <c r="U32" s="40"/>
+      <c r="V32" s="43" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="W32" s="40"/>
+      <c r="X32" s="43" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
       <c r="Z32" s="7"/>
       <c r="AA32" s="7"/>
       <c r="AB32" s="7"/>
@@ -12130,50 +12590,51 @@
       <c r="CR32" s="7"/>
       <c r="CS32" s="7"/>
       <c r="CT32" s="7"/>
-    </row>
-    <row r="33" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="94"/>
-      <c r="B33" s="95"/>
+      <c r="CU32" s="7"/>
+      <c r="CV32" s="7"/>
+      <c r="CW32" s="7"/>
+      <c r="CX32" s="7"/>
+    </row>
+    <row r="33" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="95"/>
+      <c r="B33" s="96"/>
       <c r="C33" s="83" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D33" s="37"/>
       <c r="E33" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="F33" s="39" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G33" s="40" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H33" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I33" s="40"/>
       <c r="J33" s="43" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K33" s="40"/>
       <c r="L33" s="43" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M33" s="33"/>
-      <c r="N33" s="40" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="O33" s="40"/>
-      <c r="P33" s="43" t="str">
+      <c r="M33" s="40"/>
+      <c r="N33" s="43" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
+      <c r="O33" s="33"/>
+      <c r="P33" s="40"/>
       <c r="Q33" s="40"/>
       <c r="R33" s="43" t="str">
         <f t="shared" si="26"/>
@@ -12184,10 +12645,16 @@
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="V33" s="7"/>
-      <c r="W33" s="7"/>
-      <c r="X33" s="7"/>
-      <c r="Y33" s="7"/>
+      <c r="U33" s="40"/>
+      <c r="V33" s="43" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="W33" s="40"/>
+      <c r="X33" s="43" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
       <c r="Z33" s="7"/>
       <c r="AA33" s="7"/>
       <c r="AB33" s="7"/>
@@ -12261,16 +12728,20 @@
       <c r="CR33" s="7"/>
       <c r="CS33" s="7"/>
       <c r="CT33" s="7"/>
-    </row>
-    <row r="34" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="96"/>
-      <c r="B34" s="97"/>
+      <c r="CU33" s="7"/>
+      <c r="CV33" s="7"/>
+      <c r="CW33" s="7"/>
+      <c r="CX33" s="7"/>
+    </row>
+    <row r="34" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="97"/>
+      <c r="B34" s="98"/>
       <c r="C34" s="83" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D34" s="37"/>
       <c r="E34" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="F34" s="39" t="str">
@@ -12278,33 +12749,30 @@
         <v/>
       </c>
       <c r="G34" s="40" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H34" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I34" s="40"/>
       <c r="J34" s="43" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K34" s="40"/>
       <c r="L34" s="43" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M34" s="33"/>
-      <c r="N34" s="40" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="O34" s="40"/>
-      <c r="P34" s="43" t="str">
+      <c r="M34" s="40"/>
+      <c r="N34" s="43" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
+      <c r="O34" s="33"/>
+      <c r="P34" s="40"/>
       <c r="Q34" s="40"/>
       <c r="R34" s="43" t="str">
         <f t="shared" si="26"/>
@@ -12315,10 +12783,16 @@
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="V34" s="7"/>
-      <c r="W34" s="7"/>
-      <c r="X34" s="7"/>
-      <c r="Y34" s="7"/>
+      <c r="U34" s="40"/>
+      <c r="V34" s="43" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="W34" s="40"/>
+      <c r="X34" s="43" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
       <c r="Z34" s="7"/>
       <c r="AA34" s="7"/>
       <c r="AB34" s="7"/>
@@ -12392,8 +12866,12 @@
       <c r="CR34" s="7"/>
       <c r="CS34" s="7"/>
       <c r="CT34" s="7"/>
-    </row>
-    <row r="35" spans="1:98" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="CU34" s="7"/>
+      <c r="CV34" s="7"/>
+      <c r="CW34" s="7"/>
+      <c r="CX34" s="7"/>
+    </row>
+    <row r="35" spans="1:102" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="21"/>
       <c r="B35" s="21"/>
       <c r="C35" s="48"/>
@@ -12406,18 +12884,18 @@
       <c r="J35" s="26"/>
       <c r="K35" s="26"/>
       <c r="L35" s="25"/>
-      <c r="M35" s="27"/>
-      <c r="N35" s="27"/>
+      <c r="M35" s="102"/>
+      <c r="N35" s="102"/>
       <c r="O35" s="27"/>
       <c r="P35" s="27"/>
       <c r="Q35" s="27"/>
       <c r="R35" s="27"/>
       <c r="S35" s="27"/>
       <c r="T35" s="27"/>
-      <c r="V35" s="3"/>
-      <c r="W35" s="3"/>
-      <c r="X35" s="3"/>
-      <c r="Y35" s="3"/>
+      <c r="U35" s="27"/>
+      <c r="V35" s="27"/>
+      <c r="W35" s="27"/>
+      <c r="X35" s="27"/>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3"/>
       <c r="AB35" s="3"/>
@@ -12491,34 +12969,38 @@
       <c r="CR35" s="3"/>
       <c r="CS35" s="3"/>
       <c r="CT35" s="3"/>
-    </row>
-    <row r="36" spans="1:98" s="5" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="87" t="s">
-        <v>86</v>
-      </c>
-      <c r="B36" s="88"/>
-      <c r="C36" s="89"/>
-      <c r="D36" s="90"/>
-      <c r="E36" s="90"/>
-      <c r="F36" s="90"/>
-      <c r="G36" s="90"/>
-      <c r="H36" s="90"/>
-      <c r="I36" s="90"/>
-      <c r="J36" s="90"/>
-      <c r="K36" s="90"/>
-      <c r="L36" s="90"/>
-      <c r="M36" s="90"/>
-      <c r="N36" s="90"/>
-      <c r="O36" s="90"/>
-      <c r="P36" s="90"/>
-      <c r="Q36" s="90"/>
-      <c r="R36" s="90"/>
-      <c r="S36" s="90"/>
-      <c r="T36" s="91"/>
-      <c r="V36" s="7"/>
-      <c r="W36" s="7"/>
-      <c r="X36" s="7"/>
-      <c r="Y36" s="7"/>
+      <c r="CU35" s="3"/>
+      <c r="CV35" s="3"/>
+      <c r="CW35" s="3"/>
+      <c r="CX35" s="3"/>
+    </row>
+    <row r="36" spans="1:102" s="5" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="99" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="100"/>
+      <c r="C36" s="106"/>
+      <c r="D36" s="107"/>
+      <c r="E36" s="107"/>
+      <c r="F36" s="107"/>
+      <c r="G36" s="107"/>
+      <c r="H36" s="107"/>
+      <c r="I36" s="107"/>
+      <c r="J36" s="107"/>
+      <c r="K36" s="107"/>
+      <c r="L36" s="107"/>
+      <c r="M36" s="107"/>
+      <c r="N36" s="107"/>
+      <c r="O36" s="107"/>
+      <c r="P36" s="107"/>
+      <c r="Q36" s="107"/>
+      <c r="R36" s="107"/>
+      <c r="S36" s="107"/>
+      <c r="T36" s="107"/>
+      <c r="U36" s="107"/>
+      <c r="V36" s="107"/>
+      <c r="W36" s="107"/>
+      <c r="X36" s="107"/>
       <c r="Z36" s="7"/>
       <c r="AA36" s="7"/>
       <c r="AB36" s="7"/>
@@ -12592,8 +13074,12 @@
       <c r="CR36" s="7"/>
       <c r="CS36" s="7"/>
       <c r="CT36" s="7"/>
-    </row>
-    <row r="37" spans="1:98" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="CU36" s="7"/>
+      <c r="CV36" s="7"/>
+      <c r="CW36" s="7"/>
+      <c r="CX36" s="7"/>
+    </row>
+    <row r="37" spans="1:102" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="19"/>
       <c r="B37" s="19"/>
       <c r="C37" s="28"/>
@@ -12614,10 +13100,10 @@
       <c r="R37" s="30"/>
       <c r="S37" s="30"/>
       <c r="T37" s="30"/>
-      <c r="V37" s="7"/>
-      <c r="W37" s="7"/>
-      <c r="X37" s="7"/>
-      <c r="Y37" s="7"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="105"/>
+      <c r="X37" s="105"/>
       <c r="Z37" s="7"/>
       <c r="AA37" s="7"/>
       <c r="AB37" s="7"/>
@@ -12691,13 +13177,17 @@
       <c r="CR37" s="7"/>
       <c r="CS37" s="7"/>
       <c r="CT37" s="7"/>
-    </row>
-    <row r="39" spans="1:98" ht="16" x14ac:dyDescent="0.4">
+      <c r="CU37" s="7"/>
+      <c r="CV37" s="7"/>
+      <c r="CW37" s="7"/>
+      <c r="CX37" s="7"/>
+    </row>
+    <row r="39" spans="1:102" ht="16" x14ac:dyDescent="0.4">
       <c r="A39" s="45" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:98" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A40" s="53"/>
       <c r="B40" s="47"/>
       <c r="C40" s="47"/>
@@ -12718,10 +13208,14 @@
       <c r="R40" s="47"/>
       <c r="S40" s="47"/>
       <c r="T40" s="47"/>
-    </row>
-    <row r="41" spans="1:98" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="U40" s="47"/>
+      <c r="V40" s="47"/>
+      <c r="W40" s="47"/>
+      <c r="X40" s="47"/>
+    </row>
+    <row r="41" spans="1:102" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="54" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B41" s="50"/>
       <c r="C41" s="50"/>
@@ -12742,10 +13236,10 @@
       <c r="R41" s="50"/>
       <c r="S41" s="50"/>
       <c r="T41" s="50"/>
-      <c r="U41" s="9"/>
-      <c r="V41" s="9"/>
-      <c r="W41" s="9"/>
-      <c r="X41" s="9"/>
+      <c r="U41" s="50"/>
+      <c r="V41" s="50"/>
+      <c r="W41" s="50"/>
+      <c r="X41" s="50"/>
       <c r="Y41" s="9"/>
       <c r="Z41" s="9"/>
       <c r="AA41" s="9"/>
@@ -12820,8 +13314,12 @@
       <c r="CR41" s="9"/>
       <c r="CS41" s="9"/>
       <c r="CT41" s="9"/>
-    </row>
-    <row r="42" spans="1:98" x14ac:dyDescent="0.35">
+      <c r="CU41" s="9"/>
+      <c r="CV41" s="9"/>
+      <c r="CW41" s="9"/>
+      <c r="CX41" s="9"/>
+    </row>
+    <row r="42" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A42" s="53"/>
       <c r="B42" s="47"/>
       <c r="C42" s="47"/>
@@ -12842,10 +13340,14 @@
       <c r="R42" s="47"/>
       <c r="S42" s="47"/>
       <c r="T42" s="47"/>
-    </row>
-    <row r="43" spans="1:98" x14ac:dyDescent="0.35">
+      <c r="U42" s="47"/>
+      <c r="V42" s="47"/>
+      <c r="W42" s="47"/>
+      <c r="X42" s="47"/>
+    </row>
+    <row r="43" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A43" s="55" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="B43" s="50"/>
       <c r="C43" s="50"/>
@@ -12861,20 +13363,24 @@
       <c r="M43" s="50"/>
       <c r="N43" s="50"/>
       <c r="O43" s="50"/>
-      <c r="P43" s="47"/>
-      <c r="Q43" s="47"/>
+      <c r="P43" s="50"/>
+      <c r="Q43" s="50"/>
       <c r="R43" s="47"/>
       <c r="S43" s="47"/>
       <c r="T43" s="47"/>
-    </row>
-    <row r="45" spans="1:98" ht="16" x14ac:dyDescent="0.4">
+      <c r="U43" s="47"/>
+      <c r="V43" s="47"/>
+      <c r="W43" s="47"/>
+      <c r="X43" s="47"/>
+    </row>
+    <row r="45" spans="1:102" ht="16" x14ac:dyDescent="0.4">
       <c r="A45" s="45" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="46" spans="1:98" ht="43.5" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:102" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A46" s="44" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -12888,11 +13394,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:98" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -12902,11 +13408,11 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
     </row>
-    <row r="48" spans="1:98" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -12920,7 +13426,7 @@
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -12934,7 +13440,7 @@
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -12948,7 +13454,7 @@
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -12962,7 +13468,7 @@
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -12976,7 +13482,7 @@
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -12990,7 +13496,7 @@
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -13023,7 +13529,7 @@
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B57" s="1"/>
       <c r="C57" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -13036,7 +13542,7 @@
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B58" s="1"/>
       <c r="C58" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -13049,7 +13555,7 @@
     <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B59" s="1"/>
       <c r="C59" s="1" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -13062,7 +13568,7 @@
     <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B60" s="1"/>
       <c r="C60" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -13075,7 +13581,7 @@
     <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B61" s="1"/>
       <c r="C61" s="1" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -13087,7 +13593,7 @@
     </row>
     <row r="62" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C62" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -13099,7 +13605,7 @@
     </row>
     <row r="63" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C63" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -13111,7 +13617,7 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C64" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -13123,12 +13629,12 @@
     </row>
     <row r="66" spans="1:10" ht="16" x14ac:dyDescent="0.4">
       <c r="A66" s="45" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" s="44" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="J67" s="12" t="s">
         <v>1</v>
@@ -13136,7 +13642,7 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C68" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
@@ -13148,7 +13654,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C69" s="1" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -13160,7 +13666,7 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C70" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -13172,7 +13678,7 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C71" s="1" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -13184,7 +13690,7 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C72" s="1" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -13196,7 +13702,7 @@
     </row>
     <row r="73" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C73" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -13208,7 +13714,7 @@
     </row>
     <row r="74" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C74" s="1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -13220,7 +13726,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C75" s="1" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -13232,7 +13738,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C78" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -13244,7 +13750,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C79" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
@@ -13256,7 +13762,7 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C80" s="1" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
@@ -13268,7 +13774,7 @@
     </row>
     <row r="81" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C81" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
@@ -13280,7 +13786,7 @@
     </row>
     <row r="82" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C82" s="1" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -13292,7 +13798,7 @@
     </row>
     <row r="83" spans="3:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C83" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
@@ -13304,7 +13810,7 @@
     </row>
     <row r="84" spans="3:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C84" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -13316,7 +13822,7 @@
     </row>
     <row r="85" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C85" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -13327,268 +13833,310 @@
       <c r="J85" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="E2:L2"/>
-    <mergeCell ref="E3:L3"/>
-    <mergeCell ref="N8:T8"/>
-    <mergeCell ref="D8:L8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="A9:B18"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="S9:T9"/>
-    <mergeCell ref="S25:T25"/>
+  <mergeCells count="29">
+    <mergeCell ref="W9:X9"/>
+    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="P8:X8"/>
+    <mergeCell ref="P24:X24"/>
+    <mergeCell ref="C20:X20"/>
+    <mergeCell ref="U25:V25"/>
     <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C20:T20"/>
-    <mergeCell ref="C36:T36"/>
     <mergeCell ref="A25:B34"/>
     <mergeCell ref="G25:H25"/>
     <mergeCell ref="I25:J25"/>
     <mergeCell ref="K25:L25"/>
-    <mergeCell ref="O25:P25"/>
     <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="D24:L24"/>
-    <mergeCell ref="N24:T24"/>
+    <mergeCell ref="S25:T25"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="D24:N24"/>
+    <mergeCell ref="C36:X36"/>
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="E3:L3"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A9:B18"/>
+    <mergeCell ref="S9:T9"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="D8:N8"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="E11:E18">
-    <cfRule type="expression" dxfId="119" priority="7">
+    <cfRule type="expression" dxfId="139" priority="17">
       <formula>AND(E11&lt;&gt;"",E11&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="8">
+    <cfRule type="expression" dxfId="138" priority="18">
       <formula>AND(E11&lt;&gt;"",E11&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E27:E34">
-    <cfRule type="expression" dxfId="117" priority="25">
+    <cfRule type="expression" dxfId="137" priority="35">
       <formula>AND(E27&lt;&gt;"",E27&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="116" priority="26">
+    <cfRule type="expression" dxfId="136" priority="36">
       <formula>AND(E27&lt;&gt;"",E27&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11:F18">
-    <cfRule type="containsText" dxfId="115" priority="24" operator="containsText" text="TARGET">
+    <cfRule type="containsText" dxfId="135" priority="34" operator="containsText" text="TARGET">
       <formula>NOT(ISERROR(SEARCH("TARGET",F11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27:F34">
-    <cfRule type="containsText" dxfId="114" priority="42" operator="containsText" text="TARGET">
+    <cfRule type="containsText" dxfId="134" priority="52" operator="containsText" text="TARGET">
       <formula>NOT(ISERROR(SEARCH("TARGET",F27)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:G18">
-    <cfRule type="expression" dxfId="113" priority="9">
+    <cfRule type="expression" dxfId="133" priority="19">
       <formula>AND(G11&lt;&gt;"",G11&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="112" priority="10">
+    <cfRule type="expression" dxfId="132" priority="20">
       <formula>AND(G11&lt;&gt;"",G11&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27:G34">
-    <cfRule type="expression" dxfId="111" priority="27">
+    <cfRule type="expression" dxfId="131" priority="37">
       <formula>AND(G27&lt;&gt;"",G27&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="28">
+    <cfRule type="expression" dxfId="130" priority="38">
       <formula>AND(G27&lt;&gt;"",G27&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:H18">
-    <cfRule type="expression" dxfId="109" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="129" priority="53" stopIfTrue="1">
       <formula>AND(H11&lt;&gt;"",OR(G11&lt;200,H11&lt;=-25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="128" priority="54" stopIfTrue="1">
       <formula>AND(H11&lt;&gt;"",G11&gt;=200,H11&gt;-25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H34">
-    <cfRule type="expression" dxfId="107" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="127" priority="55" stopIfTrue="1">
       <formula>AND(H27&lt;&gt;"",OR(G27&lt;200,H27&lt;=-25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="126" priority="56" stopIfTrue="1">
       <formula>AND(H27&lt;&gt;"",G27&gt;=200,H27&gt;-25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I11:I18">
-    <cfRule type="expression" dxfId="105" priority="11">
+    <cfRule type="expression" dxfId="125" priority="21">
       <formula>AND(I11&lt;&gt;"",I11&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="12">
+    <cfRule type="expression" dxfId="124" priority="22">
       <formula>AND(I11&lt;&gt;"",I11&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I27:I34">
-    <cfRule type="expression" dxfId="103" priority="29">
+    <cfRule type="expression" dxfId="123" priority="39">
       <formula>AND(I27&lt;&gt;"",I27&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="30">
+    <cfRule type="expression" dxfId="122" priority="40">
       <formula>AND(I27&lt;&gt;"",I27&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J18">
-    <cfRule type="expression" dxfId="101" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="121" priority="57" stopIfTrue="1">
       <formula>AND(J11&lt;&gt;"",OR(I11&lt;200,J11&lt;=-25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="120" priority="58" stopIfTrue="1">
       <formula>AND(J11&lt;&gt;"",I11&gt;=200,J11&gt;-25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J27:J34">
-    <cfRule type="expression" dxfId="99" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="119" priority="59" stopIfTrue="1">
       <formula>AND(J27&lt;&gt;"",OR(I27&lt;200,J27&lt;=-25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="118" priority="60" stopIfTrue="1">
       <formula>AND(J27&lt;&gt;"",I27&gt;=200,J27&gt;-25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:K18">
-    <cfRule type="expression" dxfId="97" priority="13">
+    <cfRule type="expression" dxfId="117" priority="23">
       <formula>AND(K11&lt;&gt;"",K11&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="14">
+    <cfRule type="expression" dxfId="116" priority="24">
       <formula>AND(K11&lt;&gt;"",K11&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K34">
-    <cfRule type="expression" dxfId="95" priority="31">
+    <cfRule type="expression" dxfId="115" priority="41">
       <formula>AND(K27&lt;&gt;"",K27&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="32">
+    <cfRule type="expression" dxfId="114" priority="42">
       <formula>AND(K27&lt;&gt;"",K27&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L11:L18">
-    <cfRule type="expression" dxfId="93" priority="51" stopIfTrue="1">
+  <conditionalFormatting sqref="L11:L18 N11:N18">
+    <cfRule type="expression" dxfId="113" priority="61" stopIfTrue="1">
       <formula>AND(L11&lt;&gt;"",OR(K11&lt;200,L11&lt;=-25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="112" priority="62" stopIfTrue="1">
       <formula>AND(L11&lt;&gt;"",K11&gt;=200,L11&gt;-25)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L27:L34">
-    <cfRule type="expression" dxfId="91" priority="53" stopIfTrue="1">
+  <conditionalFormatting sqref="L27:L34 N27:N34">
+    <cfRule type="expression" dxfId="111" priority="63" stopIfTrue="1">
       <formula>AND(L27&lt;&gt;"",OR(K27&lt;200,L27&lt;=-25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="110" priority="64" stopIfTrue="1">
       <formula>AND(L27&lt;&gt;"",K27&gt;=200,L27&gt;-25)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O11:O18">
-    <cfRule type="expression" dxfId="89" priority="6" stopIfTrue="1">
-      <formula>AND(O11&lt;&gt;"",O11&gt;=1.05*IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="88" priority="15">
-      <formula>AND(O11&lt;&gt;"",O11&gt;=200)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="87" priority="16">
-      <formula>AND(O11&lt;&gt;"",O11&lt;200)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O27:O34">
-    <cfRule type="expression" dxfId="86" priority="3" stopIfTrue="1">
-      <formula>AND(O27&lt;&gt;"",O27&gt;=1.05*IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="85" priority="33">
-      <formula>AND(O27&lt;&gt;"",O27&gt;=200)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="84" priority="34">
-      <formula>AND(O27&lt;&gt;"",O27&lt;200)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P11:P18">
-    <cfRule type="expression" dxfId="83" priority="55" stopIfTrue="1">
-      <formula>AND(P11&lt;&gt;"",OR(O11&lt;200,P11&lt;=-25))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="82" priority="56" stopIfTrue="1">
-      <formula>AND(P11&lt;&gt;"",O11&gt;=200,P11&gt;-25)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P27:P34">
-    <cfRule type="expression" dxfId="81" priority="57" stopIfTrue="1">
-      <formula>AND(P27&lt;&gt;"",OR(O27&lt;200,P27&lt;=-25))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="80" priority="58" stopIfTrue="1">
-      <formula>AND(P27&lt;&gt;"",O27&gt;=200,P27&gt;-25)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="Q11:Q18">
-    <cfRule type="expression" dxfId="79" priority="5" stopIfTrue="1">
-      <formula>AND(Q11&lt;&gt;"",Q11&gt;=1.05*IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="78" priority="17">
+    <cfRule type="expression" dxfId="109" priority="25">
       <formula>AND(Q11&lt;&gt;"",Q11&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="18">
+    <cfRule type="expression" dxfId="108" priority="26">
       <formula>AND(Q11&lt;&gt;"",Q11&lt;200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="107" priority="77" stopIfTrue="1">
+      <formula>AND(Q11&lt;&gt;"",Q11&gt;=1.05*IF($M11&lt;&gt;"",$M11,IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q27:Q34">
-    <cfRule type="expression" dxfId="76" priority="2" stopIfTrue="1">
-      <formula>AND(Q27&lt;&gt;"",Q27&gt;=1.05*IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="75" priority="35">
+    <cfRule type="expression" dxfId="106" priority="43">
       <formula>AND(Q27&lt;&gt;"",Q27&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="36">
+    <cfRule type="expression" dxfId="105" priority="44">
       <formula>AND(Q27&lt;&gt;"",Q27&lt;200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="104" priority="81" stopIfTrue="1">
+      <formula>AND(Q27&lt;&gt;"",Q27&gt;=1.05*IF($M27&lt;&gt;"",$M27,IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R11:R18">
-    <cfRule type="expression" dxfId="73" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="103" priority="65" stopIfTrue="1">
       <formula>AND(R11&lt;&gt;"",OR(Q11&lt;200,R11&lt;=-25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="102" priority="66" stopIfTrue="1">
       <formula>AND(R11&lt;&gt;"",Q11&gt;=200,R11&gt;-25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R27:R34">
-    <cfRule type="expression" dxfId="71" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="67" stopIfTrue="1">
       <formula>AND(R27&lt;&gt;"",OR(Q27&lt;200,R27&lt;=-25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="68" stopIfTrue="1">
       <formula>AND(R27&lt;&gt;"",Q27&gt;=200,R27&gt;-25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S11:S18">
-    <cfRule type="expression" dxfId="69" priority="4" stopIfTrue="1">
-      <formula>AND(S11&lt;&gt;"",S11&gt;=1.05*IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="68" priority="19">
+    <cfRule type="expression" dxfId="99" priority="27">
       <formula>AND(S11&lt;&gt;"",S11&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="20">
+    <cfRule type="expression" dxfId="98" priority="28">
       <formula>AND(S11&lt;&gt;"",S11&lt;200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="97" priority="78" stopIfTrue="1">
+      <formula>AND(S11&lt;&gt;"",S11&gt;=1.05*IF($M11&lt;&gt;"",$M11,IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S27:S34">
-    <cfRule type="expression" dxfId="66" priority="1" stopIfTrue="1">
-      <formula>AND(S27&lt;&gt;"",S27&gt;=1.05*IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="65" priority="37">
+    <cfRule type="expression" dxfId="96" priority="45">
       <formula>AND(S27&lt;&gt;"",S27&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="38">
+    <cfRule type="expression" dxfId="95" priority="46">
       <formula>AND(S27&lt;&gt;"",S27&lt;200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="94" priority="82" stopIfTrue="1">
+      <formula>AND(S27&lt;&gt;"",S27&gt;=1.05*IF($M27&lt;&gt;"",$M27,IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T11:T18">
-    <cfRule type="expression" dxfId="63" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="69" stopIfTrue="1">
       <formula>AND(T11&lt;&gt;"",OR(S11&lt;200,T11&lt;=-25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="70" stopIfTrue="1">
       <formula>AND(T11&lt;&gt;"",S11&gt;=200,T11&gt;-25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T27:T34">
-    <cfRule type="expression" dxfId="61" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="71" stopIfTrue="1">
       <formula>AND(T27&lt;&gt;"",OR(S27&lt;200,T27&lt;=-25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="72" stopIfTrue="1">
       <formula>AND(T27&lt;&gt;"",S27&gt;=200,T27&gt;-25)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U11:U18">
+    <cfRule type="expression" dxfId="89" priority="29">
+      <formula>AND(U11&lt;&gt;"",U11&gt;=200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="88" priority="30">
+      <formula>AND(U11&lt;&gt;"",U11&lt;200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="87" priority="79" stopIfTrue="1">
+      <formula>AND(U11&lt;&gt;"",U11&gt;=1.05*IF($M11&lt;&gt;"",$M11,IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U27:U34">
+    <cfRule type="expression" dxfId="86" priority="47">
+      <formula>AND(U27&lt;&gt;"",U27&gt;=200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="85" priority="48">
+      <formula>AND(U27&lt;&gt;"",U27&lt;200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="83" stopIfTrue="1">
+      <formula>AND(U27&lt;&gt;"",U27&gt;=1.05*IF($M27&lt;&gt;"",$M27,IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V11:V18 X11:X18">
+    <cfRule type="expression" dxfId="83" priority="73" stopIfTrue="1">
+      <formula>AND(V11&lt;&gt;"",OR(U11&lt;200,V11&lt;=-25))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="82" priority="74" stopIfTrue="1">
+      <formula>AND(V11&lt;&gt;"",U11&gt;=200,V11&gt;-25)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V27:V34 X27:X34">
+    <cfRule type="expression" dxfId="81" priority="75" stopIfTrue="1">
+      <formula>AND(V27&lt;&gt;"",OR(U27&lt;200,V27&lt;=-25))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="80" priority="76" stopIfTrue="1">
+      <formula>AND(V27&lt;&gt;"",U27&gt;=200,V27&gt;-25)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M11:M18">
+    <cfRule type="expression" dxfId="79" priority="9">
+      <formula>AND(M11&lt;&gt;"",M11&gt;=200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="78" priority="10">
+      <formula>AND(M11&lt;&gt;"",M11&lt;200)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M27:M34">
+    <cfRule type="expression" dxfId="77" priority="7">
+      <formula>AND(M27&lt;&gt;"",M27&gt;=200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="76" priority="8">
+      <formula>AND(M27&lt;&gt;"",M27&lt;200)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W11:W18">
+    <cfRule type="expression" dxfId="75" priority="5">
+      <formula>AND(W11&lt;&gt;"",W11&gt;=200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="6">
+      <formula>AND(W11&lt;&gt;"",W11&lt;200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="73" priority="80" stopIfTrue="1">
+      <formula>AND(W11&lt;&gt;"",W11&gt;=1.05*IF($M11&lt;&gt;"",$M11,IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W27:W34">
+    <cfRule type="expression" dxfId="72" priority="2">
+      <formula>AND(W27&lt;&gt;"",W27&gt;=200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="71" priority="3">
+      <formula>AND(W27&lt;&gt;"",W27&lt;200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="70" priority="84" stopIfTrue="1">
+      <formula>AND(W27&lt;&gt;"",W27&gt;=1.05*IF($M27&lt;&gt;"",$M27,IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27))))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -13600,7 +14148,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="54" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="45" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
@@ -13612,7 +14160,7 @@
     <tabColor rgb="FFF5A623"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CT85"/>
+  <dimension ref="A1:CX85"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" customWidth="1"/>
@@ -13623,16 +14171,16 @@
     <col min="7" max="7" width="12.1796875" style="4" customWidth="1"/>
     <col min="8" max="8" width="12.1796875" customWidth="1"/>
     <col min="9" max="11" width="12.1796875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="12.1796875" customWidth="1"/>
-    <col min="13" max="13" width="3" customWidth="1"/>
-    <col min="14" max="20" width="12.1796875" customWidth="1"/>
-    <col min="21" max="21" width="8.81640625" style="7"/>
-    <col min="22" max="22" width="21" style="7" customWidth="1"/>
-    <col min="23" max="25" width="13.26953125" style="7" customWidth="1"/>
-    <col min="26" max="98" width="8.81640625" style="7"/>
+    <col min="12" max="14" width="12.1796875" customWidth="1"/>
+    <col min="15" max="15" width="3" customWidth="1"/>
+    <col min="16" max="24" width="12.1796875" customWidth="1"/>
+    <col min="25" max="25" width="8.81640625" style="7"/>
+    <col min="26" max="26" width="21" style="7" customWidth="1"/>
+    <col min="27" max="29" width="13.26953125" style="7" customWidth="1"/>
+    <col min="30" max="102" width="8.81640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:98" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:102" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="14"/>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -13653,56 +14201,64 @@
       <c r="R1" s="14"/>
       <c r="S1" s="14"/>
       <c r="T1" s="14"/>
-    </row>
-    <row r="2" spans="1:98" ht="34" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+    </row>
+    <row r="2" spans="1:102" ht="34" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
-      <c r="E2" s="101" t="s">
+      <c r="E2" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="86"/>
       <c r="O2" s="13"/>
       <c r="P2" s="13"/>
       <c r="Q2" s="13"/>
       <c r="R2" s="13"/>
       <c r="S2" s="13"/>
       <c r="T2" s="13"/>
-    </row>
-    <row r="3" spans="1:98" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U2" s="13"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="13"/>
+    </row>
+    <row r="3" spans="1:102" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
-      <c r="E3" s="103" t="s">
+      <c r="E3" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="86"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="86"/>
       <c r="O3" s="13"/>
       <c r="P3" s="13"/>
       <c r="Q3" s="13"/>
       <c r="R3" s="13"/>
       <c r="S3" s="13"/>
       <c r="T3" s="13"/>
-    </row>
-    <row r="4" spans="1:98" ht="4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+    </row>
+    <row r="4" spans="1:102" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="14"/>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -13723,26 +14279,30 @@
       <c r="R4" s="14"/>
       <c r="S4" s="14"/>
       <c r="T4" s="14"/>
-      <c r="V4" s="69" t="s">
+      <c r="U4" s="14"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="14"/>
+      <c r="X4" s="14"/>
+      <c r="Z4" s="69" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:98" x14ac:dyDescent="0.35">
-      <c r="U5" s="5"/>
-      <c r="X5" s="57" t="s">
+    <row r="5" spans="1:102" x14ac:dyDescent="0.35">
+      <c r="Y5" s="5"/>
+      <c r="AB5" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="Y5" s="56">
+      <c r="AC5" s="56">
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:98" ht="16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:102" ht="16" x14ac:dyDescent="0.35">
       <c r="A6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="105"/>
-      <c r="D6" s="106"/>
+      <c r="B6" s="90"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="92"/>
       <c r="E6" s="64"/>
       <c r="F6" s="64"/>
       <c r="G6" s="58" t="s">
@@ -13761,79 +14321,83 @@
       <c r="R6" s="66"/>
       <c r="S6" s="66"/>
       <c r="T6" s="66"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="68" t="s">
+      <c r="U6" s="66"/>
+      <c r="V6" s="66"/>
+      <c r="W6" s="66"/>
+      <c r="X6" s="66"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="W6" s="67"/>
-      <c r="X6" s="67"/>
-      <c r="Y6" s="67"/>
-    </row>
-    <row r="7" spans="1:98" ht="16" x14ac:dyDescent="0.4">
+      <c r="AA6" s="67"/>
+      <c r="AB6" s="67"/>
+      <c r="AC6" s="67"/>
+    </row>
+    <row r="7" spans="1:102" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="16"/>
       <c r="E7" s="15"/>
       <c r="F7" s="15"/>
       <c r="G7" s="17"/>
       <c r="H7" s="18"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="68" t="s">
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="W7" s="68" t="s">
+      <c r="AA7" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="X7" s="68" t="s">
+      <c r="AB7" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="Y7" s="68" t="s">
+      <c r="AC7" s="68" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:98" s="5" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:102" s="5" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8"/>
       <c r="B8"/>
       <c r="C8"/>
-      <c r="D8" s="98" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" s="99"/>
-      <c r="F8" s="99"/>
-      <c r="G8" s="99"/>
-      <c r="H8" s="99"/>
-      <c r="I8" s="99"/>
-      <c r="J8" s="99"/>
-      <c r="K8" s="99"/>
-      <c r="L8" s="100"/>
-      <c r="M8"/>
-      <c r="N8" s="98" t="s">
-        <v>81</v>
-      </c>
-      <c r="O8" s="99"/>
-      <c r="P8" s="99"/>
-      <c r="Q8" s="99"/>
-      <c r="R8" s="99"/>
-      <c r="S8" s="99"/>
-      <c r="T8" s="100"/>
-      <c r="V8" s="67" t="str">
-        <f t="shared" ref="V8:V15" si="0">C11</f>
+      <c r="D8" s="103" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8" s="104"/>
+      <c r="F8" s="104"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="104"/>
+      <c r="I8" s="104"/>
+      <c r="J8" s="104"/>
+      <c r="K8" s="104"/>
+      <c r="L8" s="104"/>
+      <c r="M8" s="104"/>
+      <c r="N8" s="104"/>
+      <c r="O8"/>
+      <c r="P8" s="103" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q8" s="104"/>
+      <c r="R8" s="104"/>
+      <c r="S8" s="104"/>
+      <c r="T8" s="104"/>
+      <c r="U8" s="104"/>
+      <c r="V8" s="104"/>
+      <c r="W8" s="104"/>
+      <c r="X8" s="104"/>
+      <c r="Z8" s="67" t="str">
+        <f t="shared" ref="Z8:Z15" si="0">C11</f>
         <v>I_Links Hallux</v>
       </c>
-      <c r="W8" s="67" t="str">
-        <f t="shared" ref="W8:W15" si="1">E11</f>
-        <v/>
-      </c>
-      <c r="X8" s="67" t="str">
-        <f t="shared" ref="X8:X15" si="2">G11</f>
-        <v/>
-      </c>
-      <c r="Y8" s="67">
-        <f t="shared" ref="Y8:Y15" si="3">$Y$5</f>
+      <c r="AA8" s="67" t="str">
+        <f t="shared" ref="AA8:AA15" si="1">E11</f>
+        <v/>
+      </c>
+      <c r="AB8" s="67" t="str">
+        <f t="shared" ref="AB8:AB15" si="2">G11</f>
+        <v/>
+      </c>
+      <c r="AC8" s="67">
+        <f t="shared" ref="AC8:AC15" si="3">$AC$5</f>
         <v>200</v>
       </c>
-      <c r="Z8" s="7"/>
-      <c r="AA8" s="7"/>
-      <c r="AB8" s="7"/>
-      <c r="AC8" s="7"/>
       <c r="AD8" s="7"/>
       <c r="AE8" s="7"/>
       <c r="AF8" s="7"/>
@@ -13903,12 +14467,16 @@
       <c r="CR8" s="7"/>
       <c r="CS8" s="7"/>
       <c r="CT8" s="7"/>
-    </row>
-    <row r="9" spans="1:98" s="5" customFormat="1" ht="36" x14ac:dyDescent="0.35">
-      <c r="A9" s="92" t="s">
+      <c r="CU8" s="7"/>
+      <c r="CV8" s="7"/>
+      <c r="CW8" s="7"/>
+      <c r="CX8" s="7"/>
+    </row>
+    <row r="9" spans="1:102" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.35">
+      <c r="A9" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="93"/>
+      <c r="B9" s="94"/>
       <c r="C9" s="34"/>
       <c r="D9" s="35"/>
       <c r="E9" s="60" t="s">
@@ -13917,54 +14485,58 @@
       <c r="F9" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="85" t="s">
+      <c r="G9" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="86"/>
-      <c r="I9" s="85" t="s">
+      <c r="H9" s="89"/>
+      <c r="I9" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="86"/>
-      <c r="K9" s="85" t="s">
+      <c r="J9" s="89"/>
+      <c r="K9" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="L9" s="86"/>
-      <c r="M9" s="62"/>
-      <c r="N9" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="O9" s="85" t="s">
+      <c r="L9" s="89"/>
+      <c r="M9" s="88" t="s">
+        <v>107</v>
+      </c>
+      <c r="N9" s="89"/>
+      <c r="O9" s="62"/>
+      <c r="P9" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q9" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="P9" s="86"/>
-      <c r="Q9" s="85" t="s">
+      <c r="R9" s="89"/>
+      <c r="S9" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="R9" s="86"/>
-      <c r="S9" s="85" t="s">
+      <c r="T9" s="89"/>
+      <c r="U9" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="T9" s="86"/>
-      <c r="V9" s="67" t="str">
+      <c r="V9" s="89"/>
+      <c r="W9" s="88" t="s">
+        <v>107</v>
+      </c>
+      <c r="X9" s="89"/>
+      <c r="Z9" s="67" t="str">
         <f t="shared" si="0"/>
         <v>J_Links Tenen 2-5</v>
       </c>
-      <c r="W9" s="67" t="str">
+      <c r="AA9" s="67" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X9" s="67" t="str">
+      <c r="AB9" s="67" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y9" s="67">
+      <c r="AC9" s="67">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="Z9" s="7"/>
-      <c r="AA9" s="7"/>
-      <c r="AB9" s="7"/>
-      <c r="AC9" s="7"/>
       <c r="AD9" s="7"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="7"/>
@@ -14034,17 +14606,21 @@
       <c r="CR9" s="7"/>
       <c r="CS9" s="7"/>
       <c r="CT9" s="7"/>
-    </row>
-    <row r="10" spans="1:98" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.35">
-      <c r="A10" s="94"/>
-      <c r="B10" s="95"/>
+      <c r="CU9" s="7"/>
+      <c r="CV9" s="7"/>
+      <c r="CW9" s="7"/>
+      <c r="CX9" s="7"/>
+    </row>
+    <row r="10" spans="1:102" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.35">
+      <c r="A10" s="95"/>
+      <c r="B10" s="96"/>
       <c r="C10" s="34"/>
       <c r="D10" s="35"/>
       <c r="E10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="G10" s="36" t="s">
         <v>1</v>
@@ -14064,48 +14640,56 @@
       <c r="L10" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="M10" s="62"/>
+      <c r="M10" s="36" t="s">
+        <v>1</v>
+      </c>
       <c r="N10" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="O10" s="62"/>
+      <c r="P10" s="36" t="s">
         <v>1</v>
-      </c>
-      <c r="O10" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="P10" s="36" t="s">
-        <v>83</v>
       </c>
       <c r="Q10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="R10" s="36" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="S10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="T10" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="V10" s="67" t="str">
+        <v>109</v>
+      </c>
+      <c r="U10" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="V10" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="W10" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="X10" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z10" s="67" t="str">
         <f t="shared" si="0"/>
         <v>K_Links Metatarsaal 1</v>
       </c>
-      <c r="W10" s="67" t="str">
+      <c r="AA10" s="67" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X10" s="67" t="str">
+      <c r="AB10" s="67" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y10" s="67">
+      <c r="AC10" s="67">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="Z10" s="7"/>
-      <c r="AA10" s="7"/>
-      <c r="AB10" s="7"/>
-      <c r="AC10" s="7"/>
       <c r="AD10" s="7"/>
       <c r="AE10" s="7"/>
       <c r="AF10" s="7"/>
@@ -14175,12 +14759,16 @@
       <c r="CR10" s="7"/>
       <c r="CS10" s="7"/>
       <c r="CT10" s="7"/>
-    </row>
-    <row r="11" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="94"/>
-      <c r="B11" s="95"/>
+      <c r="CU10" s="7"/>
+      <c r="CV10" s="7"/>
+      <c r="CW10" s="7"/>
+      <c r="CX10" s="7"/>
+    </row>
+    <row r="11" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="95"/>
+      <c r="B11" s="96"/>
       <c r="C11" s="83" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D11" s="37"/>
       <c r="E11" s="38" t="str">
@@ -14209,46 +14797,49 @@
         <f t="shared" ref="L11:L18" si="9">IF(OR($E11="",K11=""),"",((K11-$E11)/$E11)*100)</f>
         <v/>
       </c>
-      <c r="M11" s="33"/>
-      <c r="N11" s="40" t="str">
-        <f t="shared" ref="N11:N18" si="10">IF(E11="","",E11)</f>
-        <v/>
-      </c>
-      <c r="O11" s="40"/>
-      <c r="P11" s="43" t="str">
-        <f t="shared" ref="P11:P18" si="11">IF(OR($N11="",O11=""),"",((O11-$N11)/$N11)*100)</f>
-        <v/>
-      </c>
+      <c r="M11" s="40"/>
+      <c r="N11" s="43" t="str">
+        <f t="shared" ref="N11:N18" si="10">IF(OR($E11="",M11=""),"",((M11-$E11)/$E11)*100)</f>
+        <v/>
+      </c>
+      <c r="O11" s="33"/>
+      <c r="P11" s="40"/>
       <c r="Q11" s="40"/>
       <c r="R11" s="43" t="str">
-        <f t="shared" ref="R11:R18" si="12">IF(OR($N11="",Q11=""),"",((Q11-$N11)/$N11)*100)</f>
+        <f t="shared" ref="R11:R18" si="11">IF(OR($P11="",Q11=""),"",((Q11-$P11)/$P11)*100)</f>
         <v/>
       </c>
       <c r="S11" s="40"/>
       <c r="T11" s="43" t="str">
-        <f t="shared" ref="T11:T18" si="13">IF(OR($N11="",S11=""),"",((S11-$N11)/$N11)*100)</f>
-        <v/>
-      </c>
-      <c r="V11" s="67" t="str">
+        <f t="shared" ref="T11:T18" si="12">IF(OR($P11="",S11=""),"",((S11-$P11)/$P11)*100)</f>
+        <v/>
+      </c>
+      <c r="U11" s="40"/>
+      <c r="V11" s="43" t="str">
+        <f t="shared" ref="V11:V18" si="13">IF(OR($P11="",U11=""),"",((U11-$P11)/$P11)*100)</f>
+        <v/>
+      </c>
+      <c r="W11" s="40"/>
+      <c r="X11" s="43" t="str">
+        <f t="shared" ref="X11:X18" si="14">IF(OR($P11="",W11=""),"",((W11-$P11)/$P11)*100)</f>
+        <v/>
+      </c>
+      <c r="Z11" s="67" t="str">
         <f t="shared" si="0"/>
         <v>L_Links Metatarsaal 2-3</v>
       </c>
-      <c r="W11" s="67" t="str">
+      <c r="AA11" s="67" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X11" s="67" t="str">
+      <c r="AB11" s="67" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y11" s="67">
+      <c r="AC11" s="67">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="Z11" s="7"/>
-      <c r="AA11" s="7"/>
-      <c r="AB11" s="7"/>
-      <c r="AC11" s="7"/>
       <c r="AD11" s="7"/>
       <c r="AE11" s="7"/>
       <c r="AF11" s="7"/>
@@ -14318,12 +14909,16 @@
       <c r="CR11" s="7"/>
       <c r="CS11" s="7"/>
       <c r="CT11" s="7"/>
-    </row>
-    <row r="12" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94"/>
-      <c r="B12" s="95"/>
+      <c r="CU11" s="7"/>
+      <c r="CV11" s="7"/>
+      <c r="CW11" s="7"/>
+      <c r="CX11" s="7"/>
+    </row>
+    <row r="12" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="95"/>
+      <c r="B12" s="96"/>
       <c r="C12" s="83" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D12" s="37"/>
       <c r="E12" s="38" t="str">
@@ -14352,46 +14947,49 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="M12" s="33"/>
-      <c r="N12" s="40" t="str">
+      <c r="M12" s="40"/>
+      <c r="N12" s="43" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O12" s="40"/>
-      <c r="P12" s="43" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
+      <c r="O12" s="33"/>
+      <c r="P12" s="40"/>
       <c r="Q12" s="40"/>
       <c r="R12" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S12" s="40"/>
       <c r="T12" s="43" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="U12" s="40"/>
+      <c r="V12" s="43" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="V12" s="67" t="str">
+      <c r="W12" s="40"/>
+      <c r="X12" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z12" s="67" t="str">
         <f t="shared" si="0"/>
         <v>M_Links Metatarsaal 4-5</v>
       </c>
-      <c r="W12" s="67" t="str">
+      <c r="AA12" s="67" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X12" s="67" t="str">
+      <c r="AB12" s="67" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y12" s="67">
+      <c r="AC12" s="67">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="Z12" s="7"/>
-      <c r="AA12" s="7"/>
-      <c r="AB12" s="7"/>
-      <c r="AC12" s="7"/>
       <c r="AD12" s="7"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="7"/>
@@ -14461,12 +15059,16 @@
       <c r="CR12" s="7"/>
       <c r="CS12" s="7"/>
       <c r="CT12" s="7"/>
-    </row>
-    <row r="13" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="94"/>
-      <c r="B13" s="95"/>
+      <c r="CU12" s="7"/>
+      <c r="CV12" s="7"/>
+      <c r="CW12" s="7"/>
+      <c r="CX12" s="7"/>
+    </row>
+    <row r="13" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="95"/>
+      <c r="B13" s="96"/>
       <c r="C13" s="83" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="38" t="str">
@@ -14495,46 +15097,49 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="M13" s="33"/>
-      <c r="N13" s="40" t="str">
+      <c r="M13" s="40"/>
+      <c r="N13" s="43" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O13" s="40"/>
-      <c r="P13" s="43" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
+      <c r="O13" s="33"/>
+      <c r="P13" s="40"/>
       <c r="Q13" s="40"/>
       <c r="R13" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S13" s="40"/>
       <c r="T13" s="43" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="U13" s="40"/>
+      <c r="V13" s="43" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="V13" s="67" t="str">
+      <c r="W13" s="40"/>
+      <c r="X13" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z13" s="67" t="str">
         <f t="shared" si="0"/>
         <v>N_Links Mediale middenvoet</v>
       </c>
-      <c r="W13" s="67" t="str">
+      <c r="AA13" s="67" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X13" s="67" t="str">
+      <c r="AB13" s="67" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y13" s="67">
+      <c r="AC13" s="67">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="Z13" s="7"/>
-      <c r="AA13" s="7"/>
-      <c r="AB13" s="7"/>
-      <c r="AC13" s="7"/>
       <c r="AD13" s="7"/>
       <c r="AE13" s="7"/>
       <c r="AF13" s="7"/>
@@ -14604,12 +15209,16 @@
       <c r="CR13" s="7"/>
       <c r="CS13" s="7"/>
       <c r="CT13" s="7"/>
-    </row>
-    <row r="14" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="94"/>
-      <c r="B14" s="95"/>
+      <c r="CU13" s="7"/>
+      <c r="CV13" s="7"/>
+      <c r="CW13" s="7"/>
+      <c r="CX13" s="7"/>
+    </row>
+    <row r="14" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="95"/>
+      <c r="B14" s="96"/>
       <c r="C14" s="83" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="38" t="str">
@@ -14638,46 +15247,49 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="M14" s="33"/>
-      <c r="N14" s="40" t="str">
+      <c r="M14" s="40"/>
+      <c r="N14" s="43" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O14" s="40"/>
-      <c r="P14" s="43" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
+      <c r="O14" s="33"/>
+      <c r="P14" s="40"/>
       <c r="Q14" s="40"/>
       <c r="R14" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S14" s="40"/>
       <c r="T14" s="43" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="U14" s="40"/>
+      <c r="V14" s="43" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="V14" s="67" t="str">
+      <c r="W14" s="40"/>
+      <c r="X14" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z14" s="67" t="str">
         <f t="shared" si="0"/>
         <v>O_Links Laterale middenvoet</v>
       </c>
-      <c r="W14" s="67" t="str">
+      <c r="AA14" s="67" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X14" s="67" t="str">
+      <c r="AB14" s="67" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y14" s="67">
+      <c r="AC14" s="67">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="Z14" s="7"/>
-      <c r="AA14" s="7"/>
-      <c r="AB14" s="7"/>
-      <c r="AC14" s="7"/>
       <c r="AD14" s="7"/>
       <c r="AE14" s="7"/>
       <c r="AF14" s="7"/>
@@ -14747,12 +15359,16 @@
       <c r="CR14" s="7"/>
       <c r="CS14" s="7"/>
       <c r="CT14" s="7"/>
-    </row>
-    <row r="15" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="94"/>
-      <c r="B15" s="95"/>
+      <c r="CU14" s="7"/>
+      <c r="CV14" s="7"/>
+      <c r="CW14" s="7"/>
+      <c r="CX14" s="7"/>
+    </row>
+    <row r="15" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="95"/>
+      <c r="B15" s="96"/>
       <c r="C15" s="83" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="38" t="str">
@@ -14781,46 +15397,49 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="M15" s="33"/>
-      <c r="N15" s="40" t="str">
+      <c r="M15" s="40"/>
+      <c r="N15" s="43" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O15" s="40"/>
-      <c r="P15" s="43" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
+      <c r="O15" s="33"/>
+      <c r="P15" s="40"/>
       <c r="Q15" s="40"/>
       <c r="R15" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S15" s="40"/>
       <c r="T15" s="43" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="U15" s="40"/>
+      <c r="V15" s="43" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="V15" s="67" t="str">
+      <c r="W15" s="40"/>
+      <c r="X15" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z15" s="67" t="str">
         <f t="shared" si="0"/>
         <v>P_Links Hiel</v>
       </c>
-      <c r="W15" s="67" t="str">
+      <c r="AA15" s="67" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X15" s="67" t="str">
+      <c r="AB15" s="67" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y15" s="67">
+      <c r="AC15" s="67">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="Z15" s="7"/>
-      <c r="AA15" s="7"/>
-      <c r="AB15" s="7"/>
-      <c r="AC15" s="7"/>
       <c r="AD15" s="7"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="7"/>
@@ -14890,12 +15509,16 @@
       <c r="CR15" s="7"/>
       <c r="CS15" s="7"/>
       <c r="CT15" s="7"/>
-    </row>
-    <row r="16" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="94"/>
-      <c r="B16" s="95"/>
+      <c r="CU15" s="7"/>
+      <c r="CV15" s="7"/>
+      <c r="CW15" s="7"/>
+      <c r="CX15" s="7"/>
+    </row>
+    <row r="16" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="95"/>
+      <c r="B16" s="96"/>
       <c r="C16" s="83" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="41" t="str">
@@ -14924,34 +15547,37 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="M16" s="33"/>
-      <c r="N16" s="40" t="str">
+      <c r="M16" s="40"/>
+      <c r="N16" s="43" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O16" s="40"/>
-      <c r="P16" s="43" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
+      <c r="O16" s="33"/>
+      <c r="P16" s="40"/>
       <c r="Q16" s="40"/>
       <c r="R16" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S16" s="40"/>
       <c r="T16" s="43" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="U16" s="40"/>
+      <c r="V16" s="43" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="V16" s="67"/>
-      <c r="W16" s="67"/>
-      <c r="X16" s="67"/>
-      <c r="Y16" s="67"/>
-      <c r="Z16" s="7"/>
-      <c r="AA16" s="7"/>
-      <c r="AB16" s="7"/>
-      <c r="AC16" s="7"/>
+      <c r="W16" s="40"/>
+      <c r="X16" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z16" s="67"/>
+      <c r="AA16" s="67"/>
+      <c r="AB16" s="67"/>
+      <c r="AC16" s="67"/>
       <c r="AD16" s="7"/>
       <c r="AE16" s="7"/>
       <c r="AF16" s="7"/>
@@ -15021,12 +15647,16 @@
       <c r="CR16" s="7"/>
       <c r="CS16" s="7"/>
       <c r="CT16" s="7"/>
-    </row>
-    <row r="17" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="94"/>
-      <c r="B17" s="95"/>
+      <c r="CU16" s="7"/>
+      <c r="CV16" s="7"/>
+      <c r="CW16" s="7"/>
+      <c r="CX16" s="7"/>
+    </row>
+    <row r="17" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="95"/>
+      <c r="B17" s="96"/>
       <c r="C17" s="83" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="41" t="str">
@@ -15055,34 +15685,37 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="M17" s="33"/>
-      <c r="N17" s="40" t="str">
+      <c r="M17" s="40"/>
+      <c r="N17" s="43" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O17" s="40"/>
-      <c r="P17" s="43" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
+      <c r="O17" s="33"/>
+      <c r="P17" s="40"/>
       <c r="Q17" s="40"/>
       <c r="R17" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S17" s="40"/>
       <c r="T17" s="43" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="U17" s="40"/>
+      <c r="V17" s="43" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="V17" s="67"/>
-      <c r="W17" s="67"/>
-      <c r="X17" s="67"/>
-      <c r="Y17" s="67"/>
-      <c r="Z17" s="7"/>
-      <c r="AA17" s="7"/>
-      <c r="AB17" s="7"/>
-      <c r="AC17" s="7"/>
+      <c r="W17" s="40"/>
+      <c r="X17" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z17" s="67"/>
+      <c r="AA17" s="67"/>
+      <c r="AB17" s="67"/>
+      <c r="AC17" s="67"/>
       <c r="AD17" s="7"/>
       <c r="AE17" s="7"/>
       <c r="AF17" s="7"/>
@@ -15152,12 +15785,16 @@
       <c r="CR17" s="7"/>
       <c r="CS17" s="7"/>
       <c r="CT17" s="7"/>
-    </row>
-    <row r="18" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="96"/>
-      <c r="B18" s="97"/>
+      <c r="CU17" s="7"/>
+      <c r="CV17" s="7"/>
+      <c r="CW17" s="7"/>
+      <c r="CX17" s="7"/>
+    </row>
+    <row r="18" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="97"/>
+      <c r="B18" s="98"/>
       <c r="C18" s="83" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D18" s="37"/>
       <c r="E18" s="41" t="str">
@@ -15186,36 +15823,39 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="M18" s="33"/>
-      <c r="N18" s="40" t="str">
+      <c r="M18" s="40"/>
+      <c r="N18" s="43" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O18" s="40"/>
-      <c r="P18" s="43" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
+      <c r="O18" s="33"/>
+      <c r="P18" s="40"/>
       <c r="Q18" s="40"/>
       <c r="R18" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S18" s="40"/>
       <c r="T18" s="43" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="U18" s="40"/>
+      <c r="V18" s="43" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="V18" s="68" t="s">
+      <c r="W18" s="40"/>
+      <c r="X18" s="43" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z18" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="W18" s="67"/>
-      <c r="X18" s="67"/>
-      <c r="Y18" s="67"/>
-      <c r="Z18" s="7"/>
-      <c r="AA18" s="7"/>
-      <c r="AB18" s="7"/>
-      <c r="AC18" s="7"/>
+      <c r="AA18" s="67"/>
+      <c r="AB18" s="67"/>
+      <c r="AC18" s="67"/>
       <c r="AD18" s="7"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="7"/>
@@ -15285,8 +15925,12 @@
       <c r="CR18" s="7"/>
       <c r="CS18" s="7"/>
       <c r="CT18" s="7"/>
-    </row>
-    <row r="19" spans="1:98" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="CU18" s="7"/>
+      <c r="CV18" s="7"/>
+      <c r="CW18" s="7"/>
+      <c r="CX18" s="7"/>
+    </row>
+    <row r="19" spans="1:102" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="21"/>
       <c r="B19" s="21"/>
       <c r="C19" s="48"/>
@@ -15299,30 +15943,30 @@
       <c r="J19" s="26"/>
       <c r="K19" s="26"/>
       <c r="L19" s="25"/>
-      <c r="M19" s="27"/>
-      <c r="N19" s="27"/>
+      <c r="M19" s="102"/>
+      <c r="N19" s="102"/>
       <c r="O19" s="27"/>
       <c r="P19" s="27"/>
       <c r="Q19" s="27"/>
       <c r="R19" s="27"/>
       <c r="S19" s="27"/>
-      <c r="T19" s="42"/>
-      <c r="V19" s="68" t="s">
+      <c r="T19" s="27"/>
+      <c r="U19" s="27"/>
+      <c r="V19" s="42"/>
+      <c r="W19" s="102"/>
+      <c r="X19" s="102"/>
+      <c r="Z19" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="W19" s="68" t="s">
+      <c r="AA19" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="X19" s="68" t="s">
+      <c r="AB19" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="Y19" s="68" t="s">
+      <c r="AC19" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="3"/>
-      <c r="AB19" s="3"/>
-      <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
@@ -15392,50 +16036,54 @@
       <c r="CR19" s="3"/>
       <c r="CS19" s="3"/>
       <c r="CT19" s="3"/>
-    </row>
-    <row r="20" spans="1:98" s="5" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="87" t="s">
-        <v>85</v>
-      </c>
-      <c r="B20" s="88"/>
-      <c r="C20" s="89"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="90"/>
-      <c r="G20" s="90"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="90"/>
-      <c r="J20" s="90"/>
-      <c r="K20" s="90"/>
-      <c r="L20" s="90"/>
-      <c r="M20" s="90"/>
-      <c r="N20" s="90"/>
-      <c r="O20" s="90"/>
-      <c r="P20" s="90"/>
-      <c r="Q20" s="90"/>
-      <c r="R20" s="90"/>
-      <c r="S20" s="90"/>
-      <c r="T20" s="90"/>
-      <c r="V20" s="67" t="str">
-        <f t="shared" ref="V20:V27" si="14">C27</f>
+      <c r="CU19" s="3"/>
+      <c r="CV19" s="3"/>
+      <c r="CW19" s="3"/>
+      <c r="CX19" s="3"/>
+    </row>
+    <row r="20" spans="1:102" s="5" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="100"/>
+      <c r="C20" s="106"/>
+      <c r="D20" s="107"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="107"/>
+      <c r="H20" s="107"/>
+      <c r="I20" s="107"/>
+      <c r="J20" s="107"/>
+      <c r="K20" s="107"/>
+      <c r="L20" s="107"/>
+      <c r="M20" s="107"/>
+      <c r="N20" s="107"/>
+      <c r="O20" s="107"/>
+      <c r="P20" s="107"/>
+      <c r="Q20" s="107"/>
+      <c r="R20" s="107"/>
+      <c r="S20" s="107"/>
+      <c r="T20" s="107"/>
+      <c r="U20" s="107"/>
+      <c r="V20" s="107"/>
+      <c r="W20" s="107"/>
+      <c r="X20" s="107"/>
+      <c r="Z20" s="67" t="str">
+        <f t="shared" ref="Z20:Z27" si="15">C27</f>
         <v>A_Rechts Hallux</v>
       </c>
-      <c r="W20" s="67" t="str">
-        <f t="shared" ref="W20:W27" si="15">E27</f>
-        <v/>
-      </c>
-      <c r="X20" s="67" t="str">
-        <f t="shared" ref="X20:X27" si="16">G27</f>
-        <v/>
-      </c>
-      <c r="Y20" s="67">
-        <f t="shared" ref="Y20:Y27" si="17">$Y$5</f>
+      <c r="AA20" s="67" t="str">
+        <f t="shared" ref="AA20:AA27" si="16">E27</f>
+        <v/>
+      </c>
+      <c r="AB20" s="67" t="str">
+        <f t="shared" ref="AB20:AB27" si="17">G27</f>
+        <v/>
+      </c>
+      <c r="AC20" s="67">
+        <f t="shared" ref="AC20:AC27" si="18">$AC$5</f>
         <v>200</v>
       </c>
-      <c r="Z20" s="7"/>
-      <c r="AA20" s="7"/>
-      <c r="AB20" s="7"/>
-      <c r="AC20" s="7"/>
       <c r="AD20" s="7"/>
       <c r="AE20" s="7"/>
       <c r="AF20" s="7"/>
@@ -15505,8 +16153,12 @@
       <c r="CR20" s="7"/>
       <c r="CS20" s="7"/>
       <c r="CT20" s="7"/>
-    </row>
-    <row r="21" spans="1:98" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="CU20" s="7"/>
+      <c r="CV20" s="7"/>
+      <c r="CW20" s="7"/>
+      <c r="CX20" s="7"/>
+    </row>
+    <row r="21" spans="1:102" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="19"/>
       <c r="B21" s="19"/>
       <c r="C21" s="28"/>
@@ -15526,27 +16178,27 @@
       <c r="Q21" s="30"/>
       <c r="R21" s="30"/>
       <c r="S21" s="30"/>
-      <c r="T21" s="32"/>
-      <c r="V21" s="67" t="str">
-        <f t="shared" si="14"/>
+      <c r="T21" s="30"/>
+      <c r="U21" s="30"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="105"/>
+      <c r="X21" s="105"/>
+      <c r="Z21" s="67" t="str">
+        <f t="shared" si="15"/>
         <v>B_Rechts Tenen 2-5</v>
       </c>
-      <c r="W21" s="67" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="X21" s="67" t="str">
+      <c r="AA21" s="67" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Y21" s="67">
+      <c r="AB21" s="67" t="str">
         <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AC21" s="67">
+        <f t="shared" si="18"/>
         <v>200</v>
       </c>
-      <c r="Z21" s="7"/>
-      <c r="AA21" s="7"/>
-      <c r="AB21" s="7"/>
-      <c r="AC21" s="7"/>
       <c r="AD21" s="7"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="7"/>
@@ -15616,8 +16268,12 @@
       <c r="CR21" s="7"/>
       <c r="CS21" s="7"/>
       <c r="CT21" s="7"/>
-    </row>
-    <row r="22" spans="1:98" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="CU21" s="7"/>
+      <c r="CV21" s="7"/>
+      <c r="CW21" s="7"/>
+      <c r="CX21" s="7"/>
+    </row>
+    <row r="22" spans="1:102" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22"/>
@@ -15638,26 +16294,26 @@
       <c r="R22"/>
       <c r="S22"/>
       <c r="T22"/>
-      <c r="V22" s="67" t="str">
-        <f t="shared" si="14"/>
+      <c r="U22"/>
+      <c r="V22"/>
+      <c r="W22"/>
+      <c r="X22"/>
+      <c r="Z22" s="67" t="str">
+        <f t="shared" si="15"/>
         <v>C_Rechts Metatarsaal 1</v>
       </c>
-      <c r="W22" s="67" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="X22" s="67" t="str">
+      <c r="AA22" s="67" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Y22" s="67">
+      <c r="AB22" s="67" t="str">
         <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AC22" s="67">
+        <f t="shared" si="18"/>
         <v>200</v>
       </c>
-      <c r="Z22" s="7"/>
-      <c r="AA22" s="7"/>
-      <c r="AB22" s="7"/>
-      <c r="AC22" s="7"/>
       <c r="AD22" s="7"/>
       <c r="AE22" s="7"/>
       <c r="AF22" s="7"/>
@@ -15727,8 +16383,12 @@
       <c r="CR22" s="7"/>
       <c r="CS22" s="7"/>
       <c r="CT22" s="7"/>
-    </row>
-    <row r="23" spans="1:98" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="CU22" s="7"/>
+      <c r="CV22" s="7"/>
+      <c r="CW22" s="7"/>
+      <c r="CX22" s="7"/>
+    </row>
+    <row r="23" spans="1:102" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23"/>
       <c r="B23"/>
       <c r="C23"/>
@@ -15749,26 +16409,26 @@
       <c r="R23"/>
       <c r="S23"/>
       <c r="T23"/>
-      <c r="V23" s="67" t="str">
-        <f t="shared" si="14"/>
+      <c r="U23"/>
+      <c r="V23"/>
+      <c r="W23"/>
+      <c r="X23"/>
+      <c r="Z23" s="67" t="str">
+        <f t="shared" si="15"/>
         <v>D_Rechts Metatarsaal 2-3</v>
       </c>
-      <c r="W23" s="67" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="X23" s="67" t="str">
+      <c r="AA23" s="67" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Y23" s="67">
+      <c r="AB23" s="67" t="str">
         <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AC23" s="67">
+        <f t="shared" si="18"/>
         <v>200</v>
       </c>
-      <c r="Z23" s="7"/>
-      <c r="AA23" s="7"/>
-      <c r="AB23" s="7"/>
-      <c r="AC23" s="7"/>
       <c r="AD23" s="7"/>
       <c r="AE23" s="7"/>
       <c r="AF23" s="7"/>
@@ -15838,52 +16498,56 @@
       <c r="CR23" s="7"/>
       <c r="CS23" s="7"/>
       <c r="CT23" s="7"/>
-    </row>
-    <row r="24" spans="1:98" s="5" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="CU23" s="7"/>
+      <c r="CV23" s="7"/>
+      <c r="CW23" s="7"/>
+      <c r="CX23" s="7"/>
+    </row>
+    <row r="24" spans="1:102" s="5" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24"/>
       <c r="B24"/>
       <c r="C24"/>
-      <c r="D24" s="98" t="s">
-        <v>80</v>
-      </c>
-      <c r="E24" s="99"/>
-      <c r="F24" s="99"/>
-      <c r="G24" s="99"/>
-      <c r="H24" s="99"/>
-      <c r="I24" s="99"/>
-      <c r="J24" s="99"/>
-      <c r="K24" s="99"/>
-      <c r="L24" s="100"/>
-      <c r="M24"/>
-      <c r="N24" s="98" t="s">
-        <v>81</v>
-      </c>
-      <c r="O24" s="99"/>
-      <c r="P24" s="99"/>
-      <c r="Q24" s="99"/>
-      <c r="R24" s="99"/>
-      <c r="S24" s="99"/>
-      <c r="T24" s="100"/>
-      <c r="V24" s="67" t="str">
-        <f t="shared" si="14"/>
+      <c r="D24" s="103" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="104"/>
+      <c r="F24" s="104"/>
+      <c r="G24" s="104"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="104"/>
+      <c r="J24" s="104"/>
+      <c r="K24" s="104"/>
+      <c r="L24" s="104"/>
+      <c r="M24" s="104"/>
+      <c r="N24" s="104"/>
+      <c r="O24"/>
+      <c r="P24" s="103" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q24" s="104"/>
+      <c r="R24" s="104"/>
+      <c r="S24" s="104"/>
+      <c r="T24" s="104"/>
+      <c r="U24" s="104"/>
+      <c r="V24" s="104"/>
+      <c r="W24" s="104"/>
+      <c r="X24" s="104"/>
+      <c r="Z24" s="67" t="str">
+        <f t="shared" si="15"/>
         <v>E_Rechts Metatarsaal 4-5</v>
       </c>
-      <c r="W24" s="67" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="X24" s="67" t="str">
+      <c r="AA24" s="67" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Y24" s="67">
+      <c r="AB24" s="67" t="str">
         <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AC24" s="67">
+        <f t="shared" si="18"/>
         <v>200</v>
       </c>
-      <c r="Z24" s="7"/>
-      <c r="AA24" s="7"/>
-      <c r="AB24" s="7"/>
-      <c r="AC24" s="7"/>
       <c r="AD24" s="7"/>
       <c r="AE24" s="7"/>
       <c r="AF24" s="7"/>
@@ -15953,12 +16617,16 @@
       <c r="CR24" s="7"/>
       <c r="CS24" s="7"/>
       <c r="CT24" s="7"/>
-    </row>
-    <row r="25" spans="1:98" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="92" t="s">
+      <c r="CU24" s="7"/>
+      <c r="CV24" s="7"/>
+      <c r="CW24" s="7"/>
+      <c r="CX24" s="7"/>
+    </row>
+    <row r="25" spans="1:102" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="93"/>
+      <c r="B25" s="94"/>
       <c r="C25" s="34"/>
       <c r="D25" s="35"/>
       <c r="E25" s="60" t="s">
@@ -15967,54 +16635,58 @@
       <c r="F25" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="G25" s="85" t="s">
+      <c r="G25" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="86"/>
-      <c r="I25" s="85" t="s">
+      <c r="H25" s="89"/>
+      <c r="I25" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="J25" s="86"/>
-      <c r="K25" s="85" t="s">
+      <c r="J25" s="89"/>
+      <c r="K25" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="L25" s="86"/>
-      <c r="M25" s="62"/>
-      <c r="N25" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="O25" s="85" t="s">
+      <c r="L25" s="89"/>
+      <c r="M25" s="88" t="s">
+        <v>107</v>
+      </c>
+      <c r="N25" s="89"/>
+      <c r="O25" s="62"/>
+      <c r="P25" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q25" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="P25" s="86"/>
-      <c r="Q25" s="85" t="s">
+      <c r="R25" s="89"/>
+      <c r="S25" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="R25" s="86"/>
-      <c r="S25" s="85" t="s">
+      <c r="T25" s="89"/>
+      <c r="U25" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="T25" s="86"/>
-      <c r="V25" s="67" t="str">
-        <f t="shared" si="14"/>
+      <c r="V25" s="89"/>
+      <c r="W25" s="88" t="s">
+        <v>107</v>
+      </c>
+      <c r="X25" s="89"/>
+      <c r="Z25" s="67" t="str">
+        <f t="shared" si="15"/>
         <v>F_Rechts Mediale middenvoet</v>
       </c>
-      <c r="W25" s="67" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="X25" s="67" t="str">
+      <c r="AA25" s="67" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Y25" s="67">
+      <c r="AB25" s="67" t="str">
         <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AC25" s="67">
+        <f t="shared" si="18"/>
         <v>200</v>
       </c>
-      <c r="Z25" s="7"/>
-      <c r="AA25" s="7"/>
-      <c r="AB25" s="7"/>
-      <c r="AC25" s="7"/>
       <c r="AD25" s="7"/>
       <c r="AE25" s="7"/>
       <c r="AF25" s="7"/>
@@ -16084,17 +16756,21 @@
       <c r="CR25" s="7"/>
       <c r="CS25" s="7"/>
       <c r="CT25" s="7"/>
-    </row>
-    <row r="26" spans="1:98" s="5" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="94"/>
-      <c r="B26" s="95"/>
+      <c r="CU25" s="7"/>
+      <c r="CV25" s="7"/>
+      <c r="CW25" s="7"/>
+      <c r="CX25" s="7"/>
+    </row>
+    <row r="26" spans="1:102" s="5" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="95"/>
+      <c r="B26" s="96"/>
       <c r="C26" s="34"/>
       <c r="D26" s="35"/>
       <c r="E26" s="36" t="s">
         <v>1</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="G26" s="36" t="s">
         <v>1</v>
@@ -16114,48 +16790,56 @@
       <c r="L26" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="M26" s="62"/>
+      <c r="M26" s="36" t="s">
+        <v>1</v>
+      </c>
       <c r="N26" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="O26" s="62"/>
+      <c r="P26" s="36" t="s">
         <v>1</v>
-      </c>
-      <c r="O26" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="P26" s="36" t="s">
-        <v>83</v>
       </c>
       <c r="Q26" s="36" t="s">
         <v>1</v>
       </c>
       <c r="R26" s="36" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="S26" s="36" t="s">
         <v>1</v>
       </c>
       <c r="T26" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="V26" s="7" t="str">
-        <f t="shared" si="14"/>
+        <v>109</v>
+      </c>
+      <c r="U26" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="V26" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="W26" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="X26" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z26" s="7" t="str">
+        <f t="shared" si="15"/>
         <v>G_Rechts Laterale middenvoet</v>
       </c>
-      <c r="W26" s="7" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="X26" s="7" t="str">
+      <c r="AA26" s="7" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Y26" s="7">
+      <c r="AB26" s="7" t="str">
         <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AC26" s="7">
+        <f t="shared" si="18"/>
         <v>200</v>
       </c>
-      <c r="Z26" s="7"/>
-      <c r="AA26" s="7"/>
-      <c r="AB26" s="7"/>
-      <c r="AC26" s="7"/>
       <c r="AD26" s="7"/>
       <c r="AE26" s="7"/>
       <c r="AF26" s="7"/>
@@ -16225,80 +16909,87 @@
       <c r="CR26" s="7"/>
       <c r="CS26" s="7"/>
       <c r="CT26" s="7"/>
-    </row>
-    <row r="27" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="94"/>
-      <c r="B27" s="95"/>
+      <c r="CU26" s="7"/>
+      <c r="CV26" s="7"/>
+      <c r="CW26" s="7"/>
+      <c r="CX26" s="7"/>
+    </row>
+    <row r="27" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="95"/>
+      <c r="B27" s="96"/>
       <c r="C27" s="83" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D27" s="37"/>
       <c r="E27" s="38" t="str">
-        <f t="shared" ref="E27:E34" si="18">IF(J47="","",J47)</f>
+        <f t="shared" ref="E27:E34" si="19">IF(J47="","",J47)</f>
         <v/>
       </c>
       <c r="F27" s="39" t="str">
-        <f t="shared" ref="F27:F33" si="19">IF($C$36=C27,"TARGET",IF(E27="","",IF(AND(E27&gt;200,RANK(E27,$E$27:$E$33)&lt;=2),"TARGET","")))</f>
+        <f t="shared" ref="F27:F33" si="20">IF($C$36=C27,"TARGET",IF(E27="","",IF(AND(E27&gt;200,RANK(E27,$E$27:$E$33)&lt;=2),"TARGET","")))</f>
         <v/>
       </c>
       <c r="G27" s="40" t="str">
-        <f t="shared" ref="G27:G34" si="20">IF(J68="","",J68)</f>
+        <f t="shared" ref="G27:G34" si="21">IF(J68="","",J68)</f>
         <v/>
       </c>
       <c r="H27" s="43" t="str">
-        <f t="shared" ref="H27:H34" si="21">IF(OR($E27="",G27=""),"",((G27-$E27)/$E27)*100)</f>
+        <f t="shared" ref="H27:H34" si="22">IF(OR($E27="",G27=""),"",((G27-$E27)/$E27)*100)</f>
         <v/>
       </c>
       <c r="I27" s="40"/>
       <c r="J27" s="43" t="str">
-        <f t="shared" ref="J27:J34" si="22">IF(OR($E27="",I27=""),"",((I27-$E27)/$E27)*100)</f>
+        <f t="shared" ref="J27:J34" si="23">IF(OR($E27="",I27=""),"",((I27-$E27)/$E27)*100)</f>
         <v/>
       </c>
       <c r="K27" s="40"/>
       <c r="L27" s="43" t="str">
-        <f t="shared" ref="L27:L34" si="23">IF(OR($E27="",K27=""),"",((K27-$E27)/$E27)*100)</f>
-        <v/>
-      </c>
-      <c r="M27" s="33"/>
-      <c r="N27" s="40" t="str">
-        <f t="shared" ref="N27:N34" si="24">IF(E27="","",E27)</f>
-        <v/>
-      </c>
-      <c r="O27" s="40"/>
-      <c r="P27" s="43" t="str">
-        <f t="shared" ref="P27:P34" si="25">IF(OR($N27="",O27=""),"",((O27-$N27)/$N27)*100)</f>
-        <v/>
-      </c>
+        <f t="shared" ref="L27:L34" si="24">IF(OR($E27="",K27=""),"",((K27-$E27)/$E27)*100)</f>
+        <v/>
+      </c>
+      <c r="M27" s="40"/>
+      <c r="N27" s="43" t="str">
+        <f t="shared" ref="N27:N34" si="25">IF(OR($E27="",M27=""),"",((M27-$E27)/$E27)*100)</f>
+        <v/>
+      </c>
+      <c r="O27" s="33"/>
+      <c r="P27" s="40"/>
       <c r="Q27" s="40"/>
       <c r="R27" s="43" t="str">
-        <f t="shared" ref="R27:R34" si="26">IF(OR($N27="",Q27=""),"",((Q27-$N27)/$N27)*100)</f>
+        <f t="shared" ref="R27:R34" si="26">IF(OR($P27="",Q27=""),"",((Q27-$P27)/$P27)*100)</f>
         <v/>
       </c>
       <c r="S27" s="40"/>
       <c r="T27" s="43" t="str">
-        <f t="shared" ref="T27:T34" si="27">IF(OR($N27="",S27=""),"",((S27-$N27)/$N27)*100)</f>
-        <v/>
-      </c>
-      <c r="V27" s="7" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="T27:T34" si="27">IF(OR($P27="",S27=""),"",((S27-$P27)/$P27)*100)</f>
+        <v/>
+      </c>
+      <c r="U27" s="40"/>
+      <c r="V27" s="43" t="str">
+        <f t="shared" ref="V27:V34" si="28">IF(OR($P27="",U27=""),"",((U27-$P27)/$P27)*100)</f>
+        <v/>
+      </c>
+      <c r="W27" s="40"/>
+      <c r="X27" s="43" t="str">
+        <f t="shared" ref="X27:X34" si="29">IF(OR($P27="",W27=""),"",((W27-$P27)/$P27)*100)</f>
+        <v/>
+      </c>
+      <c r="Z27" s="7" t="str">
+        <f t="shared" si="15"/>
         <v>H_Rechts Hiel</v>
       </c>
-      <c r="W27" s="7" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="X27" s="7" t="str">
+      <c r="AA27" s="7" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Y27" s="7">
+      <c r="AB27" s="7" t="str">
         <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AC27" s="7">
+        <f t="shared" si="18"/>
         <v>200</v>
       </c>
-      <c r="Z27" s="7"/>
-      <c r="AA27" s="7"/>
-      <c r="AB27" s="7"/>
-      <c r="AC27" s="7"/>
       <c r="AD27" s="7"/>
       <c r="AE27" s="7"/>
       <c r="AF27" s="7"/>
@@ -16368,50 +17059,51 @@
       <c r="CR27" s="7"/>
       <c r="CS27" s="7"/>
       <c r="CT27" s="7"/>
-    </row>
-    <row r="28" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="94"/>
-      <c r="B28" s="95"/>
+      <c r="CU27" s="7"/>
+      <c r="CV27" s="7"/>
+      <c r="CW27" s="7"/>
+      <c r="CX27" s="7"/>
+    </row>
+    <row r="28" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="95"/>
+      <c r="B28" s="96"/>
       <c r="C28" s="83" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D28" s="37"/>
       <c r="E28" s="38" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="F28" s="39" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G28" s="40" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H28" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I28" s="40"/>
       <c r="J28" s="43" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K28" s="40"/>
       <c r="L28" s="43" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M28" s="33"/>
-      <c r="N28" s="40" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="O28" s="40"/>
-      <c r="P28" s="43" t="str">
+      <c r="M28" s="40"/>
+      <c r="N28" s="43" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
+      <c r="O28" s="33"/>
+      <c r="P28" s="40"/>
       <c r="Q28" s="40"/>
       <c r="R28" s="43" t="str">
         <f t="shared" si="26"/>
@@ -16422,10 +17114,16 @@
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="V28" s="7"/>
-      <c r="W28" s="7"/>
-      <c r="X28" s="7"/>
-      <c r="Y28" s="7"/>
+      <c r="U28" s="40"/>
+      <c r="V28" s="43" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="W28" s="40"/>
+      <c r="X28" s="43" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
       <c r="Z28" s="7"/>
       <c r="AA28" s="7"/>
       <c r="AB28" s="7"/>
@@ -16499,50 +17197,51 @@
       <c r="CR28" s="7"/>
       <c r="CS28" s="7"/>
       <c r="CT28" s="7"/>
-    </row>
-    <row r="29" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="94"/>
-      <c r="B29" s="95"/>
+      <c r="CU28" s="7"/>
+      <c r="CV28" s="7"/>
+      <c r="CW28" s="7"/>
+      <c r="CX28" s="7"/>
+    </row>
+    <row r="29" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="95"/>
+      <c r="B29" s="96"/>
       <c r="C29" s="83" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D29" s="37"/>
       <c r="E29" s="38" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="F29" s="39" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G29" s="40" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H29" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I29" s="40"/>
       <c r="J29" s="43" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K29" s="40"/>
       <c r="L29" s="43" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M29" s="33"/>
-      <c r="N29" s="40" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="O29" s="40"/>
-      <c r="P29" s="43" t="str">
+      <c r="M29" s="40"/>
+      <c r="N29" s="43" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
+      <c r="O29" s="33"/>
+      <c r="P29" s="40"/>
       <c r="Q29" s="40"/>
       <c r="R29" s="43" t="str">
         <f t="shared" si="26"/>
@@ -16553,10 +17252,16 @@
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="V29" s="7"/>
-      <c r="W29" s="7"/>
-      <c r="X29" s="7"/>
-      <c r="Y29" s="7"/>
+      <c r="U29" s="40"/>
+      <c r="V29" s="43" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="W29" s="40"/>
+      <c r="X29" s="43" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
       <c r="Z29" s="7"/>
       <c r="AA29" s="7"/>
       <c r="AB29" s="7"/>
@@ -16630,50 +17335,51 @@
       <c r="CR29" s="7"/>
       <c r="CS29" s="7"/>
       <c r="CT29" s="7"/>
-    </row>
-    <row r="30" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="94"/>
-      <c r="B30" s="95"/>
+      <c r="CU29" s="7"/>
+      <c r="CV29" s="7"/>
+      <c r="CW29" s="7"/>
+      <c r="CX29" s="7"/>
+    </row>
+    <row r="30" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="95"/>
+      <c r="B30" s="96"/>
       <c r="C30" s="83" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D30" s="37"/>
       <c r="E30" s="38" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="F30" s="39" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G30" s="40" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H30" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I30" s="40"/>
       <c r="J30" s="43" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K30" s="40"/>
       <c r="L30" s="43" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M30" s="33"/>
-      <c r="N30" s="40" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="O30" s="40"/>
-      <c r="P30" s="43" t="str">
+      <c r="M30" s="40"/>
+      <c r="N30" s="43" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
+      <c r="O30" s="33"/>
+      <c r="P30" s="40"/>
       <c r="Q30" s="40"/>
       <c r="R30" s="43" t="str">
         <f t="shared" si="26"/>
@@ -16684,10 +17390,16 @@
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="V30" s="7"/>
-      <c r="W30" s="7"/>
-      <c r="X30" s="7"/>
-      <c r="Y30" s="7"/>
+      <c r="U30" s="40"/>
+      <c r="V30" s="43" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="W30" s="40"/>
+      <c r="X30" s="43" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
       <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
       <c r="AB30" s="7"/>
@@ -16761,50 +17473,51 @@
       <c r="CR30" s="7"/>
       <c r="CS30" s="7"/>
       <c r="CT30" s="7"/>
-    </row>
-    <row r="31" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="94"/>
-      <c r="B31" s="95"/>
+      <c r="CU30" s="7"/>
+      <c r="CV30" s="7"/>
+      <c r="CW30" s="7"/>
+      <c r="CX30" s="7"/>
+    </row>
+    <row r="31" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="95"/>
+      <c r="B31" s="96"/>
       <c r="C31" s="83" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D31" s="37"/>
       <c r="E31" s="38" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="F31" s="39" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G31" s="40" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H31" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I31" s="40"/>
       <c r="J31" s="43" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K31" s="40"/>
       <c r="L31" s="43" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M31" s="33"/>
-      <c r="N31" s="40" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="O31" s="40"/>
-      <c r="P31" s="43" t="str">
+      <c r="M31" s="40"/>
+      <c r="N31" s="43" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
+      <c r="O31" s="33"/>
+      <c r="P31" s="40"/>
       <c r="Q31" s="40"/>
       <c r="R31" s="43" t="str">
         <f t="shared" si="26"/>
@@ -16815,10 +17528,16 @@
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="V31" s="7"/>
-      <c r="W31" s="7"/>
-      <c r="X31" s="7"/>
-      <c r="Y31" s="7"/>
+      <c r="U31" s="40"/>
+      <c r="V31" s="43" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="W31" s="40"/>
+      <c r="X31" s="43" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
       <c r="Z31" s="7"/>
       <c r="AA31" s="7"/>
       <c r="AB31" s="7"/>
@@ -16892,50 +17611,51 @@
       <c r="CR31" s="7"/>
       <c r="CS31" s="7"/>
       <c r="CT31" s="7"/>
-    </row>
-    <row r="32" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="94"/>
-      <c r="B32" s="95"/>
+      <c r="CU31" s="7"/>
+      <c r="CV31" s="7"/>
+      <c r="CW31" s="7"/>
+      <c r="CX31" s="7"/>
+    </row>
+    <row r="32" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="95"/>
+      <c r="B32" s="96"/>
       <c r="C32" s="83" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D32" s="37"/>
       <c r="E32" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="F32" s="39" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G32" s="40" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H32" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I32" s="40"/>
       <c r="J32" s="43" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K32" s="40"/>
       <c r="L32" s="43" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M32" s="33"/>
-      <c r="N32" s="40" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="O32" s="40"/>
-      <c r="P32" s="43" t="str">
+      <c r="M32" s="40"/>
+      <c r="N32" s="43" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
+      <c r="O32" s="33"/>
+      <c r="P32" s="40"/>
       <c r="Q32" s="40"/>
       <c r="R32" s="43" t="str">
         <f t="shared" si="26"/>
@@ -16946,10 +17666,16 @@
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="V32" s="7"/>
-      <c r="W32" s="7"/>
-      <c r="X32" s="7"/>
-      <c r="Y32" s="7"/>
+      <c r="U32" s="40"/>
+      <c r="V32" s="43" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="W32" s="40"/>
+      <c r="X32" s="43" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
       <c r="Z32" s="7"/>
       <c r="AA32" s="7"/>
       <c r="AB32" s="7"/>
@@ -17023,50 +17749,51 @@
       <c r="CR32" s="7"/>
       <c r="CS32" s="7"/>
       <c r="CT32" s="7"/>
-    </row>
-    <row r="33" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="94"/>
-      <c r="B33" s="95"/>
+      <c r="CU32" s="7"/>
+      <c r="CV32" s="7"/>
+      <c r="CW32" s="7"/>
+      <c r="CX32" s="7"/>
+    </row>
+    <row r="33" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="95"/>
+      <c r="B33" s="96"/>
       <c r="C33" s="83" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D33" s="37"/>
       <c r="E33" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="F33" s="39" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G33" s="40" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H33" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I33" s="40"/>
       <c r="J33" s="43" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K33" s="40"/>
       <c r="L33" s="43" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M33" s="33"/>
-      <c r="N33" s="40" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="O33" s="40"/>
-      <c r="P33" s="43" t="str">
+      <c r="M33" s="40"/>
+      <c r="N33" s="43" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
+      <c r="O33" s="33"/>
+      <c r="P33" s="40"/>
       <c r="Q33" s="40"/>
       <c r="R33" s="43" t="str">
         <f t="shared" si="26"/>
@@ -17077,10 +17804,16 @@
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="V33" s="7"/>
-      <c r="W33" s="7"/>
-      <c r="X33" s="7"/>
-      <c r="Y33" s="7"/>
+      <c r="U33" s="40"/>
+      <c r="V33" s="43" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="W33" s="40"/>
+      <c r="X33" s="43" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
       <c r="Z33" s="7"/>
       <c r="AA33" s="7"/>
       <c r="AB33" s="7"/>
@@ -17154,16 +17887,20 @@
       <c r="CR33" s="7"/>
       <c r="CS33" s="7"/>
       <c r="CT33" s="7"/>
-    </row>
-    <row r="34" spans="1:98" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="96"/>
-      <c r="B34" s="97"/>
+      <c r="CU33" s="7"/>
+      <c r="CV33" s="7"/>
+      <c r="CW33" s="7"/>
+      <c r="CX33" s="7"/>
+    </row>
+    <row r="34" spans="1:102" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="97"/>
+      <c r="B34" s="98"/>
       <c r="C34" s="83" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D34" s="37"/>
       <c r="E34" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="F34" s="39" t="str">
@@ -17171,33 +17908,30 @@
         <v/>
       </c>
       <c r="G34" s="40" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H34" s="43" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I34" s="40"/>
       <c r="J34" s="43" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K34" s="40"/>
       <c r="L34" s="43" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="M34" s="33"/>
-      <c r="N34" s="40" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="O34" s="40"/>
-      <c r="P34" s="43" t="str">
+      <c r="M34" s="40"/>
+      <c r="N34" s="43" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
+      <c r="O34" s="33"/>
+      <c r="P34" s="40"/>
       <c r="Q34" s="40"/>
       <c r="R34" s="43" t="str">
         <f t="shared" si="26"/>
@@ -17208,10 +17942,16 @@
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="V34" s="7"/>
-      <c r="W34" s="7"/>
-      <c r="X34" s="7"/>
-      <c r="Y34" s="7"/>
+      <c r="U34" s="40"/>
+      <c r="V34" s="43" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="W34" s="40"/>
+      <c r="X34" s="43" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
       <c r="Z34" s="7"/>
       <c r="AA34" s="7"/>
       <c r="AB34" s="7"/>
@@ -17285,8 +18025,12 @@
       <c r="CR34" s="7"/>
       <c r="CS34" s="7"/>
       <c r="CT34" s="7"/>
-    </row>
-    <row r="35" spans="1:98" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="CU34" s="7"/>
+      <c r="CV34" s="7"/>
+      <c r="CW34" s="7"/>
+      <c r="CX34" s="7"/>
+    </row>
+    <row r="35" spans="1:102" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="21"/>
       <c r="B35" s="21"/>
       <c r="C35" s="48"/>
@@ -17299,18 +18043,18 @@
       <c r="J35" s="26"/>
       <c r="K35" s="26"/>
       <c r="L35" s="25"/>
-      <c r="M35" s="27"/>
-      <c r="N35" s="27"/>
+      <c r="M35" s="102"/>
+      <c r="N35" s="102"/>
       <c r="O35" s="27"/>
       <c r="P35" s="27"/>
       <c r="Q35" s="27"/>
       <c r="R35" s="27"/>
       <c r="S35" s="27"/>
       <c r="T35" s="27"/>
-      <c r="V35" s="3"/>
-      <c r="W35" s="3"/>
-      <c r="X35" s="3"/>
-      <c r="Y35" s="3"/>
+      <c r="U35" s="27"/>
+      <c r="V35" s="27"/>
+      <c r="W35" s="27"/>
+      <c r="X35" s="27"/>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3"/>
       <c r="AB35" s="3"/>
@@ -17384,34 +18128,38 @@
       <c r="CR35" s="3"/>
       <c r="CS35" s="3"/>
       <c r="CT35" s="3"/>
-    </row>
-    <row r="36" spans="1:98" s="5" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="87" t="s">
-        <v>86</v>
-      </c>
-      <c r="B36" s="88"/>
-      <c r="C36" s="89"/>
-      <c r="D36" s="90"/>
-      <c r="E36" s="90"/>
-      <c r="F36" s="90"/>
-      <c r="G36" s="90"/>
-      <c r="H36" s="90"/>
-      <c r="I36" s="90"/>
-      <c r="J36" s="90"/>
-      <c r="K36" s="90"/>
-      <c r="L36" s="90"/>
-      <c r="M36" s="90"/>
-      <c r="N36" s="90"/>
-      <c r="O36" s="90"/>
-      <c r="P36" s="90"/>
-      <c r="Q36" s="90"/>
-      <c r="R36" s="90"/>
-      <c r="S36" s="90"/>
-      <c r="T36" s="91"/>
-      <c r="V36" s="7"/>
-      <c r="W36" s="7"/>
-      <c r="X36" s="7"/>
-      <c r="Y36" s="7"/>
+      <c r="CU35" s="3"/>
+      <c r="CV35" s="3"/>
+      <c r="CW35" s="3"/>
+      <c r="CX35" s="3"/>
+    </row>
+    <row r="36" spans="1:102" s="5" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="99" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="100"/>
+      <c r="C36" s="106"/>
+      <c r="D36" s="107"/>
+      <c r="E36" s="107"/>
+      <c r="F36" s="107"/>
+      <c r="G36" s="107"/>
+      <c r="H36" s="107"/>
+      <c r="I36" s="107"/>
+      <c r="J36" s="107"/>
+      <c r="K36" s="107"/>
+      <c r="L36" s="107"/>
+      <c r="M36" s="107"/>
+      <c r="N36" s="107"/>
+      <c r="O36" s="107"/>
+      <c r="P36" s="107"/>
+      <c r="Q36" s="107"/>
+      <c r="R36" s="107"/>
+      <c r="S36" s="107"/>
+      <c r="T36" s="107"/>
+      <c r="U36" s="107"/>
+      <c r="V36" s="107"/>
+      <c r="W36" s="107"/>
+      <c r="X36" s="107"/>
       <c r="Z36" s="7"/>
       <c r="AA36" s="7"/>
       <c r="AB36" s="7"/>
@@ -17485,8 +18233,12 @@
       <c r="CR36" s="7"/>
       <c r="CS36" s="7"/>
       <c r="CT36" s="7"/>
-    </row>
-    <row r="37" spans="1:98" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="CU36" s="7"/>
+      <c r="CV36" s="7"/>
+      <c r="CW36" s="7"/>
+      <c r="CX36" s="7"/>
+    </row>
+    <row r="37" spans="1:102" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="19"/>
       <c r="B37" s="19"/>
       <c r="C37" s="28"/>
@@ -17507,10 +18259,10 @@
       <c r="R37" s="30"/>
       <c r="S37" s="30"/>
       <c r="T37" s="30"/>
-      <c r="V37" s="7"/>
-      <c r="W37" s="7"/>
-      <c r="X37" s="7"/>
-      <c r="Y37" s="7"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="105"/>
+      <c r="X37" s="105"/>
       <c r="Z37" s="7"/>
       <c r="AA37" s="7"/>
       <c r="AB37" s="7"/>
@@ -17584,13 +18336,17 @@
       <c r="CR37" s="7"/>
       <c r="CS37" s="7"/>
       <c r="CT37" s="7"/>
-    </row>
-    <row r="39" spans="1:98" ht="16" x14ac:dyDescent="0.4">
+      <c r="CU37" s="7"/>
+      <c r="CV37" s="7"/>
+      <c r="CW37" s="7"/>
+      <c r="CX37" s="7"/>
+    </row>
+    <row r="39" spans="1:102" ht="16" x14ac:dyDescent="0.4">
       <c r="A39" s="45" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:98" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A40" s="53"/>
       <c r="B40" s="47"/>
       <c r="C40" s="47"/>
@@ -17611,10 +18367,14 @@
       <c r="R40" s="47"/>
       <c r="S40" s="47"/>
       <c r="T40" s="47"/>
-    </row>
-    <row r="41" spans="1:98" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="U40" s="47"/>
+      <c r="V40" s="47"/>
+      <c r="W40" s="47"/>
+      <c r="X40" s="47"/>
+    </row>
+    <row r="41" spans="1:102" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="54" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B41" s="50"/>
       <c r="C41" s="50"/>
@@ -17635,10 +18395,10 @@
       <c r="R41" s="50"/>
       <c r="S41" s="50"/>
       <c r="T41" s="50"/>
-      <c r="U41" s="9"/>
-      <c r="V41" s="9"/>
-      <c r="W41" s="9"/>
-      <c r="X41" s="9"/>
+      <c r="U41" s="50"/>
+      <c r="V41" s="50"/>
+      <c r="W41" s="50"/>
+      <c r="X41" s="50"/>
       <c r="Y41" s="9"/>
       <c r="Z41" s="9"/>
       <c r="AA41" s="9"/>
@@ -17713,8 +18473,12 @@
       <c r="CR41" s="9"/>
       <c r="CS41" s="9"/>
       <c r="CT41" s="9"/>
-    </row>
-    <row r="42" spans="1:98" x14ac:dyDescent="0.35">
+      <c r="CU41" s="9"/>
+      <c r="CV41" s="9"/>
+      <c r="CW41" s="9"/>
+      <c r="CX41" s="9"/>
+    </row>
+    <row r="42" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A42" s="53"/>
       <c r="B42" s="47"/>
       <c r="C42" s="47"/>
@@ -17735,10 +18499,14 @@
       <c r="R42" s="47"/>
       <c r="S42" s="47"/>
       <c r="T42" s="47"/>
-    </row>
-    <row r="43" spans="1:98" x14ac:dyDescent="0.35">
+      <c r="U42" s="47"/>
+      <c r="V42" s="47"/>
+      <c r="W42" s="47"/>
+      <c r="X42" s="47"/>
+    </row>
+    <row r="43" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A43" s="55" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="B43" s="50"/>
       <c r="C43" s="50"/>
@@ -17754,20 +18522,24 @@
       <c r="M43" s="50"/>
       <c r="N43" s="50"/>
       <c r="O43" s="50"/>
-      <c r="P43" s="47"/>
-      <c r="Q43" s="47"/>
+      <c r="P43" s="50"/>
+      <c r="Q43" s="50"/>
       <c r="R43" s="47"/>
       <c r="S43" s="47"/>
       <c r="T43" s="47"/>
-    </row>
-    <row r="45" spans="1:98" ht="16" x14ac:dyDescent="0.4">
+      <c r="U43" s="47"/>
+      <c r="V43" s="47"/>
+      <c r="W43" s="47"/>
+      <c r="X43" s="47"/>
+    </row>
+    <row r="45" spans="1:102" ht="16" x14ac:dyDescent="0.4">
       <c r="A45" s="45" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="46" spans="1:98" ht="43.5" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:102" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A46" s="44" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -17781,11 +18553,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:98" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -17795,11 +18567,11 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
     </row>
-    <row r="48" spans="1:98" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -17813,7 +18585,7 @@
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -17827,7 +18599,7 @@
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -17841,7 +18613,7 @@
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -17855,7 +18627,7 @@
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -17869,7 +18641,7 @@
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -17883,7 +18655,7 @@
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -17916,7 +18688,7 @@
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B57" s="1"/>
       <c r="C57" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -17929,7 +18701,7 @@
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B58" s="1"/>
       <c r="C58" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -17942,7 +18714,7 @@
     <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B59" s="1"/>
       <c r="C59" s="1" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -17955,7 +18727,7 @@
     <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B60" s="1"/>
       <c r="C60" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -17968,7 +18740,7 @@
     <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B61" s="1"/>
       <c r="C61" s="1" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -17980,7 +18752,7 @@
     </row>
     <row r="62" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C62" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -17992,7 +18764,7 @@
     </row>
     <row r="63" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C63" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -18004,7 +18776,7 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C64" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -18016,12 +18788,12 @@
     </row>
     <row r="66" spans="1:10" ht="16" x14ac:dyDescent="0.4">
       <c r="A66" s="45" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" s="44" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="J67" s="12" t="s">
         <v>1</v>
@@ -18029,7 +18801,7 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C68" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
@@ -18041,7 +18813,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C69" s="1" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -18053,7 +18825,7 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C70" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -18065,7 +18837,7 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C71" s="1" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -18077,7 +18849,7 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C72" s="1" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -18089,7 +18861,7 @@
     </row>
     <row r="73" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C73" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -18101,7 +18873,7 @@
     </row>
     <row r="74" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C74" s="1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -18113,7 +18885,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C75" s="1" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -18125,7 +18897,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C78" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -18137,7 +18909,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C79" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
@@ -18149,7 +18921,7 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C80" s="1" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
@@ -18161,7 +18933,7 @@
     </row>
     <row r="81" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C81" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
@@ -18173,7 +18945,7 @@
     </row>
     <row r="82" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C82" s="1" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -18185,7 +18957,7 @@
     </row>
     <row r="83" spans="3:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C83" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
@@ -18197,7 +18969,7 @@
     </row>
     <row r="84" spans="3:10" ht="29" x14ac:dyDescent="0.35">
       <c r="C84" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -18209,7 +18981,7 @@
     </row>
     <row r="85" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C85" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -18220,267 +18992,309 @@
       <c r="J85" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="S25:T25"/>
+  <mergeCells count="29">
+    <mergeCell ref="W9:X9"/>
+    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="P8:X8"/>
+    <mergeCell ref="P24:X24"/>
+    <mergeCell ref="C20:X20"/>
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="E3:L3"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="D8:N8"/>
+    <mergeCell ref="S9:T9"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A9:B18"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="D24:N24"/>
+    <mergeCell ref="U25:V25"/>
     <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:T36"/>
     <mergeCell ref="A25:B34"/>
     <mergeCell ref="G25:H25"/>
     <mergeCell ref="I25:J25"/>
     <mergeCell ref="K25:L25"/>
-    <mergeCell ref="O25:P25"/>
     <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="S9:T9"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:T20"/>
-    <mergeCell ref="D24:L24"/>
-    <mergeCell ref="N24:T24"/>
-    <mergeCell ref="A9:B18"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="E2:L2"/>
-    <mergeCell ref="E3:L3"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="D8:L8"/>
-    <mergeCell ref="N8:T8"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="C36:X36"/>
   </mergeCells>
   <conditionalFormatting sqref="E11:E18">
-    <cfRule type="expression" dxfId="59" priority="7">
+    <cfRule type="expression" dxfId="69" priority="17">
       <formula>AND(E11&lt;&gt;"",E11&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="8">
+    <cfRule type="expression" dxfId="68" priority="18">
       <formula>AND(E11&lt;&gt;"",E11&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E27:E34">
-    <cfRule type="expression" dxfId="57" priority="25">
+    <cfRule type="expression" dxfId="67" priority="35">
       <formula>AND(E27&lt;&gt;"",E27&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="26">
+    <cfRule type="expression" dxfId="66" priority="36">
       <formula>AND(E27&lt;&gt;"",E27&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11:F18">
-    <cfRule type="containsText" dxfId="55" priority="24" operator="containsText" text="TARGET">
+    <cfRule type="containsText" dxfId="65" priority="34" operator="containsText" text="TARGET">
       <formula>NOT(ISERROR(SEARCH("TARGET",F11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27:F34">
-    <cfRule type="containsText" dxfId="54" priority="42" operator="containsText" text="TARGET">
+    <cfRule type="containsText" dxfId="64" priority="52" operator="containsText" text="TARGET">
       <formula>NOT(ISERROR(SEARCH("TARGET",F27)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:G18">
-    <cfRule type="expression" dxfId="53" priority="9">
+    <cfRule type="expression" dxfId="63" priority="19">
       <formula>AND(G11&lt;&gt;"",G11&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="10">
+    <cfRule type="expression" dxfId="62" priority="20">
       <formula>AND(G11&lt;&gt;"",G11&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27:G34">
-    <cfRule type="expression" dxfId="51" priority="27">
+    <cfRule type="expression" dxfId="61" priority="37">
       <formula>AND(G27&lt;&gt;"",G27&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="28">
+    <cfRule type="expression" dxfId="60" priority="38">
       <formula>AND(G27&lt;&gt;"",G27&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:H18">
-    <cfRule type="expression" dxfId="49" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="53" stopIfTrue="1">
       <formula>AND(H11&lt;&gt;"",OR(G11&lt;200,H11&lt;=-25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="54" stopIfTrue="1">
       <formula>AND(H11&lt;&gt;"",G11&gt;=200,H11&gt;-25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H34">
-    <cfRule type="expression" dxfId="47" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="55" stopIfTrue="1">
       <formula>AND(H27&lt;&gt;"",OR(G27&lt;200,H27&lt;=-25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="56" stopIfTrue="1">
       <formula>AND(H27&lt;&gt;"",G27&gt;=200,H27&gt;-25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I11:I18">
-    <cfRule type="expression" dxfId="45" priority="11">
+    <cfRule type="expression" dxfId="55" priority="21">
       <formula>AND(I11&lt;&gt;"",I11&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="12">
+    <cfRule type="expression" dxfId="54" priority="22">
       <formula>AND(I11&lt;&gt;"",I11&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I27:I34">
-    <cfRule type="expression" dxfId="43" priority="29">
+    <cfRule type="expression" dxfId="53" priority="39">
       <formula>AND(I27&lt;&gt;"",I27&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="30">
+    <cfRule type="expression" dxfId="52" priority="40">
       <formula>AND(I27&lt;&gt;"",I27&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J18">
-    <cfRule type="expression" dxfId="41" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="57" stopIfTrue="1">
       <formula>AND(J11&lt;&gt;"",OR(I11&lt;200,J11&lt;=-25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="58" stopIfTrue="1">
       <formula>AND(J11&lt;&gt;"",I11&gt;=200,J11&gt;-25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J27:J34">
-    <cfRule type="expression" dxfId="39" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="59" stopIfTrue="1">
       <formula>AND(J27&lt;&gt;"",OR(I27&lt;200,J27&lt;=-25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="60" stopIfTrue="1">
       <formula>AND(J27&lt;&gt;"",I27&gt;=200,J27&gt;-25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:K18">
-    <cfRule type="expression" dxfId="37" priority="13">
+    <cfRule type="expression" dxfId="47" priority="23">
       <formula>AND(K11&lt;&gt;"",K11&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="14">
+    <cfRule type="expression" dxfId="46" priority="24">
       <formula>AND(K11&lt;&gt;"",K11&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K34">
-    <cfRule type="expression" dxfId="35" priority="31">
+    <cfRule type="expression" dxfId="45" priority="41">
       <formula>AND(K27&lt;&gt;"",K27&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="32">
+    <cfRule type="expression" dxfId="44" priority="42">
       <formula>AND(K27&lt;&gt;"",K27&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L11:L18">
-    <cfRule type="expression" dxfId="33" priority="51" stopIfTrue="1">
+  <conditionalFormatting sqref="L11:L18 N11:N18">
+    <cfRule type="expression" dxfId="43" priority="61" stopIfTrue="1">
       <formula>AND(L11&lt;&gt;"",OR(K11&lt;200,L11&lt;=-25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="62" stopIfTrue="1">
       <formula>AND(L11&lt;&gt;"",K11&gt;=200,L11&gt;-25)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L27:L34">
-    <cfRule type="expression" dxfId="31" priority="53" stopIfTrue="1">
+  <conditionalFormatting sqref="L27:L34 N27:N34">
+    <cfRule type="expression" dxfId="41" priority="63" stopIfTrue="1">
       <formula>AND(L27&lt;&gt;"",OR(K27&lt;200,L27&lt;=-25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="64" stopIfTrue="1">
       <formula>AND(L27&lt;&gt;"",K27&gt;=200,L27&gt;-25)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O11:O18">
-    <cfRule type="expression" dxfId="29" priority="6" stopIfTrue="1">
-      <formula>AND(O11&lt;&gt;"",O11&gt;=1.05*IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11)))</formula>
+  <conditionalFormatting sqref="Q11:Q18">
+    <cfRule type="expression" dxfId="23" priority="77" stopIfTrue="1">
+      <formula>AND(Q11&lt;&gt;"",Q11&gt;=1.05*IF($M11&lt;&gt;"",$M11,IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11))))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="15">
-      <formula>AND(O11&lt;&gt;"",O11&gt;=200)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="16">
-      <formula>AND(O11&lt;&gt;"",O11&lt;200)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O27:O34">
-    <cfRule type="expression" dxfId="26" priority="3" stopIfTrue="1">
-      <formula>AND(O27&lt;&gt;"",O27&gt;=1.05*IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="33">
-      <formula>AND(O27&lt;&gt;"",O27&gt;=200)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="34">
-      <formula>AND(O27&lt;&gt;"",O27&lt;200)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P11:P18">
-    <cfRule type="expression" dxfId="23" priority="55" stopIfTrue="1">
-      <formula>AND(P11&lt;&gt;"",OR(O11&lt;200,P11&lt;=-25))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="56" stopIfTrue="1">
-      <formula>AND(P11&lt;&gt;"",O11&gt;=200,P11&gt;-25)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P27:P34">
-    <cfRule type="expression" dxfId="21" priority="57" stopIfTrue="1">
-      <formula>AND(P27&lt;&gt;"",OR(O27&lt;200,P27&lt;=-25))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="58" stopIfTrue="1">
-      <formula>AND(P27&lt;&gt;"",O27&gt;=200,P27&gt;-25)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q11:Q18">
-    <cfRule type="expression" dxfId="19" priority="5" stopIfTrue="1">
-      <formula>AND(Q11&lt;&gt;"",Q11&gt;=1.05*IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="17">
+    <cfRule type="expression" dxfId="22" priority="25">
       <formula>AND(Q11&lt;&gt;"",Q11&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="18">
+    <cfRule type="expression" dxfId="21" priority="26">
       <formula>AND(Q11&lt;&gt;"",Q11&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q27:Q34">
-    <cfRule type="expression" dxfId="16" priority="2" stopIfTrue="1">
-      <formula>AND(Q27&lt;&gt;"",Q27&gt;=1.05*IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27)))</formula>
+    <cfRule type="expression" dxfId="11" priority="81" stopIfTrue="1">
+      <formula>AND(Q27&lt;&gt;"",Q27&gt;=1.05*IF($M27&lt;&gt;"",$M27,IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27))))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="35">
+    <cfRule type="expression" dxfId="10" priority="43">
       <formula>AND(Q27&lt;&gt;"",Q27&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="36">
+    <cfRule type="expression" dxfId="9" priority="44">
       <formula>AND(Q27&lt;&gt;"",Q27&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R11:R18">
-    <cfRule type="expression" dxfId="13" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="65" stopIfTrue="1">
       <formula>AND(R11&lt;&gt;"",OR(Q11&lt;200,R11&lt;=-25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="66" stopIfTrue="1">
       <formula>AND(R11&lt;&gt;"",Q11&gt;=200,R11&gt;-25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R27:R34">
-    <cfRule type="expression" dxfId="11" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="67" stopIfTrue="1">
       <formula>AND(R27&lt;&gt;"",OR(Q27&lt;200,R27&lt;=-25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="68" stopIfTrue="1">
       <formula>AND(R27&lt;&gt;"",Q27&gt;=200,R27&gt;-25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S11:S18">
-    <cfRule type="expression" dxfId="9" priority="4" stopIfTrue="1">
-      <formula>AND(S11&lt;&gt;"",S11&gt;=1.05*IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11)))</formula>
+    <cfRule type="expression" dxfId="20" priority="78" stopIfTrue="1">
+      <formula>AND(S11&lt;&gt;"",S11&gt;=1.05*IF($M11&lt;&gt;"",$M11,IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11))))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="19">
+    <cfRule type="expression" dxfId="19" priority="27">
       <formula>AND(S11&lt;&gt;"",S11&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="20">
+    <cfRule type="expression" dxfId="18" priority="28">
       <formula>AND(S11&lt;&gt;"",S11&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S27:S34">
-    <cfRule type="expression" dxfId="6" priority="1" stopIfTrue="1">
-      <formula>AND(S27&lt;&gt;"",S27&gt;=1.05*IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27)))</formula>
+    <cfRule type="expression" dxfId="8" priority="82" stopIfTrue="1">
+      <formula>AND(S27&lt;&gt;"",S27&gt;=1.05*IF($M27&lt;&gt;"",$M27,IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27))))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="37">
+    <cfRule type="expression" dxfId="7" priority="45">
       <formula>AND(S27&lt;&gt;"",S27&gt;=200)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="38">
+    <cfRule type="expression" dxfId="6" priority="46">
       <formula>AND(S27&lt;&gt;"",S27&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T11:T18">
-    <cfRule type="expression" dxfId="3" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="69" stopIfTrue="1">
       <formula>AND(T11&lt;&gt;"",OR(S11&lt;200,T11&lt;=-25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="70" stopIfTrue="1">
       <formula>AND(T11&lt;&gt;"",S11&gt;=200,T11&gt;-25)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T27:T34">
-    <cfRule type="expression" dxfId="1" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="71" stopIfTrue="1">
       <formula>AND(T27&lt;&gt;"",OR(S27&lt;200,T27&lt;=-25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="72" stopIfTrue="1">
       <formula>AND(T27&lt;&gt;"",S27&gt;=200,T27&gt;-25)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U11:U18">
+    <cfRule type="expression" dxfId="17" priority="79" stopIfTrue="1">
+      <formula>AND(U11&lt;&gt;"",U11&gt;=1.05*IF($M11&lt;&gt;"",$M11,IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11))))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="29">
+      <formula>AND(U11&lt;&gt;"",U11&gt;=200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="30">
+      <formula>AND(U11&lt;&gt;"",U11&lt;200)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U27:U34">
+    <cfRule type="expression" dxfId="5" priority="83" stopIfTrue="1">
+      <formula>AND(U27&lt;&gt;"",U27&gt;=1.05*IF($M27&lt;&gt;"",$M27,IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27))))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="47">
+      <formula>AND(U27&lt;&gt;"",U27&gt;=200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="48">
+      <formula>AND(U27&lt;&gt;"",U27&lt;200)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V11:V18 X11:X18">
+    <cfRule type="expression" dxfId="31" priority="73" stopIfTrue="1">
+      <formula>AND(V11&lt;&gt;"",OR(U11&lt;200,V11&lt;=-25))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="74" stopIfTrue="1">
+      <formula>AND(V11&lt;&gt;"",U11&gt;=200,V11&gt;-25)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V27:V34 X27:X34">
+    <cfRule type="expression" dxfId="29" priority="75" stopIfTrue="1">
+      <formula>AND(V27&lt;&gt;"",OR(U27&lt;200,V27&lt;=-25))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="76" stopIfTrue="1">
+      <formula>AND(V27&lt;&gt;"",U27&gt;=200,V27&gt;-25)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M11:M18">
+    <cfRule type="expression" dxfId="27" priority="9">
+      <formula>AND(M11&lt;&gt;"",M11&gt;=200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="10">
+      <formula>AND(M11&lt;&gt;"",M11&lt;200)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M27:M34">
+    <cfRule type="expression" dxfId="25" priority="7">
+      <formula>AND(M27&lt;&gt;"",M27&gt;=200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="8">
+      <formula>AND(M27&lt;&gt;"",M27&lt;200)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W11:W18">
+    <cfRule type="expression" dxfId="14" priority="80" stopIfTrue="1">
+      <formula>AND(W11&lt;&gt;"",W11&gt;=1.05*IF($M11&lt;&gt;"",$M11,IF($K11&lt;&gt;"",$K11,IF($I11&lt;&gt;"",$I11,$G11))))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="5">
+      <formula>AND(W11&lt;&gt;"",W11&gt;=200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="6">
+      <formula>AND(W11&lt;&gt;"",W11&lt;200)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W27:W34">
+    <cfRule type="expression" dxfId="2" priority="84" stopIfTrue="1">
+      <formula>AND(W27&lt;&gt;"",W27&gt;=1.05*IF($M27&lt;&gt;"",$M27,IF($K27&lt;&gt;"",$K27,IF($I27&lt;&gt;"",$I27,$G27))))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>AND(W27&lt;&gt;"",W27&gt;=200)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>AND(W27&lt;&gt;"",W27&lt;200)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -18492,7 +19306,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="54" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="45" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
